--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -1151,13 +1151,13 @@
         <v>1.64</v>
       </c>
       <c r="H4" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="G8" t="n">
         <v>3.35</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -766,10 +766,10 @@
         <v>2.34</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -1736,13 +1736,13 @@
         <v>2.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="G2" t="n">
         <v>3.35</v>
@@ -766,13 +766,13 @@
         <v>2.34</v>
       </c>
       <c r="I2" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G3" t="n">
         <v>3.35</v>
       </c>
       <c r="H3" t="n">
-        <v>2.94</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>4.4</v>
@@ -966,7 +966,7 @@
         <v>2.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v>3.35</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I8" t="n">
         <v>4</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="I9" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
         <v>2.38</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q9" t="n">
         <v>3</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Aris FC Limassol</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 09:16:36</t>
+          <t>2026-04-12 11:37:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Apollon Limassol</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>2.86</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 09:16:36</t>
+          <t>2026-04-12 11:37:19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hunedoara</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Puskas Akademia</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1.64</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.66</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 09:16:36</t>
+          <t>2026-04-12 11:37:19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="G5" t="n">
-        <v>660</v>
+        <v>3.35</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 09:16:36</t>
+          <t>2026-04-12 11:37:19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 09:16:36</t>
+          <t>2026-04-12 11:37:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 09:16:36</t>
+          <t>2026-04-12 11:37:19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Puskas Akademia</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="G8" t="n">
-        <v>3.35</v>
+        <v>1.58</v>
       </c>
       <c r="H8" t="n">
-        <v>2.74</v>
+        <v>6.4</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.44</v>
+        <v>1.49</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,201 +2084,977 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 09:16:36</t>
+          <t>2026-04-12 11:37:19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Italian Serie B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-04-12 11:37:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Varnamo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-12 11:37:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Dobrudzha</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Botev Plovdiv</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-12 11:37:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Egyptian Premier</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Kahraba Ismailia</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ismaily</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-12 11:37:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Al Ittihad (EGY)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>ZED FC</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G13" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H13" t="n">
         <v>2.68</v>
       </c>
-      <c r="I9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="I13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-04-12 09:16:36</t>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-12 11:37:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BH14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,31 +760,31 @@
         <v>3.1</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="H2" t="n">
         <v>2.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
         <v>1.95</v>
@@ -793,134 +793,134 @@
         <v>1.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="H3" t="n">
         <v>2.86</v>
       </c>
       <c r="I3" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
@@ -969,16 +969,16 @@
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
         <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
         <v>1.8</v>
@@ -990,7 +990,7 @@
         <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="T3" t="n">
         <v>1.65</v>
@@ -999,7 +999,7 @@
         <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
         <v>1.54</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.26</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -1339,34 +1339,34 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
         <v>3.35</v>
       </c>
       <c r="H5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I5" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
         <v>1.91</v>
@@ -1375,134 +1375,134 @@
         <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -1551,152 +1551,152 @@
         <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -1727,34 +1727,34 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
         <v>1.7</v>
@@ -1763,141 +1763,141 @@
         <v>2.12</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Puskas Akademia</t>
+          <t>NK Maribor</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.46</v>
+        <v>2.42</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="n">
-        <v>6.4</v>
+        <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>8.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>6.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Puskas Akademia</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>1.46</v>
       </c>
       <c r="G9" t="n">
-        <v>2.94</v>
+        <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>2.82</v>
+        <v>6.4</v>
       </c>
       <c r="I9" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>3.85</v>
+        <v>1.97</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>2.78</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.97</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.36</v>
+        <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="H12" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="J12" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>1.97</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,373 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Kahraba Ismailia</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ismaily</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-12 13:55:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Al Ittihad (EGY)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>ZED FC</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="F14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G14" t="n">
         <v>4</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H14" t="n">
         <v>2.68</v>
       </c>
-      <c r="I13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="I14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2026-04-12 11:37:19</t>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH14"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
@@ -775,19 +775,19 @@
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
         <v>1.88</v>
@@ -796,16 +796,16 @@
         <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="W2" t="n">
         <v>1.39</v>
@@ -820,7 +820,7 @@
         <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="n">
         <v>16.5</v>
@@ -832,13 +832,13 @@
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF2" t="n">
         <v>29</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -862,7 +862,7 @@
         <v>42</v>
       </c>
       <c r="AO2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
         <v>11</v>
@@ -871,16 +871,16 @@
         <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
         <v>8.4</v>
@@ -892,7 +892,7 @@
         <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>12</v>
@@ -916,11 +916,11 @@
         <v>24</v>
       </c>
       <c r="BG2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
         <v>2.86</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
@@ -978,7 +978,7 @@
         <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
         <v>1.8</v>
@@ -999,7 +999,7 @@
         <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
         <v>1.54</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -1339,55 +1339,55 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J5" t="n">
         <v>3.35</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
         <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R5" t="n">
         <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W5" t="n">
         <v>1.43</v>
@@ -1396,10 +1396,10 @@
         <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
         <v>40</v>
@@ -1417,7 +1417,7 @@
         <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
         <v>16</v>
@@ -1432,7 +1432,7 @@
         <v>65</v>
       </c>
       <c r="AK5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
@@ -1444,7 +1444,7 @@
         <v>38</v>
       </c>
       <c r="AO5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
@@ -1456,7 +1456,7 @@
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1480,29 +1480,29 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC5" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
         <v>16</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -1536,167 +1536,167 @@
         <v>2.56</v>
       </c>
       <c r="G6" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="H6" t="n">
         <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
         <v>2.76</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.57</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>1.45</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q6" t="n">
         <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY6" t="n">
         <v>11</v>
       </c>
-      <c r="Y6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
+      <c r="AZ6" t="n">
         <v>20</v>
       </c>
-      <c r="AH6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BA6" t="n">
-        <v>2.28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.22</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.28</v>
+        <v>8.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.28</v>
+        <v>7.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
         <v>2.72</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J7" t="n">
         <v>2.66</v>
@@ -1745,13 +1745,13 @@
         <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.37</v>
@@ -1763,134 +1763,134 @@
         <v>2.12</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
         <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL7" t="n">
         <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
         <v>5.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY7" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BD7" t="n">
         <v>36</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
         <v>1.94</v>
@@ -1969,7 +1969,7 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
         <v>1.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.46</v>
       </c>
       <c r="G9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H9" t="n">
         <v>6.4</v>
@@ -2130,162 +2130,162 @@
         <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q9" t="n">
         <v>1.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="H10" t="n">
-        <v>2.86</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X10" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF10" t="n">
         <v>3.3</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>1.97</v>
+        <v>2.82</v>
       </c>
       <c r="H11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.3</v>
       </c>
-      <c r="I11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -2703,10 +2703,10 @@
         <v>3.85</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I12" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J12" t="n">
         <v>3.2</v>
@@ -2715,16 +2715,16 @@
         <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P12" t="n">
         <v>1.81</v>
@@ -2733,134 +2733,134 @@
         <v>1.97</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="I13" t="n">
         <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,1528 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H14" t="n">
         <v>2.68</v>
       </c>
       <c r="I14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J14" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Q14" t="n">
         <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Al-Quadisiya (KSA)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Al-Shabab (KSA)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X15" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Queens Park</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Raith</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Aldershot</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Southend</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Woking</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Solihull Moors</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Wealdstone</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Boston Utd</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Airdrieonians</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Dunfermline</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Scottish League One</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Peterhead</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Inverness CT</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,22 +760,22 @@
         <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="H2" t="n">
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -784,10 +784,10 @@
         <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
         <v>1.88</v>
@@ -799,13 +799,13 @@
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W2" t="n">
         <v>1.39</v>
@@ -874,7 +874,7 @@
         <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -898,19 +898,19 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>60</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>24</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="H3" t="n">
         <v>2.86</v>
@@ -966,7 +966,7 @@
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>1.41</v>
@@ -999,7 +999,7 @@
         <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
         <v>1.54</v>
@@ -1068,7 +1068,7 @@
         <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
         <v>7.6</v>
@@ -1080,7 +1080,7 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
@@ -1092,19 +1092,19 @@
         <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>70</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>18.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
@@ -1369,10 +1369,10 @@
         <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
         <v>1.35</v>
@@ -1381,16 +1381,16 @@
         <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
         <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X5" t="n">
         <v>17</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
@@ -1572,7 +1572,7 @@
         <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T6" t="n">
         <v>2.14</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
         <v>2.72</v>
       </c>
       <c r="I7" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.45</v>
@@ -1751,10 +1751,10 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="P7" t="n">
         <v>1.7</v>
@@ -1766,7 +1766,7 @@
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
         <v>1.8</v>
@@ -1778,7 +1778,7 @@
         <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="X7" t="n">
         <v>13.5</v>
@@ -1844,7 +1844,7 @@
         <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
         <v>7.8</v>
@@ -1856,7 +1856,7 @@
         <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
         <v>13.5</v>
@@ -1868,19 +1868,19 @@
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>75</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H9" t="n">
         <v>6.4</v>
@@ -2127,13 +2127,13 @@
         <v>8.4</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
@@ -2148,7 +2148,7 @@
         <v>2.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R9" t="n">
         <v>1.56</v>
@@ -2157,16 +2157,16 @@
         <v>2.06</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2196,7 +2196,7 @@
         <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2223,52 +2223,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.97</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>2.12</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="AA10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM10" t="n">
         <v>120</v>
       </c>
-      <c r="AB10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AN10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR10" t="n">
         <v>15</v>
       </c>
-      <c r="AG10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN10" t="n">
+      <c r="AS10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT10" t="n">
         <v>9.4</v>
       </c>
-      <c r="AO10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AU10" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4</v>
       </c>
       <c r="BA10" t="n">
         <v>4.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.3</v>
+        <v>20</v>
       </c>
       <c r="BG10" t="n">
         <v>4.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>3.3</v>
       </c>
       <c r="K11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU11" t="n">
         <v>3.6</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X11" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS11" t="n">
+      <c r="AV11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW11" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AX11" t="n">
-        <v>13.5</v>
+        <v>3.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>3.6</v>
       </c>
       <c r="AZ11" t="n">
         <v>4.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD11" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
         <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>20</v>
+        <v>3.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H12" t="n">
         <v>2.28</v>
@@ -2712,7 +2712,7 @@
         <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2733,22 +2733,22 @@
         <v>1.97</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>1.97</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V12" t="n">
         <v>1.56</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
         <v>18.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -2897,16 +2897,16 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2933,19 +2933,19 @@
         <v>5.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="V13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W13" t="n">
         <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y13" t="n">
         <v>10.5</v>
@@ -2957,7 +2957,7 @@
         <v>70</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC13" t="n">
         <v>8</v>
@@ -2969,10 +2969,10 @@
         <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH13" t="n">
         <v>27</v>
@@ -2984,7 +2984,7 @@
         <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL13" t="n">
         <v>80</v>
@@ -2999,28 +2999,28 @@
         <v>75</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3029,32 +3029,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -3109,13 +3109,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="O14" t="n">
         <v>1.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q14" t="n">
         <v>3</v>
@@ -3124,7 +3124,7 @@
         <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3139,34 +3139,34 @@
         <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AA14" t="n">
         <v>75</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="AH14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.81</v>
+        <v>3.9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.86</v>
+        <v>3.9</v>
       </c>
       <c r="AR14" t="n">
-        <v>10</v>
+        <v>2.02</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.26</v>
+        <v>8</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.92</v>
+        <v>4.3</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.88</v>
+        <v>4.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="AW14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BB14" t="n">
         <v>2.24</v>
       </c>
-      <c r="AX14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>2.32</v>
-      </c>
       <c r="BC14" t="n">
-        <v>2.32</v>
+        <v>1.27</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.32</v>
+        <v>1.27</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.32</v>
+        <v>1.28</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.32</v>
+        <v>1.27</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G15" t="n">
         <v>1.78</v>
@@ -3303,22 +3303,22 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="Q15" t="n">
         <v>1.42</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T15" t="n">
         <v>1.5</v>
@@ -3327,16 +3327,16 @@
         <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X15" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y15" t="n">
         <v>36</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>34</v>
       </c>
       <c r="Z15" t="n">
         <v>60</v>
@@ -3354,10 +3354,10 @@
         <v>27</v>
       </c>
       <c r="AE15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG15" t="n">
         <v>13</v>
@@ -3387,19 +3387,19 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="AR15" t="n">
         <v>4</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
         <v>8.800000000000001</v>
@@ -3408,13 +3408,13 @@
         <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="AZ15" t="n">
         <v>13</v>
@@ -3423,33 +3423,33 @@
         <v>4</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="BC15" t="n">
         <v>11</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Queens Park</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Raith</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
-        <v>2.62</v>
+        <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>2.96</v>
+        <v>2.04</v>
       </c>
       <c r="J16" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="M16" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.51</v>
+        <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>1.54</v>
+        <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.52</v>
+        <v>1.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
-        <v>5.1</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="W16" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -3658,169 +3658,169 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H17" t="n">
         <v>3.65</v>
       </c>
-      <c r="G17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.78</v>
-      </c>
       <c r="I17" t="n">
-        <v>2.08</v>
+        <v>4.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU17" t="n">
         <v>5.4</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -3852,112 +3852,112 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Boston Utd</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="G18" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="H18" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="R18" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>1.84</v>
+        <v>2.42</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
@@ -3969,52 +3969,52 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Boston Utd</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="I19" t="n">
-        <v>3.95</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.15</v>
       </c>
-      <c r="K19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.12</v>
-      </c>
       <c r="O19" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>2.06</v>
       </c>
       <c r="R19" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>1.69</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="W19" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Queens Park</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Raith</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H20" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="I20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N20" t="n">
         <v>2.6</v>
       </c>
-      <c r="J20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O20" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V20" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR20" t="n">
         <v>13</v>
       </c>
-      <c r="Y20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE20" t="n">
+      <c r="AS20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW20" t="n">
         <v>30</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>20</v>
       </c>
       <c r="AX20" t="n">
         <v>16.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BB20" t="n">
         <v>44</v>
       </c>
       <c r="BC20" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BD20" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BE20" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="BF20" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BG20" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -4449,52 +4449,52 @@
         <v>1000</v>
       </c>
       <c r="H21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
         <v>1.04</v>
       </c>
-      <c r="I21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N21" t="n">
-        <v>1.08</v>
+        <v>1.94</v>
       </c>
       <c r="O21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P21" t="n">
-        <v>1.08</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="R21" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U21" t="n">
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,395 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X22" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-12 18:24:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X23" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -760,13 +760,13 @@
         <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="H2" t="n">
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
@@ -775,7 +775,7 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -805,7 +805,7 @@
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W2" t="n">
         <v>1.39</v>
@@ -874,7 +874,7 @@
         <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -898,29 +898,29 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>24</v>
+        <v>3.9</v>
       </c>
       <c r="BG2" t="n">
         <v>13</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H3" t="n">
         <v>2.86</v>
@@ -999,10 +999,10 @@
         <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
         <v>16</v>
@@ -1023,7 +1023,7 @@
         <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
         <v>46</v>
@@ -1068,7 +1068,7 @@
         <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
         <v>7.6</v>
@@ -1080,7 +1080,7 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
@@ -1092,29 +1092,29 @@
         <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>18.5</v>
+        <v>3.75</v>
       </c>
       <c r="BG3" t="n">
-        <v>25</v>
+        <v>3.85</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -1345,10 +1345,10 @@
         <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I5" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
         <v>3.45</v>
@@ -1387,7 +1387,7 @@
         <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
         <v>1.44</v>
@@ -1396,22 +1396,22 @@
         <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA5" t="n">
         <v>40</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
         <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>32</v>
@@ -1420,10 +1420,10 @@
         <v>25</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
         <v>46</v>
@@ -1444,7 +1444,7 @@
         <v>38</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
@@ -1456,7 +1456,7 @@
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1480,29 +1480,29 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BG5" t="n">
         <v>16</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
         <v>2.72</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
@@ -1751,10 +1751,10 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
         <v>1.7</v>
@@ -1766,7 +1766,7 @@
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
         <v>1.8</v>
@@ -1844,7 +1844,7 @@
         <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT7" t="n">
         <v>7.8</v>
@@ -1856,7 +1856,7 @@
         <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX7" t="n">
         <v>13.5</v>
@@ -1868,29 +1868,29 @@
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>25</v>
+        <v>3.85</v>
       </c>
       <c r="BG7" t="n">
-        <v>25</v>
+        <v>3.85</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
         <v>1.56</v>
@@ -2124,28 +2124,28 @@
         <v>6.4</v>
       </c>
       <c r="I9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
         <v>1.49</v>
@@ -2154,13 +2154,13 @@
         <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="U9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
@@ -2253,7 +2253,7 @@
         <v>7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
@@ -2262,7 +2262,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD9" t="n">
         <v>1.03</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
@@ -2378,22 +2378,22 @@
         <v>12.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
         <v>36</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
         <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>55</v>
@@ -2414,7 +2414,7 @@
         <v>32</v>
       </c>
       <c r="AO10" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2426,7 +2426,7 @@
         <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT10" t="n">
         <v>9.4</v>
@@ -2438,7 +2438,7 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
@@ -2447,32 +2447,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF10" t="n">
         <v>20</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
         <v>4.8</v>
@@ -2524,25 +2524,25 @@
         <v>1.29</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
         <v>1.02</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
         <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T11" t="n">
         <v>1.62</v>
@@ -2557,116 +2557,116 @@
         <v>2.08</v>
       </c>
       <c r="X11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
         <v>26</v>
       </c>
-      <c r="Z11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>22</v>
-      </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK11" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.6</v>
+        <v>1.41</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.9</v>
+        <v>1.45</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.75</v>
+        <v>1.34</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.6</v>
+        <v>1.45</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.1</v>
+        <v>1.37</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.6</v>
+        <v>1.32</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.1</v>
+        <v>1.37</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.1</v>
+        <v>1.37</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>1.45</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.4</v>
+        <v>1.45</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>1.43</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.3</v>
+        <v>1.45</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>1.45</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H12" t="n">
         <v>2.28</v>
@@ -2748,13 +2748,13 @@
         <v>1.56</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
         <v>18.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
         <v>21</v>
@@ -2766,10 +2766,10 @@
         <v>17.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
         <v>38</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -2906,13 +2906,13 @@
         <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
         <v>2.54</v>
@@ -2933,10 +2933,10 @@
         <v>5.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="V13" t="n">
         <v>1.43</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
         <v>1.87</v>
       </c>
       <c r="O14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="P14" t="n">
         <v>1.37</v>
@@ -3124,7 +3124,7 @@
         <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3244,11 +3244,11 @@
         <v>1.27</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="H15" t="n">
         <v>5.2</v>
@@ -3330,7 +3330,7 @@
         <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="X15" t="n">
         <v>38</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J16" t="n">
         <v>3.85</v>
@@ -3494,7 +3494,7 @@
         <v>1.23</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
         <v>5.3</v>
@@ -3506,7 +3506,7 @@
         <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R16" t="n">
         <v>1.66</v>
@@ -3521,7 +3521,7 @@
         <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="W16" t="n">
         <v>1.25</v>
@@ -3581,62 +3581,62 @@
         <v>8.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BG16" t="n">
         <v>5.9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G17" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="H17" t="n">
         <v>3.65</v>
       </c>
       <c r="I17" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
@@ -3706,7 +3706,7 @@
         <v>1.14</v>
       </c>
       <c r="S17" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3715,49 +3715,49 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC17" t="n">
         <v>12.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
         <v>15.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK17" t="n">
         <v>30</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU17" t="n">
         <v>5.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY17" t="n">
         <v>6.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC17" t="n">
         <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.16</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
@@ -3873,7 +3873,7 @@
         <v>3.55</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
         <v>4.2</v>
@@ -3891,13 +3891,13 @@
         <v>1.21</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
         <v>1.69</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
         <v>2.42</v>
@@ -3912,13 +3912,13 @@
         <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z18" t="n">
         <v>36</v>
@@ -3933,7 +3933,7 @@
         <v>13</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
@@ -3969,7 +3969,7 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="AQ18" t="n">
         <v>9.199999999999999</v>
@@ -3978,10 +3978,10 @@
         <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU18" t="n">
         <v>5.6</v>
@@ -3990,7 +3990,7 @@
         <v>8.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -4002,7 +4002,7 @@
         <v>9.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="BB18" t="n">
         <v>17.5</v>
@@ -4014,17 +4014,17 @@
         <v>19</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
         <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
         <v>3.15</v>
@@ -4094,13 +4094,13 @@
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="V19" t="n">
         <v>1.62</v>
@@ -4172,7 +4172,7 @@
         <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
@@ -4196,19 +4196,19 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>80</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
         <v>32</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
         <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U20" t="n">
         <v>1.8</v>
@@ -4396,13 +4396,13 @@
         <v>44</v>
       </c>
       <c r="BC20" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
         <v>50</v>
       </c>
       <c r="BE20" t="n">
-        <v>120</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
         <v>44</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I21" t="n">
         <v>1.63</v>
       </c>
       <c r="J21" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4476,7 +4476,7 @@
         <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R21" t="n">
         <v>1.32</v>
@@ -4488,10 +4488,10 @@
         <v>1.66</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="W21" t="n">
         <v>1.13</v>
@@ -4551,52 +4551,52 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
         <v>2.58</v>
       </c>
       <c r="I22" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>4.4</v>
@@ -4667,16 +4667,16 @@
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
         <v>1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T22" t="n">
         <v>1.49</v>
@@ -4685,7 +4685,7 @@
         <v>2.9</v>
       </c>
       <c r="V22" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W22" t="n">
         <v>1.64</v>
@@ -4694,7 +4694,7 @@
         <v>32</v>
       </c>
       <c r="Y22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z22" t="n">
         <v>23</v>
@@ -4715,7 +4715,7 @@
         <v>22</v>
       </c>
       <c r="AF22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG22" t="n">
         <v>12.5</v>
@@ -4763,7 +4763,7 @@
         <v>10</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
         <v>21</v>
@@ -4781,7 +4781,7 @@
         <v>24</v>
       </c>
       <c r="BB22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC22" t="n">
         <v>21</v>
@@ -4796,11 +4796,11 @@
         <v>11</v>
       </c>
       <c r="BG22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -4831,37 +4831,37 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G23" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I23" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="J23" t="n">
         <v>4.6</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.12</v>
       </c>
       <c r="P23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q23" t="n">
         <v>1.38</v>
@@ -4870,25 +4870,25 @@
         <v>2.02</v>
       </c>
       <c r="S23" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T23" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U23" t="n">
         <v>3.15</v>
       </c>
       <c r="V23" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
         <v>42</v>
       </c>
       <c r="Y23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="n">
         <v>18</v>
@@ -4897,7 +4897,7 @@
         <v>24</v>
       </c>
       <c r="AB23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AC23" t="n">
         <v>12.5</v>
@@ -4951,10 +4951,10 @@
         <v>21</v>
       </c>
       <c r="AT23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV23" t="n">
         <v>10.5</v>
@@ -4963,7 +4963,7 @@
         <v>14.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY23" t="n">
         <v>16</v>
@@ -4990,11 +4990,11 @@
         <v>17.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -760,13 +760,13 @@
         <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="H2" t="n">
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
@@ -805,7 +805,7 @@
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W2" t="n">
         <v>1.39</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H3" t="n">
         <v>2.86</v>
       </c>
       <c r="I3" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
@@ -999,7 +999,7 @@
         <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
         <v>1.55</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>2.36</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J5" t="n">
         <v>3.45</v>
@@ -1357,7 +1357,7 @@
         <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
@@ -1387,7 +1387,7 @@
         <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W5" t="n">
         <v>1.44</v>
@@ -1408,7 +1408,7 @@
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>13</v>
@@ -1456,7 +1456,7 @@
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1480,29 +1480,29 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD5" t="n">
         <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
         <v>16</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G6" t="n">
         <v>2.9</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -1751,10 +1751,10 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
         <v>1.7</v>
@@ -1778,7 +1778,7 @@
         <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="X7" t="n">
         <v>13.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG9" t="n">
         <v>15</v>
@@ -2217,22 +2217,22 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
@@ -2241,10 +2241,10 @@
         <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AX9" t="n">
         <v>7.2</v>
@@ -2256,7 +2256,7 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BB9" t="n">
         <v>9.199999999999999</v>
@@ -2265,20 +2265,20 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -2324,13 +2324,13 @@
         <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
         <v>3.45</v>
@@ -2426,7 +2426,7 @@
         <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT10" t="n">
         <v>9.4</v>
@@ -2438,7 +2438,7 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
@@ -2447,19 +2447,19 @@
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE10" t="n">
         <v>5.5</v>
@@ -2468,11 +2468,11 @@
         <v>20</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -2509,13 +2509,13 @@
         <v>1.97</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
         <v>4.8</v>
@@ -2539,22 +2539,22 @@
         <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="T11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2605,68 +2605,68 @@
         <v>100</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="H12" t="n">
         <v>2.28</v>
       </c>
       <c r="I12" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J12" t="n">
         <v>3.2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I13" t="n">
         <v>3.3</v>
@@ -2906,13 +2906,13 @@
         <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
         <v>2.54</v>
@@ -2975,7 +2975,7 @@
         <v>15.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
         <v>85</v>
@@ -3032,7 +3032,7 @@
         <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB13" t="n">
         <v>5.4</v>
@@ -3041,7 +3041,7 @@
         <v>5.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE13" t="n">
         <v>5.8</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.25</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.15</v>
       </c>
       <c r="L14" t="n">
         <v>1.67</v>
@@ -3109,13 +3109,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="O14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="P14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q14" t="n">
         <v>3</v>
@@ -3133,28 +3133,28 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X14" t="n">
-        <v>6.8</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.8</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3166,7 +3166,7 @@
         <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
         <v>1000</v>
@@ -3193,16 +3193,16 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>1.27</v>
       </c>
       <c r="AT14" t="n">
         <v>4.3</v>
@@ -3217,38 +3217,38 @@
         <v>8</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BA14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BG14" t="n">
         <v>1.99</v>
       </c>
-      <c r="BB14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="G15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
         <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,13 +3303,13 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q15" t="n">
         <v>1.42</v>
@@ -3327,31 +3327,31 @@
         <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="X15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z15" t="n">
         <v>60</v>
       </c>
       <c r="AA15" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>70</v>
@@ -3363,10 +3363,10 @@
         <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
         <v>21</v>
@@ -3387,43 +3387,43 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AR15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT15" t="n">
         <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>16</v>
+        <v>3.9</v>
       </c>
       <c r="AW15" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>3.75</v>
       </c>
       <c r="BA15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BC15" t="n">
         <v>11</v>
@@ -3432,17 +3432,17 @@
         <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>2.78</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
         <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R16" t="n">
         <v>1.66</v>
@@ -3521,7 +3521,7 @@
         <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="W16" t="n">
         <v>1.25</v>
@@ -3530,10 +3530,10 @@
         <v>34</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AA16" t="n">
         <v>25</v>
@@ -3542,10 +3542,10 @@
         <v>28</v>
       </c>
       <c r="AC16" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
         <v>20</v>
@@ -3557,7 +3557,7 @@
         <v>21</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI16" t="n">
         <v>29</v>
@@ -3578,7 +3578,7 @@
         <v>32</v>
       </c>
       <c r="AO16" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AP16" t="n">
         <v>4.4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="H17" t="n">
         <v>3.65</v>
@@ -3679,7 +3679,7 @@
         <v>4.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
@@ -3718,7 +3718,7 @@
         <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>3.6</v>
       </c>
       <c r="H19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I19" t="n">
         <v>2.6</v>
@@ -4109,7 +4109,7 @@
         <v>1.39</v>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Y19" t="n">
         <v>11.5</v>
@@ -4172,7 +4172,7 @@
         <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
@@ -4196,29 +4196,29 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>32</v>
+        <v>4.9</v>
       </c>
       <c r="BG19" t="n">
         <v>17.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H20" t="n">
         <v>2.66</v>
@@ -4276,7 +4276,7 @@
         <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P20" t="n">
         <v>1.54</v>
@@ -4291,7 +4291,7 @@
         <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
         <v>1.8</v>
@@ -4300,10 +4300,10 @@
         <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y20" t="n">
         <v>8.800000000000001</v>
@@ -4396,23 +4396,23 @@
         <v>44</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD20" t="n">
         <v>50</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF20" t="n">
-        <v>44</v>
+        <v>7.4</v>
       </c>
       <c r="BG20" t="n">
         <v>34</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
         <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>1.86</v>
+        <v>2.36</v>
       </c>
       <c r="W21" t="n">
         <v>1.13</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>1.81</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>1.76</v>
       </c>
       <c r="S22" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T22" t="n">
         <v>1.49</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G23" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I23" t="n">
         <v>1.87</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.89</v>
       </c>
       <c r="J23" t="n">
         <v>4.6</v>
@@ -4879,22 +4879,22 @@
         <v>3.15</v>
       </c>
       <c r="V23" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W23" t="n">
         <v>1.33</v>
       </c>
       <c r="X23" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Y23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB23" t="n">
         <v>32</v>
@@ -4915,7 +4915,7 @@
         <v>17.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI23" t="n">
         <v>21</v>
@@ -4930,7 +4930,7 @@
         <v>34</v>
       </c>
       <c r="AM23" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN23" t="n">
         <v>19</v>
@@ -4942,7 +4942,7 @@
         <v>34</v>
       </c>
       <c r="AQ23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR23" t="n">
         <v>16.5</v>
@@ -4951,7 +4951,7 @@
         <v>21</v>
       </c>
       <c r="AT23" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AU23" t="n">
         <v>11.5</v>
@@ -4975,26 +4975,26 @@
         <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BC23" t="n">
         <v>32</v>
       </c>
       <c r="BD23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE23" t="n">
         <v>36</v>
       </c>
       <c r="BF23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG23" t="n">
         <v>5.7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -760,22 +760,22 @@
         <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="n">
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -793,22 +793,22 @@
         <v>1.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
         <v>18.5</v>
@@ -826,7 +826,7 @@
         <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
         <v>14</v>
@@ -874,7 +874,7 @@
         <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
         <v>18</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY2" t="n">
         <v>10.5</v>
@@ -898,13 +898,13 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB2" t="n">
         <v>4</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BD2" t="n">
         <v>4</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -954,43 +954,43 @@
         <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
         <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
         <v>1.65</v>
@@ -1002,7 +1002,7 @@
         <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X3" t="n">
         <v>16</v>
@@ -1089,7 +1089,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
         <v>3.95</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I5" t="n">
         <v>2.58</v>
@@ -1369,19 +1369,19 @@
         <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R5" t="n">
         <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
         <v>2.12</v>
@@ -1483,7 +1483,7 @@
         <v>5.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC5" t="n">
         <v>5.8</v>
@@ -1492,7 +1492,7 @@
         <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
         <v>6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
         <v>2.9</v>
@@ -1551,7 +1551,7 @@
         <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>2.78</v>
       </c>
       <c r="G7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.45</v>
@@ -1751,10 +1751,10 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
         <v>1.7</v>
@@ -1766,7 +1766,7 @@
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
         <v>1.8</v>
@@ -1778,7 +1778,7 @@
         <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="X7" t="n">
         <v>13.5</v>
@@ -1796,7 +1796,7 @@
         <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
         <v>16</v>
@@ -1811,7 +1811,7 @@
         <v>16</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
         <v>65</v>
@@ -1844,19 +1844,19 @@
         <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
         <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AV7" t="n">
         <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AX7" t="n">
         <v>13.5</v>
@@ -1868,29 +1868,29 @@
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC7" t="n">
         <v>3.95</v>
       </c>
-      <c r="BB7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BD7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
         <v>4.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>1.21</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
         <v>2.6</v>
@@ -2226,7 +2226,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AR9" t="n">
         <v>2.5</v>
@@ -2241,7 +2241,7 @@
         <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AW9" t="n">
         <v>2.5</v>
@@ -2265,7 +2265,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BE9" t="n">
         <v>2.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="H11" t="n">
         <v>3.75</v>
@@ -2515,13 +2515,13 @@
         <v>5.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>4.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
@@ -2542,7 +2542,7 @@
         <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
         <v>1.63</v>
@@ -2554,7 +2554,7 @@
         <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2614,10 +2614,10 @@
         <v>1.74</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AS11" t="n">
         <v>1.74</v>
@@ -2626,16 +2626,16 @@
         <v>1.58</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AV11" t="n">
         <v>1.63</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AY11" t="n">
         <v>1.55</v>
@@ -2644,29 +2644,29 @@
         <v>1.62</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BB11" t="n">
         <v>1.63</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BF11" t="n">
         <v>1.51</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H12" t="n">
         <v>2.28</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H13" t="n">
         <v>2.96</v>
@@ -2912,7 +2912,7 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
         <v>2.54</v>
@@ -2921,7 +2921,7 @@
         <v>1.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q13" t="n">
         <v>2.62</v>
@@ -2942,7 +2942,7 @@
         <v>1.43</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X13" t="n">
         <v>8.800000000000001</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -3097,16 +3097,16 @@
         <v>2.86</v>
       </c>
       <c r="J14" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="N14" t="n">
         <v>2.14</v>
@@ -3124,19 +3124,19 @@
         <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V14" t="n">
         <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -3279,28 +3279,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="G15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
         <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
@@ -3312,7 +3312,7 @@
         <v>2.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
         <v>1.71</v>
@@ -3330,7 +3330,7 @@
         <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="X15" t="n">
         <v>34</v>
@@ -3339,7 +3339,7 @@
         <v>32</v>
       </c>
       <c r="Z15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA15" t="n">
         <v>140</v>
@@ -3378,7 +3378,7 @@
         <v>32</v>
       </c>
       <c r="AM15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN15" t="n">
         <v>7</v>
@@ -3387,22 +3387,22 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ15" t="n">
         <v>4</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT15" t="n">
         <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV15" t="n">
         <v>3.9</v>
@@ -3417,32 +3417,32 @@
         <v>3.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD15" t="n">
         <v>18</v>
       </c>
       <c r="BE15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG15" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
         <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R16" t="n">
         <v>1.66</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
         <v>3.65</v>
@@ -3679,7 +3679,7 @@
         <v>4.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
@@ -3691,7 +3691,7 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O17" t="n">
         <v>1.26</v>
@@ -3715,10 +3715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W17" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
         <v>2.42</v>
       </c>
       <c r="T18" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="U18" t="n">
         <v>1.92</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
         <v>2.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
         <v>3.75</v>
@@ -4082,7 +4082,7 @@
         <v>3.15</v>
       </c>
       <c r="O19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
         <v>1.74</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
         <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U20" t="n">
         <v>1.8</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
@@ -4455,7 +4455,7 @@
         <v>1.63</v>
       </c>
       <c r="J21" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
         <v>950</v>
@@ -4491,7 +4491,7 @@
         <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="W21" t="n">
         <v>1.13</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>4.4</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L22" t="n">
         <v>1.26</v>
@@ -4667,7 +4667,7 @@
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q22" t="n">
         <v>1.5</v>
@@ -4781,7 +4781,7 @@
         <v>24</v>
       </c>
       <c r="BB22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC22" t="n">
         <v>21</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>4.1</v>
       </c>
       <c r="H23" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I23" t="n">
         <v>1.87</v>
@@ -4855,7 +4855,7 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.12</v>
@@ -4879,22 +4879,22 @@
         <v>3.15</v>
       </c>
       <c r="V23" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X23" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Y23" t="n">
         <v>19.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB23" t="n">
         <v>32</v>
@@ -4915,13 +4915,13 @@
         <v>17.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI23" t="n">
         <v>21</v>
       </c>
       <c r="AJ23" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK23" t="n">
         <v>36</v>
@@ -4936,13 +4936,13 @@
         <v>19</v>
       </c>
       <c r="AO23" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AP23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AQ23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR23" t="n">
         <v>16.5</v>
@@ -4951,7 +4951,7 @@
         <v>21</v>
       </c>
       <c r="AT23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU23" t="n">
         <v>11.5</v>
@@ -4963,10 +4963,10 @@
         <v>14.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ23" t="n">
         <v>13.5</v>
@@ -4990,11 +4990,11 @@
         <v>18</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -760,16 +760,16 @@
         <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H2" t="n">
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
@@ -805,10 +805,10 @@
         <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X2" t="n">
         <v>18.5</v>
@@ -847,7 +847,7 @@
         <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK2" t="n">
         <v>46</v>
@@ -886,7 +886,7 @@
         <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX2" t="n">
         <v>17.5</v>
@@ -913,14 +913,14 @@
         <v>4.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BG2" t="n">
         <v>13</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H3" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I3" t="n">
         <v>3.65</v>
@@ -966,7 +966,7 @@
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>1.42</v>
@@ -981,16 +981,16 @@
         <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R3" t="n">
         <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T3" t="n">
         <v>1.65</v>
@@ -999,10 +999,10 @@
         <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
         <v>16</v>
@@ -1011,7 +1011,7 @@
         <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA3" t="n">
         <v>65</v>
@@ -1023,10 +1023,10 @@
         <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
         <v>21</v>
@@ -1041,7 +1041,7 @@
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK3" t="n">
         <v>36</v>
@@ -1056,7 +1056,7 @@
         <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP3" t="n">
         <v>9.6</v>
@@ -1077,7 +1077,7 @@
         <v>5.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
         <v>3.9</v>
@@ -1089,32 +1089,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB3" t="n">
         <v>3.95</v>
       </c>
-      <c r="BB3" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BC3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
         <v>4.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
@@ -1393,7 +1393,7 @@
         <v>1.44</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
         <v>11</v>
@@ -1408,7 +1408,7 @@
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
         <v>13</v>
@@ -1417,7 +1417,7 @@
         <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG5" t="n">
         <v>15.5</v>
@@ -1441,7 +1441,7 @@
         <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
         <v>23</v>
@@ -1456,7 +1456,7 @@
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1480,29 +1480,29 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.9</v>
+        <v>40</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
         <v>34</v>
       </c>
       <c r="BE5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF5" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>6</v>
       </c>
       <c r="BG5" t="n">
         <v>16</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1536,10 +1536,10 @@
         <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
         <v>3.7</v>
@@ -1548,10 +1548,10 @@
         <v>2.76</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
@@ -1584,7 +1584,7 @@
         <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X6" t="n">
         <v>8.199999999999999</v>
@@ -1659,22 +1659,22 @@
         <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
         <v>7.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
         <v>7.6</v>
@@ -1689,14 +1689,14 @@
         <v>8.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I7" t="n">
         <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.45</v>
@@ -1754,10 +1754,10 @@
         <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
         <v>2.12</v>
@@ -1778,13 +1778,13 @@
         <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
         <v>23</v>
@@ -1793,10 +1793,10 @@
         <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
         <v>16</v>
@@ -1811,7 +1811,7 @@
         <v>16</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
         <v>65</v>
@@ -1826,19 +1826,19 @@
         <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO7" t="n">
         <v>44</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR7" t="n">
         <v>13.5</v>
@@ -1847,16 +1847,16 @@
         <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AV7" t="n">
         <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AX7" t="n">
         <v>13.5</v>
@@ -1865,7 +1865,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
         <v>4</v>
@@ -1874,7 +1874,7 @@
         <v>4</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BD7" t="n">
         <v>4</v>
@@ -1883,14 +1883,14 @@
         <v>4.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1921,160 +1921,160 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
         <v>1.01</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="AQ8" t="n">
         <v>1.01</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AR8" t="n">
         <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H9" t="n">
         <v>6.4</v>
@@ -2133,31 +2133,31 @@
         <v>5.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q9" t="n">
         <v>1.49</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="T9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U9" t="n">
         <v>1.87</v>
@@ -2166,7 +2166,7 @@
         <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2193,10 +2193,10 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2217,46 +2217,46 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.2</v>
+        <v>2.58</v>
       </c>
       <c r="AY9" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="BB9" t="n">
         <v>9.199999999999999</v>
@@ -2265,20 +2265,20 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2327,13 +2327,13 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.35</v>
@@ -2423,7 +2423,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>5.2</v>
       </c>
       <c r="AS10" t="n">
         <v>5.4</v>
@@ -2444,13 +2444,13 @@
         <v>13.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>5.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="BB10" t="n">
         <v>5.4</v>
@@ -2459,10 +2459,10 @@
         <v>5.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.4</v>
+        <v>32</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF10" t="n">
         <v>20</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2503,28 +2503,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.92</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
         <v>1.02</v>
@@ -2533,28 +2533,28 @@
         <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2563,37 +2563,37 @@
         <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
         <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE11" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK11" t="n">
         <v>1000</v>
@@ -2602,71 +2602,71 @@
         <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.71</v>
+        <v>1.27</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2700,76 +2700,76 @@
         <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="H12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I12" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="J12" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.35</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U12" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X12" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
         <v>48</v>
       </c>
       <c r="AB12" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
         <v>38</v>
@@ -2778,22 +2778,22 @@
         <v>32</v>
       </c>
       <c r="AG12" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ12" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AK12" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AL12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2802,65 +2802,65 @@
         <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.22</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.52</v>
+        <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.3</v>
+        <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.12</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.28</v>
+        <v>9</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.48</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY12" t="n">
-        <v>2.34</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.4</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.54</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.58</v>
+        <v>4.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.54</v>
+        <v>4.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.56</v>
+        <v>4.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.66</v>
+        <v>5</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.64</v>
+        <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.64</v>
+        <v>17.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>2.98</v>
       </c>
       <c r="H13" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>3.3</v>
@@ -2906,7 +2906,7 @@
         <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2915,10 +2915,10 @@
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P13" t="n">
         <v>1.52</v>
@@ -2948,7 +2948,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Y13" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z13" t="n">
         <v>23</v>
@@ -3008,7 +3008,7 @@
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3020,7 +3020,7 @@
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3032,29 +3032,29 @@
         <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>3.75</v>
       </c>
       <c r="H14" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="I14" t="n">
         <v>2.86</v>
@@ -3100,28 +3100,28 @@
         <v>2.62</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="M14" t="n">
         <v>1.17</v>
       </c>
       <c r="N14" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="P14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q14" t="n">
         <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S14" t="n">
         <v>7.6</v>
@@ -3130,13 +3130,13 @@
         <v>2.42</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V14" t="n">
         <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -3193,43 +3193,43 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AS14" t="n">
         <v>1.27</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU14" t="n">
         <v>4.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.04</v>
+        <v>1.61</v>
       </c>
       <c r="AW14" t="n">
-        <v>8</v>
+        <v>1.72</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.32</v>
+        <v>1.77</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.26</v>
+        <v>1.74</v>
       </c>
       <c r="BC14" t="n">
         <v>1.28</v>
@@ -3241,14 +3241,14 @@
         <v>1.29</v>
       </c>
       <c r="BF14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BG14" t="n">
         <v>1.28</v>
       </c>
-      <c r="BG14" t="n">
-        <v>1.99</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
         <v>6.4</v>
@@ -3297,31 +3297,31 @@
         <v>5.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
         <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U15" t="n">
         <v>2.16</v>
@@ -3330,7 +3330,7 @@
         <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X15" t="n">
         <v>34</v>
@@ -3387,62 +3387,62 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="BA15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC15" t="n">
         <v>4</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BD15" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>18</v>
-      </c>
       <c r="BE15" t="n">
-        <v>4.4</v>
+        <v>42</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G16" t="n">
         <v>4.9</v>
@@ -3482,13 +3482,13 @@
         <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.23</v>
@@ -3506,7 +3506,7 @@
         <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="R16" t="n">
         <v>1.66</v>
@@ -3515,13 +3515,13 @@
         <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="U16" t="n">
         <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
         <v>1.25</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H17" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
         <v>3.55</v>
@@ -3685,16 +3685,16 @@
         <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -3703,10 +3703,10 @@
         <v>1.84</v>
       </c>
       <c r="R17" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3715,10 +3715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3727,7 +3727,7 @@
         <v>22</v>
       </c>
       <c r="Z17" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -3757,7 +3757,7 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK17" t="n">
         <v>30</v>
@@ -3775,16 +3775,16 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AQ17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -3796,7 +3796,7 @@
         <v>9.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AX17" t="n">
         <v>8.4</v>
@@ -3808,29 +3808,29 @@
         <v>10.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
         <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>2.3</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J19" t="n">
         <v>3.25</v>
@@ -4082,7 +4082,7 @@
         <v>3.15</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P19" t="n">
         <v>1.74</v>
@@ -4097,7 +4097,7 @@
         <v>3.85</v>
       </c>
       <c r="T19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U19" t="n">
         <v>1.98</v>
@@ -4163,7 +4163,7 @@
         <v>30</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>7</v>
@@ -4178,7 +4178,7 @@
         <v>8.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV19" t="n">
         <v>8.6</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>3.35</v>
       </c>
       <c r="H20" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I20" t="n">
         <v>2.96</v>
@@ -4267,13 +4267,13 @@
         <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
         <v>1.52</v>
@@ -4282,7 +4282,7 @@
         <v>1.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R20" t="n">
         <v>1.19</v>
@@ -4291,7 +4291,7 @@
         <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>1.8</v>
@@ -4300,7 +4300,7 @@
         <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
         <v>9.199999999999999</v>
@@ -4333,7 +4333,7 @@
         <v>15.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4345,19 +4345,19 @@
         <v>48</v>
       </c>
       <c r="AL20" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
         <v>50</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ20" t="n">
         <v>6.4</v>
@@ -4378,7 +4378,7 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>30</v>
+        <v>7.2</v>
       </c>
       <c r="AX20" t="n">
         <v>16.5</v>
@@ -4396,23 +4396,23 @@
         <v>44</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD20" t="n">
         <v>50</v>
       </c>
       <c r="BE20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG20" t="n">
         <v>34</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="H21" t="n">
         <v>1.5</v>
@@ -4455,158 +4455,158 @@
         <v>1.63</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1.94</v>
+        <v>3.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q21" t="n">
         <v>1.69</v>
       </c>
       <c r="R21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AY21" t="n">
         <v>1.32</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>1.99</v>
+        <v>1.3</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.99</v>
+        <v>2.86</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.99</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.99</v>
+        <v>1.21</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.99</v>
+        <v>1.21</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.99</v>
+        <v>1.21</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.99</v>
+        <v>1.21</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G22" t="n">
         <v>2.54</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.56</v>
       </c>
       <c r="H22" t="n">
         <v>2.58</v>
@@ -4649,7 +4649,7 @@
         <v>2.6</v>
       </c>
       <c r="J22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K22" t="n">
         <v>4.6</v>
@@ -4691,7 +4691,7 @@
         <v>1.64</v>
       </c>
       <c r="X22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y22" t="n">
         <v>18.5</v>
@@ -4700,10 +4700,10 @@
         <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC22" t="n">
         <v>11</v>
@@ -4733,10 +4733,10 @@
         <v>23</v>
       </c>
       <c r="AL22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN22" t="n">
         <v>12</v>
@@ -4757,7 +4757,7 @@
         <v>32</v>
       </c>
       <c r="AT22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU22" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
         <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY22" t="n">
         <v>11.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>1.85</v>
       </c>
       <c r="I23" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="J23" t="n">
         <v>4.6</v>
@@ -4891,7 +4891,7 @@
         <v>19.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA23" t="n">
         <v>24</v>
@@ -4936,13 +4936,13 @@
         <v>19</v>
       </c>
       <c r="AO23" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AP23" t="n">
         <v>36</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR23" t="n">
         <v>16.5</v>
@@ -4990,11 +4990,11 @@
         <v>18</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -760,13 +760,13 @@
         <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="H2" t="n">
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="J2" t="n">
         <v>3.45</v>
@@ -805,7 +805,7 @@
         <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="W2" t="n">
         <v>1.39</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G3" t="n">
         <v>2.82</v>
       </c>
       <c r="H3" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I3" t="n">
         <v>3.65</v>
@@ -966,10 +966,10 @@
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -981,10 +981,10 @@
         <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
         <v>1.31</v>
@@ -999,7 +999,7 @@
         <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
         <v>1.55</v>
@@ -1011,7 +1011,7 @@
         <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA3" t="n">
         <v>65</v>
@@ -1026,7 +1026,7 @@
         <v>16.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
         <v>21</v>
@@ -1041,7 +1041,7 @@
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK3" t="n">
         <v>36</v>
@@ -1056,7 +1056,7 @@
         <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP3" t="n">
         <v>9.6</v>
@@ -1077,7 +1077,7 @@
         <v>5.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
         <v>3.9</v>
@@ -1089,32 +1089,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BB3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD3" t="n">
         <v>3.95</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4</v>
       </c>
       <c r="BE3" t="n">
         <v>4.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
         <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
         <v>15.5</v>
@@ -1486,7 +1486,7 @@
         <v>40</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD5" t="n">
         <v>34</v>
@@ -1495,14 +1495,14 @@
         <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
         <v>16</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1539,25 +1539,25 @@
         <v>2.82</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="O6" t="n">
         <v>1.6</v>
@@ -1581,13 +1581,13 @@
         <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
         <v>1.54</v>
       </c>
       <c r="X6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y6" t="n">
         <v>9.4</v>
@@ -1596,13 +1596,13 @@
         <v>23</v>
       </c>
       <c r="AA6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD6" t="n">
         <v>16.5</v>
@@ -1635,13 +1635,13 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
         <v>7.6</v>
@@ -1650,7 +1650,7 @@
         <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1662,7 +1662,7 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX6" t="n">
         <v>13.5</v>
@@ -1674,29 +1674,29 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB6" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB6" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BC6" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF6" t="n">
         <v>8.6</v>
       </c>
-      <c r="BF6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BG6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I7" t="n">
         <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
@@ -1760,16 +1760,16 @@
         <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
@@ -1778,13 +1778,13 @@
         <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
         <v>23</v>
@@ -1796,7 +1796,7 @@
         <v>12.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
         <v>16</v>
@@ -1826,7 +1826,7 @@
         <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
         <v>42</v>
@@ -1835,10 +1835,10 @@
         <v>44</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
         <v>13.5</v>
@@ -1850,7 +1850,7 @@
         <v>7.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AV7" t="n">
         <v>9.6</v>
@@ -1883,14 +1883,14 @@
         <v>4.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BG7" t="n">
         <v>3.9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="J8" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.3</v>
@@ -1963,128 +1963,128 @@
         <v>2.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U8" t="n">
         <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
         <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
         <v>5.7</v>
@@ -2145,22 +2145,22 @@
         <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="R9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T9" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="U9" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2193,22 +2193,22 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2217,68 +2217,68 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.1</v>
+        <v>21</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.58</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
         <v>3.3</v>
@@ -2327,13 +2327,13 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
         <v>1.35</v>
@@ -2450,7 +2450,7 @@
         <v>5.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>34</v>
+        <v>5.4</v>
       </c>
       <c r="BB10" t="n">
         <v>5.4</v>
@@ -2459,10 +2459,10 @@
         <v>5.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>32</v>
+        <v>5.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF10" t="n">
         <v>20</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.97</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M11" t="n">
         <v>1.03</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
       </c>
       <c r="N11" t="n">
         <v>1.02</v>
       </c>
       <c r="O11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>2.12</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO11" t="n">
         <v>50</v>
       </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP11" t="n">
-        <v>1.39</v>
+        <v>4.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.39</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.56</v>
+        <v>4.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.39</v>
+        <v>4.9</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.29</v>
+        <v>3.75</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.39</v>
+        <v>3.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.32</v>
+        <v>4.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.39</v>
+        <v>4.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.39</v>
+        <v>3.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.27</v>
+        <v>3.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.31</v>
+        <v>4</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.39</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.32</v>
+        <v>4.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.39</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.39</v>
+        <v>4.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.61</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.27</v>
+        <v>3.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="H12" t="n">
         <v>2.3</v>
@@ -2721,7 +2721,7 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
         <v>1.35</v>
@@ -2733,13 +2733,13 @@
         <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
         <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
         <v>2.04</v>
@@ -2748,7 +2748,7 @@
         <v>1.63</v>
       </c>
       <c r="W12" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
         <v>15</v>
@@ -2760,7 +2760,7 @@
         <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AB12" t="n">
         <v>14</v>
@@ -2772,10 +2772,10 @@
         <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AG12" t="n">
         <v>16.5</v>
@@ -2784,7 +2784,7 @@
         <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
         <v>70</v>
@@ -2808,13 +2808,13 @@
         <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AR12" t="n">
         <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
         <v>9.4</v>
@@ -2838,29 +2838,29 @@
         <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC12" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC12" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE12" t="n">
         <v>5</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>17.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>3.3</v>
       </c>
       <c r="J13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
         <v>3.15</v>
@@ -2915,13 +2915,13 @@
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O13" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q13" t="n">
         <v>2.62</v>
@@ -2966,10 +2966,10 @@
         <v>17</v>
       </c>
       <c r="AE13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
         <v>15.5</v>
@@ -2984,7 +2984,7 @@
         <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL13" t="n">
         <v>80</v>
@@ -2996,7 +2996,7 @@
         <v>60</v>
       </c>
       <c r="AO13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP13" t="n">
         <v>7.4</v>
@@ -3008,7 +3008,7 @@
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3020,7 +3020,7 @@
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3032,29 +3032,29 @@
         <v>19</v>
       </c>
       <c r="BA13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC13" t="n">
         <v>6</v>
       </c>
-      <c r="BB13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BD13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF13" t="n">
         <v>6.2</v>
       </c>
-      <c r="BF13" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -3085,46 +3085,46 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="H14" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I14" t="n">
         <v>2.86</v>
       </c>
       <c r="J14" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="L14" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
         <v>1.17</v>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="P14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
         <v>1.13</v>
       </c>
       <c r="S14" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="T14" t="n">
         <v>2.42</v>
@@ -3136,10 +3136,10 @@
         <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AQ14" t="n">
         <v>4</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU14" t="n">
         <v>4.1</v>
       </c>
       <c r="AV14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.61</v>
       </c>
-      <c r="AW14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BF14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BG14" t="n">
         <v>1.58</v>
       </c>
-      <c r="BG14" t="n">
-        <v>1.28</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -3279,46 +3279,46 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="G15" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
         <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="R15" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="S15" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
         <v>1.51</v>
@@ -3327,10 +3327,10 @@
         <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X15" t="n">
         <v>34</v>
@@ -3345,7 +3345,7 @@
         <v>140</v>
       </c>
       <c r="AB15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC15" t="n">
         <v>13.5</v>
@@ -3357,10 +3357,10 @@
         <v>70</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
         <v>21</v>
@@ -3372,7 +3372,7 @@
         <v>21</v>
       </c>
       <c r="AK15" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AL15" t="n">
         <v>32</v>
@@ -3381,68 +3381,68 @@
         <v>75</v>
       </c>
       <c r="AN15" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT15" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AU15" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AY15" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>42</v>
+        <v>6.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -3482,10 +3482,10 @@
         <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
         <v>5.8</v>
@@ -3497,31 +3497,31 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
         <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="T16" t="n">
         <v>1.52</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="W16" t="n">
         <v>1.25</v>
@@ -3578,7 +3578,7 @@
         <v>32</v>
       </c>
       <c r="AO16" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AP16" t="n">
         <v>4.4</v>
@@ -3599,7 +3599,7 @@
         <v>3.65</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="AW16" t="n">
         <v>4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H17" t="n">
         <v>3.55</v>
@@ -3679,158 +3679,158 @@
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V17" t="n">
         <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AC17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ17" t="n">
+      <c r="BA17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF17" t="n">
         <v>10.5</v>
       </c>
-      <c r="BA17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.93</v>
-      </c>
       <c r="BG17" t="n">
-        <v>1.93</v>
+        <v>4.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>2.16</v>
       </c>
       <c r="G18" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>3.55</v>
@@ -3882,149 +3882,149 @@
         <v>1.28</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
         <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y18" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
         <v>24</v>
       </c>
-      <c r="AG18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>34</v>
-      </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.9</v>
+        <v>13.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU18" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU18" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AV18" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BD18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG18" t="n">
         <v>19</v>
       </c>
-      <c r="BE18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="I19" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>3.25</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.44</v>
@@ -4082,10 +4082,10 @@
         <v>3.15</v>
       </c>
       <c r="O19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
         <v>2.06</v>
@@ -4094,10 +4094,10 @@
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U19" t="n">
         <v>1.98</v>
@@ -4106,13 +4106,13 @@
         <v>1.62</v>
       </c>
       <c r="W19" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
         <v>18.5</v>
@@ -4142,7 +4142,7 @@
         <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ19" t="n">
         <v>75</v>
@@ -4151,7 +4151,7 @@
         <v>44</v>
       </c>
       <c r="AL19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
         <v>140</v>
@@ -4172,13 +4172,13 @@
         <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
         <v>8.6</v>
@@ -4196,29 +4196,29 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC19" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC19" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF19" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4.9</v>
       </c>
       <c r="BG19" t="n">
         <v>17.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -4267,16 +4267,16 @@
         <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P20" t="n">
         <v>1.54</v>
@@ -4291,7 +4291,7 @@
         <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
         <v>1.8</v>
@@ -4300,7 +4300,7 @@
         <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
         <v>9.199999999999999</v>
@@ -4333,7 +4333,7 @@
         <v>15.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4345,7 +4345,7 @@
         <v>48</v>
       </c>
       <c r="AL20" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -4402,17 +4402,17 @@
         <v>50</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="BG20" t="n">
         <v>34</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -4455,13 +4455,13 @@
         <v>1.63</v>
       </c>
       <c r="J21" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K21" t="n">
         <v>5.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -4485,16 +4485,16 @@
         <v>2.76</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V21" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4557,7 +4557,7 @@
         <v>2.3</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AS21" t="n">
         <v>1.37</v>
@@ -4569,7 +4569,7 @@
         <v>1.37</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AW21" t="n">
         <v>1.37</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>2.52</v>
       </c>
       <c r="G22" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H22" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J22" t="n">
         <v>4.5</v>
@@ -4685,13 +4685,13 @@
         <v>2.9</v>
       </c>
       <c r="V22" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W22" t="n">
         <v>1.64</v>
       </c>
       <c r="X22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y22" t="n">
         <v>18.5</v>
@@ -4706,7 +4706,7 @@
         <v>18</v>
       </c>
       <c r="AC22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD22" t="n">
         <v>12.5</v>
@@ -4730,10 +4730,10 @@
         <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM22" t="n">
         <v>48</v>
@@ -4745,7 +4745,7 @@
         <v>12</v>
       </c>
       <c r="AP22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ22" t="n">
         <v>17.5</v>
@@ -4757,7 +4757,7 @@
         <v>32</v>
       </c>
       <c r="AT22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU22" t="n">
         <v>10</v>
@@ -4781,7 +4781,7 @@
         <v>24</v>
       </c>
       <c r="BB22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC22" t="n">
         <v>21</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G23" t="n">
         <v>4</v>
-      </c>
-      <c r="G23" t="n">
-        <v>4.1</v>
       </c>
       <c r="H23" t="n">
         <v>1.85</v>
       </c>
       <c r="I23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="J23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.22</v>
@@ -4855,7 +4855,7 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.12</v>
@@ -4867,10 +4867,10 @@
         <v>1.38</v>
       </c>
       <c r="R23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S23" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="T23" t="n">
         <v>1.42</v>
@@ -4879,19 +4879,19 @@
         <v>3.15</v>
       </c>
       <c r="V23" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="W23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
         <v>42</v>
       </c>
       <c r="Y23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA23" t="n">
         <v>24</v>
@@ -4936,7 +4936,7 @@
         <v>19</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AP23" t="n">
         <v>36</v>
@@ -4963,7 +4963,7 @@
         <v>14.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AY23" t="n">
         <v>16.5</v>
@@ -4984,17 +4984,17 @@
         <v>30</v>
       </c>
       <c r="BE23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -760,13 +760,13 @@
         <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="H2" t="n">
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.45</v>
@@ -775,7 +775,7 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -805,7 +805,7 @@
         <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W2" t="n">
         <v>1.39</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -951,28 +951,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G3" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I3" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
         <v>3.35</v>
@@ -990,22 +990,22 @@
         <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
         <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
         <v>14</v>
@@ -1020,7 +1020,7 @@
         <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>16.5</v>
@@ -1029,13 +1029,13 @@
         <v>46</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
         <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
@@ -1062,13 +1062,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT3" t="n">
         <v>7.6</v>
@@ -1080,41 +1080,41 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC3" t="n">
         <v>3.95</v>
       </c>
-      <c r="BB3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BD3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.75</v>
+        <v>18</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>2.58</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
         <v>3.75</v>
@@ -1432,7 +1432,7 @@
         <v>65</v>
       </c>
       <c r="AK5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
@@ -1486,7 +1486,7 @@
         <v>40</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
         <v>34</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="L6" t="n">
         <v>1.6</v>
@@ -1578,7 +1578,7 @@
         <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
         <v>1.38</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
         <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
@@ -1760,25 +1760,25 @@
         <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="X7" t="n">
         <v>13.5</v>
@@ -1826,7 +1826,7 @@
         <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN7" t="n">
         <v>42</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -1924,142 +1924,142 @@
         <v>2.58</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.5</v>
       </c>
-      <c r="I8" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.78</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
         <v>44</v>
       </c>
       <c r="AB8" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
         <v>14.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV8" t="n">
         <v>9.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA8" t="n">
         <v>4.5</v>
@@ -2068,23 +2068,23 @@
         <v>4.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD8" t="n">
         <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I9" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K9" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="T9" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2193,92 +2193,92 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>17</v>
       </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BA9" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BC9" t="n">
         <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H10" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I10" t="n">
         <v>3.05</v>
@@ -2324,7 +2324,7 @@
         <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.44</v>
@@ -2333,37 +2333,37 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.35</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.32</v>
-      </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
         <v>13</v>
@@ -2384,7 +2384,7 @@
         <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF10" t="n">
         <v>20</v>
@@ -2417,62 +2417,62 @@
         <v>32</v>
       </c>
       <c r="AP10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>10</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AR10" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU10" t="n">
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BC10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE10" t="n">
         <v>5.8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.5</v>
       </c>
       <c r="BF10" t="n">
         <v>20</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="H11" t="n">
         <v>3.9</v>
@@ -2515,7 +2515,7 @@
         <v>5.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
         <v>4.8</v>
@@ -2614,10 +2614,10 @@
         <v>4.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS11" t="n">
         <v>4.9</v>
@@ -2659,14 +2659,14 @@
         <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BG11" t="n">
         <v>4.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -2745,7 +2745,7 @@
         <v>2.04</v>
       </c>
       <c r="V12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W12" t="n">
         <v>1.37</v>
@@ -2805,46 +2805,46 @@
         <v>27</v>
       </c>
       <c r="AP12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT12" t="n">
         <v>10</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
         <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>4.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13.5</v>
+        <v>5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB12" t="n">
         <v>4.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD12" t="n">
         <v>4.9</v>
@@ -2853,14 +2853,14 @@
         <v>5</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
         <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V13" t="n">
         <v>1.43</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H14" t="n">
         <v>2.68</v>
       </c>
       <c r="I14" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="K14" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="L14" t="n">
         <v>1.62</v>
@@ -3112,7 +3112,7 @@
         <v>2.16</v>
       </c>
       <c r="O14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="P14" t="n">
         <v>1.38</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AS14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>1.57</v>
       </c>
-      <c r="AT14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV14" t="n">
+      <c r="BA14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BC14" t="n">
         <v>1.62</v>
       </c>
-      <c r="AW14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.58</v>
-      </c>
       <c r="BD14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.58</v>
+        <v>2.62</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H15" t="n">
         <v>4.9</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
         <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L15" t="n">
         <v>1.21</v>
@@ -3324,13 +3324,13 @@
         <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X15" t="n">
         <v>34</v>
@@ -3348,7 +3348,7 @@
         <v>16</v>
       </c>
       <c r="AC15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD15" t="n">
         <v>25</v>
@@ -3360,10 +3360,10 @@
         <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
         <v>60</v>
@@ -3375,7 +3375,7 @@
         <v>970</v>
       </c>
       <c r="AL15" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AM15" t="n">
         <v>75</v>
@@ -3384,65 +3384,65 @@
         <v>6.2</v>
       </c>
       <c r="AO15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.5</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB15" t="n">
         <v>6</v>
       </c>
-      <c r="BB15" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BC15" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.6</v>
+        <v>46</v>
       </c>
       <c r="BF15" t="n">
         <v>5.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>3.75</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="H16" t="n">
         <v>1.78</v>
@@ -3485,7 +3485,7 @@
         <v>1.96</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
         <v>5.8</v>
@@ -3497,7 +3497,7 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.16</v>
@@ -3524,7 +3524,7 @@
         <v>2.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
         <v>34</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J17" t="n">
         <v>3.75</v>
@@ -3694,7 +3694,7 @@
         <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
         <v>2.22</v>
@@ -3706,7 +3706,7 @@
         <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="T17" t="n">
         <v>1.64</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -4020,11 +4020,11 @@
         <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -4055,100 +4055,100 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G19" t="n">
         <v>3.05</v>
       </c>
-      <c r="G19" t="n">
-        <v>3.25</v>
-      </c>
       <c r="H19" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
         <v>3.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P19" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="W19" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X19" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z19" t="n">
         <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AB19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG19" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
         <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ19" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AK19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL19" t="n">
         <v>55</v>
@@ -4157,37 +4157,37 @@
         <v>140</v>
       </c>
       <c r="AN19" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AO19" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AP19" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="AW19" t="n">
         <v>20</v>
       </c>
       <c r="AX19" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
@@ -4196,29 +4196,29 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF19" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>5.2</v>
       </c>
       <c r="BG19" t="n">
         <v>17.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="G20" t="n">
         <v>3.35</v>
@@ -4261,13 +4261,13 @@
         <v>2.96</v>
       </c>
       <c r="J20" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K20" t="n">
         <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -4452,10 +4452,10 @@
         <v>1.5</v>
       </c>
       <c r="I21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K21" t="n">
         <v>5.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G22" t="n">
         <v>2.52</v>
       </c>
-      <c r="G22" t="n">
-        <v>2.56</v>
-      </c>
       <c r="H22" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I22" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="J22" t="n">
         <v>4.5</v>
@@ -4679,25 +4679,25 @@
         <v>2.26</v>
       </c>
       <c r="T22" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U22" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V22" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X22" t="n">
         <v>32</v>
       </c>
       <c r="Y22" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
         <v>38</v>
@@ -4706,13 +4706,13 @@
         <v>18</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF22" t="n">
         <v>22</v>
@@ -4724,10 +4724,10 @@
         <v>14.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
         <v>22</v>
@@ -4739,10 +4739,10 @@
         <v>48</v>
       </c>
       <c r="AN22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP22" t="n">
         <v>28</v>
@@ -4751,7 +4751,7 @@
         <v>17.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS22" t="n">
         <v>32</v>
@@ -4769,7 +4769,7 @@
         <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY22" t="n">
         <v>11.5</v>
@@ -4784,7 +4784,7 @@
         <v>32</v>
       </c>
       <c r="BC22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD22" t="n">
         <v>24</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G23" t="n">
         <v>3.95</v>
       </c>
-      <c r="G23" t="n">
-        <v>4</v>
-      </c>
       <c r="H23" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="I23" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="J23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K23" t="n">
         <v>4.7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.22</v>
@@ -4870,22 +4870,22 @@
         <v>2.04</v>
       </c>
       <c r="S23" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="T23" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U23" t="n">
         <v>3.15</v>
       </c>
       <c r="V23" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W23" t="n">
         <v>1.33</v>
       </c>
       <c r="X23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y23" t="n">
         <v>20</v>
@@ -4900,22 +4900,22 @@
         <v>32</v>
       </c>
       <c r="AC23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD23" t="n">
         <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF23" t="n">
         <v>42</v>
       </c>
       <c r="AG23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI23" t="n">
         <v>21</v>
@@ -4927,13 +4927,13 @@
         <v>36</v>
       </c>
       <c r="AL23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM23" t="n">
         <v>42</v>
       </c>
       <c r="AN23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO23" t="n">
         <v>5.9</v>
@@ -4966,10 +4966,10 @@
         <v>36</v>
       </c>
       <c r="AY23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
         <v>19</v>
@@ -4987,14 +4987,14 @@
         <v>38</v>
       </c>
       <c r="BF23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -766,7 +766,7 @@
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="J2" t="n">
         <v>3.45</v>
@@ -805,7 +805,7 @@
         <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="W2" t="n">
         <v>1.39</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H3" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
@@ -981,7 +981,7 @@
         <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
@@ -999,10 +999,10 @@
         <v>1.91</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
@@ -1020,7 +1020,7 @@
         <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>16.5</v>
@@ -1044,7 +1044,7 @@
         <v>46</v>
       </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1065,13 +1065,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
         <v>5.8</v>
@@ -1080,10 +1080,10 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="AY3" t="n">
         <v>9</v>
@@ -1092,29 +1092,29 @@
         <v>12.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF3" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>18</v>
-      </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
         <v>1.25</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -1369,10 +1369,10 @@
         <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
         <v>1.35</v>
@@ -1495,14 +1495,14 @@
         <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG5" t="n">
         <v>16</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
         <v>2.78</v>
@@ -1554,19 +1554,19 @@
         <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
         <v>1.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="R6" t="n">
         <v>1.16</v>
@@ -1575,13 +1575,13 @@
         <v>5.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
         <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
         <v>1.54</v>
@@ -1641,7 +1641,7 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>7.6</v>
@@ -1674,29 +1674,29 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF6" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>8.6</v>
       </c>
       <c r="BG6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -1736,10 +1736,10 @@
         <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
@@ -1754,10 +1754,10 @@
         <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
         <v>2.12</v>
@@ -1775,10 +1775,10 @@
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
         <v>13.5</v>
@@ -1787,7 +1787,7 @@
         <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
         <v>60</v>
@@ -1826,10 +1826,10 @@
         <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO7" t="n">
         <v>44</v>
@@ -1841,10 +1841,10 @@
         <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AT7" t="n">
         <v>7.6</v>
@@ -1853,7 +1853,7 @@
         <v>5.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
         <v>3.9</v>
@@ -1865,13 +1865,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
         <v>4</v>
       </c>
       <c r="BB7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BC7" t="n">
         <v>3.9</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -1921,73 +1921,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
         <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
         <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W8" t="n">
         <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB8" t="n">
         <v>18</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>18.5</v>
       </c>
       <c r="AC8" t="n">
         <v>11</v>
@@ -2011,80 +2011,80 @@
         <v>36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AO8" t="n">
         <v>17.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT8" t="n">
         <v>12</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
         <v>9.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
         <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB8" t="n">
         <v>4.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG8" t="n">
         <v>11.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
         <v>18</v>
@@ -2217,7 +2217,7 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
@@ -2226,25 +2226,25 @@
         <v>17.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
         <v>9.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
         <v>8.6</v>
@@ -2256,7 +2256,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
         <v>10.5</v>
@@ -2268,17 +2268,17 @@
         <v>22</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
         <v>5.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -2378,10 +2378,10 @@
         <v>12.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
         <v>34</v>
@@ -2423,10 +2423,10 @@
         <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
         <v>9.6</v>
@@ -2438,7 +2438,7 @@
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX10" t="n">
         <v>15.5</v>
@@ -2447,32 +2447,32 @@
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE10" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.8</v>
       </c>
       <c r="BF10" t="n">
         <v>20</v>
       </c>
       <c r="BG10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H11" t="n">
         <v>3.9</v>
@@ -2515,7 +2515,7 @@
         <v>5.2</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
         <v>4.8</v>
@@ -2557,116 +2557,116 @@
         <v>2.14</v>
       </c>
       <c r="X11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA11" t="n">
         <v>120</v>
       </c>
       <c r="AB11" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>20</v>
       </c>
-      <c r="AI11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>22</v>
-      </c>
       <c r="AK11" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM11" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF11" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G12" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="I12" t="n">
         <v>2.58</v>
@@ -2712,7 +2712,7 @@
         <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.42</v>
@@ -2742,55 +2742,55 @@
         <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
         <v>1.65</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
         <v>15</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
         <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH12" t="n">
         <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL12" t="n">
         <v>60</v>
@@ -2802,65 +2802,65 @@
         <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>4.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -3106,31 +3106,31 @@
         <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N14" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="P14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Q14" t="n">
         <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="U14" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="V14" t="n">
         <v>1.53</v>
@@ -3139,7 +3139,7 @@
         <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
@@ -3148,7 +3148,7 @@
         <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AB14" t="n">
         <v>970</v>
@@ -3196,59 +3196,59 @@
         <v>4.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.02</v>
+        <v>4.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.63</v>
+        <v>2.32</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="AX14" t="n">
         <v>1.69</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.99</v>
+        <v>2.66</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="BD14" t="n">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H15" t="n">
         <v>4.9</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.21</v>
@@ -3309,13 +3309,13 @@
         <v>1.16</v>
       </c>
       <c r="P15" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q15" t="n">
         <v>1.48</v>
       </c>
       <c r="R15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S15" t="n">
         <v>2.2</v>
@@ -3324,13 +3324,13 @@
         <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V15" t="n">
         <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X15" t="n">
         <v>34</v>
@@ -3348,10 +3348,10 @@
         <v>16</v>
       </c>
       <c r="AC15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE15" t="n">
         <v>70</v>
@@ -3363,7 +3363,7 @@
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI15" t="n">
         <v>60</v>
@@ -3387,49 +3387,49 @@
         <v>50</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU15" t="n">
         <v>5.1</v>
       </c>
-      <c r="AU15" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AV15" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AY15" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB15" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB15" t="n">
-        <v>6</v>
-      </c>
       <c r="BC15" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE15" t="n">
         <v>46</v>
@@ -3438,11 +3438,11 @@
         <v>5.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -3482,10 +3482,10 @@
         <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
         <v>5.8</v>
@@ -3506,19 +3506,19 @@
         <v>2.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="R16" t="n">
         <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="T16" t="n">
         <v>1.52</v>
       </c>
       <c r="U16" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V16" t="n">
         <v>2.04</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
         <v>1.64</v>
       </c>
       <c r="U17" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V17" t="n">
         <v>1.33</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="I19" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
         <v>3.7</v>
@@ -4079,7 +4079,7 @@
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>1.36</v>
@@ -4103,13 +4103,13 @@
         <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y19" t="n">
         <v>11.5</v>
@@ -4121,7 +4121,7 @@
         <v>50</v>
       </c>
       <c r="AB19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC19" t="n">
         <v>9.199999999999999</v>
@@ -4133,7 +4133,7 @@
         <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
         <v>13</v>
@@ -4145,10 +4145,10 @@
         <v>50</v>
       </c>
       <c r="AJ19" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL19" t="n">
         <v>55</v>
@@ -4157,31 +4157,31 @@
         <v>140</v>
       </c>
       <c r="AN19" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO19" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP19" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AR19" t="n">
         <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW19" t="n">
         <v>20</v>
@@ -4196,29 +4196,29 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE19" t="n">
         <v>5.7</v>
       </c>
-      <c r="BB19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BF19" t="n">
-        <v>5.4</v>
+        <v>23</v>
       </c>
       <c r="BG19" t="n">
         <v>17.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>2.94</v>
       </c>
       <c r="G20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
         <v>2.7</v>
       </c>
       <c r="I20" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J20" t="n">
         <v>2.9</v>
@@ -4267,7 +4267,7 @@
         <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
@@ -4285,7 +4285,7 @@
         <v>2.54</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
         <v>5.1</v>
@@ -4333,7 +4333,7 @@
         <v>15.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4345,7 +4345,7 @@
         <v>48</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -4378,7 +4378,7 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX20" t="n">
         <v>16.5</v>
@@ -4396,13 +4396,13 @@
         <v>44</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD20" t="n">
         <v>50</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
         <v>44</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G22" t="n">
         <v>2.52</v>
       </c>
       <c r="H22" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I22" t="n">
         <v>2.66</v>
@@ -4688,7 +4688,7 @@
         <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X22" t="n">
         <v>32</v>
@@ -4697,7 +4697,7 @@
         <v>19</v>
       </c>
       <c r="Z22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
         <v>38</v>
@@ -4706,7 +4706,7 @@
         <v>18</v>
       </c>
       <c r="AC22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD22" t="n">
         <v>13</v>
@@ -4721,7 +4721,7 @@
         <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>26</v>
@@ -4748,7 +4748,7 @@
         <v>28</v>
       </c>
       <c r="AQ22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR22" t="n">
         <v>20</v>
@@ -4760,7 +4760,7 @@
         <v>17</v>
       </c>
       <c r="AU22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV22" t="n">
         <v>12</v>
@@ -4775,7 +4775,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
         <v>24</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>3.9</v>
       </c>
       <c r="G23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I23" t="n">
         <v>1.88</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.89</v>
       </c>
       <c r="J23" t="n">
         <v>4.6</v>
@@ -4849,34 +4849,34 @@
         <v>4.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R23" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S23" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="T23" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U23" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="V23" t="n">
         <v>2.12</v>
@@ -4891,13 +4891,13 @@
         <v>20</v>
       </c>
       <c r="Z23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA23" t="n">
         <v>24</v>
       </c>
       <c r="AB23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC23" t="n">
         <v>13</v>
@@ -4906,22 +4906,22 @@
         <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AF23" t="n">
         <v>42</v>
       </c>
       <c r="AG23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH23" t="n">
         <v>15</v>
       </c>
       <c r="AI23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="n">
         <v>36</v>
@@ -4930,28 +4930,28 @@
         <v>32</v>
       </c>
       <c r="AM23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN23" t="n">
         <v>18</v>
       </c>
       <c r="AO23" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AP23" t="n">
         <v>36</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AU23" t="n">
         <v>11.5</v>
@@ -4963,7 +4963,7 @@
         <v>14.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY23" t="n">
         <v>16</v>
@@ -4975,26 +4975,26 @@
         <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BC23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF23" t="n">
         <v>17</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aris FC Limassol</t>
+          <t>Al-Jndal</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Al-Ula FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="G2" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>2.24</v>
+        <v>1.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.44</v>
+        <v>1.41</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.69</v>
+        <v>3.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
@@ -942,186 +942,186 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris FC Limassol</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Apollon Limassol</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="H3" t="n">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>3.35</v>
+        <v>2.46</v>
       </c>
       <c r="J3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T3" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="U3" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="W3" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="X3" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
         <v>14</v>
       </c>
-      <c r="Z3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AE3" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH3" t="n">
         <v>21</v>
       </c>
       <c r="AI3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL3" t="n">
         <v>60</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>55</v>
-      </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AO3" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD3" t="n">
         <v>4</v>
       </c>
-      <c r="AS3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX3" t="n">
+      <c r="BE3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF3" t="n">
         <v>3.9</v>
       </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG3" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,186 +1136,186 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Hunedoara</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Apollon Limassol</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.26</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>1.26</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>FC Hunedoara</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1.89</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>1.26</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="I6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.7</v>
       </c>
-      <c r="J6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.96</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.47</v>
+        <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.84</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF6" t="n">
         <v>5.9</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X6" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG6" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omonia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="H7" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>2.76</v>
       </c>
       <c r="R7" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE7" t="n">
         <v>60</v>
       </c>
-      <c r="AB7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>44</v>
-      </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AK7" t="n">
         <v>44</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
         <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE7" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF7" t="n">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NK Maribor</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="I8" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.27</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.54</v>
-      </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="U8" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
         <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AF8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH8" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="AO8" t="n">
-        <v>17.5</v>
+        <v>44</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY8" t="n">
         <v>9.6</v>
       </c>
-      <c r="AW8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>3.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>13</v>
+        <v>3.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>11.5</v>
+        <v>3.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Puskas Akademia</t>
+          <t>NK Maribor</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.46</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6</v>
+        <v>2.44</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>2.76</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R9" t="n">
         <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="V9" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>2.74</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
+      <c r="AW9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX9" t="n">
         <v>18</v>
       </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AY9" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:20:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al-Wahda (KSA)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.08</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.35</v>
-      </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Puskas Akademia</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="G11" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
         <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="U11" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2.14</v>
+        <v>2.68</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
         <v>12.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>20</v>
       </c>
-      <c r="AE11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN11" t="n">
+      <c r="AR11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY11" t="n">
         <v>8.6</v>
       </c>
-      <c r="AO11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP11" t="n">
+      <c r="AZ11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD11" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU11" t="n">
+      <c r="BE11" t="n">
         <v>4.9</v>
       </c>
-      <c r="AV11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY11" t="n">
+      <c r="BF11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.9</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.98</v>
+        <v>1.72</v>
       </c>
       <c r="G12" t="n">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="H12" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
-        <v>2.58</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="S12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF12" t="n">
         <v>3.6</v>
       </c>
-      <c r="T12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X12" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G13" t="n">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="H13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>3.3</v>
       </c>
-      <c r="J13" t="n">
-        <v>2.92</v>
-      </c>
       <c r="K13" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>2.58</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="P13" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.06</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>5.3</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="U13" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="V13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI13" t="n">
         <v>55</v>
       </c>
-      <c r="AF13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>85</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AK13" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AL13" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AO13" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="AS13" t="n">
         <v>6.2</v>
       </c>
       <c r="AT13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19</v>
       </c>
       <c r="BA13" t="n">
         <v>6.4</v>
       </c>
       <c r="BB13" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD13" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BE13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG13" t="n">
         <v>6</v>
       </c>
-      <c r="BD13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,114 +3071,114 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="G14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.6</v>
       </c>
-      <c r="H14" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S14" t="n">
-        <v>6.8</v>
-      </c>
       <c r="T14" t="n">
-        <v>2.48</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>1.58</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ14" t="n">
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3190,72 +3190,72 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="AT14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA14" t="n">
         <v>4.9</v>
       </c>
-      <c r="AU14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BB14" t="n">
-        <v>2.66</v>
+        <v>4.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.79</v>
+        <v>4.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.68</v>
+        <v>5.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.82</v>
+        <v>4.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.81</v>
+        <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.66</v>
+        <v>18.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.64</v>
+        <v>2.72</v>
       </c>
       <c r="G15" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>2.98</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="P15" t="n">
-        <v>2.72</v>
+        <v>1.53</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>55</v>
       </c>
-      <c r="AA15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE15" t="n">
+      <c r="AK15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL15" t="n">
         <v>70</v>
       </c>
-      <c r="AF15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>27</v>
-      </c>
       <c r="AM15" t="n">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AN15" t="n">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="AO15" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="AS15" t="n">
         <v>8.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AW15" t="n">
         <v>8</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.9</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC15" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BD15" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,75 +3459,75 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78</v>
+        <v>2.68</v>
       </c>
       <c r="I16" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>2.72</v>
       </c>
       <c r="K16" t="n">
-        <v>5.8</v>
+        <v>2.98</v>
       </c>
       <c r="L16" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O16" t="n">
-        <v>1.16</v>
+        <v>1.76</v>
       </c>
       <c r="P16" t="n">
-        <v>2.66</v>
+        <v>1.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.47</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>1.12</v>
       </c>
       <c r="S16" t="n">
-        <v>2.18</v>
+        <v>7.6</v>
       </c>
       <c r="T16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.52</v>
       </c>
-      <c r="U16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2.04</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="X16" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -3536,114 +3536,114 @@
         <v>970</v>
       </c>
       <c r="AA16" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="AB16" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
         <v>970</v>
       </c>
       <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG16" t="n">
         <v>970</v>
       </c>
-      <c r="AE16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>21</v>
-      </c>
       <c r="AH16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AR16" t="n">
-        <v>3.9</v>
+        <v>2.36</v>
       </c>
       <c r="AS16" t="n">
         <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.5</v>
+        <v>2.14</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.3</v>
+        <v>1.79</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.6</v>
+        <v>1.79</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>2.32</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.7</v>
+        <v>1.82</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.3</v>
+        <v>1.79</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.9</v>
+        <v>2.68</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,184 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="G17" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="S17" t="n">
-        <v>2.68</v>
+        <v>2.16</v>
       </c>
       <c r="T17" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="U17" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="X17" t="n">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="Z17" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>20</v>
       </c>
-      <c r="AI17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>32</v>
-      </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AL17" t="n">
         <v>32</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>17.5</v>
+        <v>5.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AP17" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>5.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Utd</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.16</v>
+        <v>3.75</v>
       </c>
       <c r="G18" t="n">
-        <v>2.44</v>
+        <v>4.5</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="L18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.28</v>
       </c>
-      <c r="M18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.71</v>
-      </c>
       <c r="X18" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="Y18" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF18" t="n">
         <v>42</v>
       </c>
-      <c r="AF18" t="n">
-        <v>17</v>
-      </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AH18" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK18" t="n">
         <v>48</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>24</v>
-      </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN18" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ18" t="n">
         <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>20</v>
+        <v>3.95</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.6</v>
+        <v>3.65</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>19</v>
+        <v>4.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BF18" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,94 +4046,94 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.92</v>
+        <v>2.16</v>
       </c>
       <c r="H19" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.36</v>
       </c>
-      <c r="P19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.52</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="X19" t="n">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC19" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>13</v>
@@ -4142,90 +4142,90 @@
         <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AK19" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AY19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG19" t="n">
         <v>20</v>
       </c>
-      <c r="AX19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Queens Park</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Raith</t>
+          <t>Boston Utd</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.94</v>
+        <v>2.16</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="M20" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>1.54</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.54</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>5.1</v>
+        <v>2.74</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="X20" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB20" t="n">
         <v>21</v>
       </c>
-      <c r="AG20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX20" t="n">
+      <c r="BC20" t="n">
         <v>16.5</v>
       </c>
-      <c r="AY20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BD20" t="n">
-        <v>50</v>
+        <v>3.85</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="BF20" t="n">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5</v>
+        <v>2.66</v>
       </c>
       <c r="I21" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="P21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1.69</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
-        <v>2.54</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.37</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.48</v>
+        <v>4.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.37</v>
+        <v>4.7</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.31</v>
+        <v>3.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.37</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.9</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.37</v>
+        <v>4.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.32</v>
+        <v>3.9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.3</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.86</v>
+        <v>4.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>4.7</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.21</v>
+        <v>4.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.21</v>
+        <v>5.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.21</v>
+        <v>4.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.24</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,378 +4623,766 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Queens Park</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Raith</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="G22" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="H22" t="n">
         <v>2.64</v>
       </c>
       <c r="I22" t="n">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="J22" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="L22" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="N22" t="n">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="P22" t="n">
-        <v>2.92</v>
+        <v>1.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.5</v>
+        <v>2.54</v>
       </c>
       <c r="R22" t="n">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>2.26</v>
+        <v>5.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W22" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="X22" t="n">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y22" t="n">
-        <v>19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH22" t="n">
         <v>23</v>
       </c>
-      <c r="AA22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD22" t="n">
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR22" t="n">
         <v>13</v>
       </c>
-      <c r="AE22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH22" t="n">
+      <c r="AS22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX22" t="n">
         <v>15</v>
       </c>
-      <c r="AI22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ22" t="n">
+      <c r="AY22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>17</v>
       </c>
-      <c r="AR22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>14</v>
-      </c>
       <c r="BA22" t="n">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC22" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BD22" t="n">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="BF22" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Scottish League One</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Peterhead</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Inverness CT</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:50:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>UEFA Champions League</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X24" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:50:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Atletico Madrid</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F25" t="n">
         <v>3.9</v>
       </c>
-      <c r="G23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="G25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H25" t="n">
         <v>1.88</v>
       </c>
-      <c r="J23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="I25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J25" t="n">
         <v>4.7</v>
       </c>
-      <c r="L23" t="n">
+      <c r="K25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L25" t="n">
         <v>1.21</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>1.02</v>
       </c>
-      <c r="N23" t="n">
-        <v>9</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="N25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O25" t="n">
         <v>1.11</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>1.37</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>2.06</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>1.92</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>1.42</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>3.25</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V25" t="n">
         <v>2.12</v>
       </c>
-      <c r="W23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="W25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X25" t="n">
         <v>44</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y25" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI25" t="n">
         <v>20</v>
       </c>
-      <c r="Z23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="AJ25" t="n">
         <v>75</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AK25" t="n">
         <v>36</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AL25" t="n">
         <v>32</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AM25" t="n">
         <v>40</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AN25" t="n">
         <v>18</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AO25" t="n">
         <v>5.8</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AP25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX25" t="n">
         <v>36</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AY25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA25" t="n">
         <v>19</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="BB25" t="n">
+        <v>65</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF25" t="n">
         <v>17</v>
       </c>
-      <c r="AS23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>60</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG23" t="n">
+      <c r="BG25" t="n">
         <v>5.5</v>
       </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2026-04-13 09:39:50</t>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH25"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al-Jndal</t>
+          <t>Dalian Kewei</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al-Ula FC</t>
+          <t>Haimen Codion</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K2" t="n">
         <v>7.6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>13</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,22 +781,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.38</v>
+        <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -805,10 +805,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>3.05</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aris FC Limassol</t>
+          <t>Beijing Tech FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Shanghai Port B</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>3.55</v>
+        <v>550</v>
       </c>
       <c r="H3" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>2.46</v>
+        <v>660</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.32</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.27</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>1.32</v>
       </c>
       <c r="T3" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>04:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Jiangxi Lushan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Apollon Limassol</t>
+          <t>Guizhou Zhucheng Athletic</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="G4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I4" t="n">
         <v>2.82</v>
       </c>
-      <c r="H4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.35</v>
-      </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,60 +1325,60 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>05:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Hunedoara</t>
+          <t>Hubei Istar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Ganzhou Ruishi FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.26</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Alashkert</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>FC Ararat Yerevan</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1.41</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>1.66</v>
       </c>
       <c r="H6" t="n">
-        <v>2.36</v>
+        <v>5.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.58</v>
+        <v>140</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>1.81</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,117 +1713,117 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Guangdong Mingtu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Guangzhou Alpha</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J7" t="n">
         <v>2.6</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.8</v>
-      </c>
       <c r="K7" t="n">
-        <v>2.96</v>
+        <v>5.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>1.44</v>
       </c>
       <c r="O7" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
@@ -1835,69 +1835,69 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>10:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Al-Jndal</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia</t>
+          <t>Al-Ula FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>2.76</v>
+        <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>1.45</v>
       </c>
       <c r="J8" t="n">
-        <v>2.94</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>3.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Aris FC Limassol</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NK Maribor</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="H9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I9" t="n">
         <v>2.44</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.76</v>
-      </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="U9" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="Y9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG9" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AH9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
         <v>42</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AO9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW9" t="n">
         <v>18</v>
       </c>
-      <c r="AC9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH9" t="n">
+      <c r="AX9" t="n">
         <v>17.5</v>
       </c>
-      <c r="AI9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG9" t="n">
         <v>13</v>
       </c>
-      <c r="AU9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:20:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al-Wahda (KSA)</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Adalh</t>
+          <t>Apollon Limassol</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>1.15</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>1.15</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.19</v>
+        <v>1.91</v>
       </c>
       <c r="R10" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>1.19</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,72 +2489,72 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hunedoara</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puskas Akademia</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>1.28</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>1.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>1.31</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2569,10 +2569,10 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2581,10 +2581,10 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2593,10 +2593,10 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2605,75 +2605,75 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>2.54</v>
       </c>
       <c r="J12" t="n">
         <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U12" t="n">
         <v>2.12</v>
       </c>
-      <c r="T12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.32</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="X12" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM12" t="n">
         <v>110</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AN12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR12" t="n">
         <v>14</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AS12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY12" t="n">
         <v>12</v>
       </c>
-      <c r="AD12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG12" t="n">
         <v>5.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G13" t="n">
         <v>2.82</v>
       </c>
       <c r="H13" t="n">
-        <v>2.84</v>
+        <v>3.45</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="L13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.38</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.55</v>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA13" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
         <v>48</v>
       </c>
       <c r="AK13" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY13" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT13" t="n">
+      <c r="AZ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE13" t="n">
         <v>9.6</v>
       </c>
-      <c r="AU13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7</v>
-      </c>
       <c r="BF13" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,99 +3071,99 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="I14" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
         <v>1.41</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AF14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG14" t="n">
         <v>16</v>
@@ -3172,90 +3172,90 @@
         <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="n">
         <v>44</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO14" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AP14" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.6</v>
+        <v>3.95</v>
       </c>
       <c r="AX14" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>18.5</v>
+        <v>3.9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>NK Maribor</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="M15" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.54</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S15" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="U15" t="n">
-        <v>1.79</v>
+        <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W15" t="n">
         <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="Z15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
         <v>21</v>
       </c>
-      <c r="AA15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>55</v>
-      </c>
       <c r="AO15" t="n">
-        <v>65</v>
+        <v>17.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AR15" t="n">
         <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AX15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF15" t="n">
         <v>14.5</v>
       </c>
-      <c r="AY15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,102 +3459,102 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:20:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Al-Wahda (KSA)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>2.68</v>
+        <v>1.02</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.18</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.12</v>
-      </c>
       <c r="S16" t="n">
-        <v>7.6</v>
+        <v>1.19</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
         <v>1000</v>
@@ -3581,69 +3581,69 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.36</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.32</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.82</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>Puskas Akademia</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.58</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.63</v>
-      </c>
       <c r="H17" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="J17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>4.6</v>
       </c>
-      <c r="K17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X17" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BA17" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.75</v>
+        <v>2.68</v>
       </c>
       <c r="G18" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="H18" t="n">
-        <v>1.78</v>
+        <v>2.9</v>
       </c>
       <c r="I18" t="n">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>5.8</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="R18" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>2.18</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="X18" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE18" t="n">
         <v>34</v>
       </c>
-      <c r="Y18" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE18" t="n">
+      <c r="AF18" t="n">
         <v>20</v>
       </c>
-      <c r="AF18" t="n">
-        <v>42</v>
-      </c>
       <c r="AG18" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AK18" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AL18" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AN18" t="n">
         <v>32</v>
       </c>
       <c r="AO18" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY18" t="n">
         <v>11</v>
       </c>
-      <c r="AR18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="G19" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="I19" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>1.02</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S19" t="n">
-        <v>2.68</v>
+        <v>2.12</v>
       </c>
       <c r="T19" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="U19" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="X19" t="n">
         <v>24</v>
       </c>
       <c r="Y19" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="Z19" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB19" t="n">
         <v>12.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
         <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="AO19" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AP19" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="BA19" t="n">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="BD19" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boston Utd</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="G20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H20" t="n">
         <v>2.44</v>
       </c>
-      <c r="H20" t="n">
-        <v>3</v>
-      </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="J20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.55</v>
       </c>
-      <c r="K20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.74</v>
-      </c>
       <c r="T20" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="U20" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Y20" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO20" t="n">
         <v>30</v>
       </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>32</v>
-      </c>
       <c r="AP20" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>17.5</v>
+        <v>5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AT20" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU20" t="n">
         <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>4.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>16.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,99 +4429,99 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J21" t="n">
         <v>2.9</v>
       </c>
-      <c r="H21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="O21" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="P21" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z21" t="n">
         <v>21</v>
       </c>
       <c r="AA21" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD21" t="n">
         <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>14.5</v>
@@ -4530,90 +4530,90 @@
         <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ21" t="n">
         <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AL21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN21" t="n">
         <v>55</v>
       </c>
-      <c r="AM21" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN21" t="n">
+      <c r="AO21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW21" t="n">
         <v>38</v>
       </c>
-      <c r="AO21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AX21" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE21" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BD21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF21" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,105 +4623,105 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Queens Park</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raith</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="G22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.3</v>
       </c>
-      <c r="H22" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="R22" t="n">
         <v>1.12</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.22</v>
-      </c>
       <c r="S22" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W22" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="X22" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG22" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
@@ -4730,7 +4730,7 @@
         <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -4742,72 +4742,72 @@
         <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AR22" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="AT22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV22" t="n">
         <v>7</v>
       </c>
-      <c r="AU22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>10</v>
-      </c>
       <c r="AW22" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="AX22" t="n">
-        <v>15</v>
+        <v>3.05</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>3.55</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>3.15</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="BC22" t="n">
-        <v>8</v>
+        <v>1.73</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE22" t="n">
-        <v>9</v>
+        <v>1.76</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="BG22" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N23" t="n">
         <v>6</v>
       </c>
-      <c r="G23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.75</v>
-      </c>
       <c r="O23" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="S23" t="n">
-        <v>2.74</v>
+        <v>2.18</v>
       </c>
       <c r="T23" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="V23" t="n">
-        <v>2.52</v>
+        <v>1.19</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>2.66</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.5</v>
+        <v>22</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.65</v>
+        <v>7.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.75</v>
+        <v>5.9</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AX23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF23" t="n">
         <v>5</v>
       </c>
-      <c r="AY23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BG23" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="G24" t="n">
-        <v>2.54</v>
+        <v>4.5</v>
       </c>
       <c r="H24" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.64</v>
+        <v>1.94</v>
       </c>
       <c r="J24" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="M24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.16</v>
       </c>
       <c r="P24" t="n">
-        <v>2.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R24" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="S24" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="T24" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="U24" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.61</v>
+        <v>2.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN24" t="n">
         <v>32</v>
       </c>
-      <c r="Y24" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AO24" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AP24" t="n">
-        <v>28</v>
+        <v>4.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>20</v>
+        <v>3.95</v>
       </c>
       <c r="AS24" t="n">
-        <v>34</v>
+        <v>4.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>17.5</v>
+        <v>4.3</v>
       </c>
       <c r="AU24" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AX24" t="n">
-        <v>19.5</v>
+        <v>4.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="BB24" t="n">
-        <v>32</v>
+        <v>4.8</v>
       </c>
       <c r="BC24" t="n">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>24</v>
+        <v>4.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>44</v>
+        <v>4.7</v>
       </c>
       <c r="BF24" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,184 +5205,1348 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>3.95</v>
+        <v>2.16</v>
       </c>
       <c r="H25" t="n">
-        <v>1.88</v>
+        <v>3.7</v>
       </c>
       <c r="I25" t="n">
-        <v>1.89</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="R25" t="n">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="S25" t="n">
-        <v>1.92</v>
+        <v>2.68</v>
       </c>
       <c r="T25" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="U25" t="n">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="V25" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.34</v>
+        <v>1.86</v>
       </c>
       <c r="X25" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AA25" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="AC25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG25" t="n">
         <v>13</v>
       </c>
-      <c r="AD25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AH25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AJ25" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AK25" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AL25" t="n">
         <v>32</v>
       </c>
       <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Wealdstone</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Boston Utd</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X26" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL26" t="n">
         <v>40</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Airdrieonians</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Dunfermline</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Queens Park</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Raith</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z28" t="n">
         <v>18</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Scottish League One</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Peterhead</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Inverness CT</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N30" t="n">
+        <v>7</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X30" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X31" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO31" t="n">
         <v>5.8</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AP31" t="n">
         <v>38</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="AQ31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR31" t="n">
         <v>17</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AS31" t="n">
         <v>22</v>
       </c>
-      <c r="AT25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AU25" t="n">
+      <c r="AT31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU31" t="n">
         <v>11.5</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AV31" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AW31" t="n">
         <v>14.5</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AX31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>65</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE31" t="n">
         <v>36</v>
       </c>
-      <c r="AY25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>65</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF25" t="n">
+      <c r="BF31" t="n">
         <v>17</v>
       </c>
-      <c r="BG25" t="n">
+      <c r="BG31" t="n">
         <v>5.5</v>
       </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>2026-04-13 11:50:04</t>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="G2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="AY2" t="n">
         <v>3.35</v>
       </c>
-      <c r="J2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="G3" t="n">
         <v>550</v>
@@ -963,7 +963,7 @@
         <v>660</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -972,25 +972,25 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="O3" t="n">
         <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Q3" t="n">
         <v>1.32</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -1157,16 +1157,16 @@
         <v>2.82</v>
       </c>
       <c r="J4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
         <v>1.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
         <v>1.51</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
         <v>1.81</v>
@@ -1566,13 +1566,13 @@
         <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.28</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
         <v>1.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>1.72</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
         <v>1.44</v>
@@ -1775,7 +1775,7 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
         <v>1.24</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2348,7 +2348,7 @@
         <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
         <v>1.66</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -2709,13 +2709,13 @@
         <v>2.54</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -2853,14 +2853,14 @@
         <v>6.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG12" t="n">
         <v>5.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="G13" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="K13" t="n">
         <v>2.96</v>
@@ -2915,34 +2915,34 @@
         <v>1.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="P13" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
         <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
         <v>8</v>
@@ -2969,10 +2969,10 @@
         <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH13" t="n">
         <v>26</v>
@@ -2981,46 +2981,46 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AL13" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR13" t="n">
         <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3032,29 +3032,29 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.74</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="n">
         <v>2.78</v>
@@ -3097,7 +3097,7 @@
         <v>3.2</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="K14" t="n">
         <v>3.3</v>
@@ -3112,7 +3112,7 @@
         <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="P14" t="n">
         <v>1.7</v>
@@ -3136,7 +3136,7 @@
         <v>1.49</v>
       </c>
       <c r="W14" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="X14" t="n">
         <v>13</v>
@@ -3166,7 +3166,7 @@
         <v>24</v>
       </c>
       <c r="AG14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH14" t="n">
         <v>21</v>
@@ -3196,7 +3196,7 @@
         <v>7.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR14" t="n">
         <v>14</v>
@@ -3211,10 +3211,10 @@
         <v>5.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AX14" t="n">
         <v>14</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H15" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I15" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J15" t="n">
         <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.27</v>
@@ -3327,7 +3327,7 @@
         <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W15" t="n">
         <v>1.5</v>
@@ -3381,7 +3381,7 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="n">
         <v>17.5</v>
@@ -3396,7 +3396,7 @@
         <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
         <v>13</v>
@@ -3420,19 +3420,19 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
         <v>4.9</v>
       </c>
       <c r="BC15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BD15" t="n">
         <v>5.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF15" t="n">
         <v>14.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>1.47</v>
       </c>
       <c r="G17" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="H17" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.26</v>
@@ -3709,16 +3709,16 @@
         <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3733,13 +3733,13 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -3757,10 +3757,10 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK17" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AL17" t="n">
         <v>1000</v>
@@ -3769,68 +3769,68 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>19.5</v>
+        <v>5.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -3867,73 +3867,73 @@
         <v>2.78</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="I18" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="O18" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
         <v>1.56</v>
       </c>
       <c r="X18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="n">
         <v>22</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB18" t="n">
         <v>12.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
         <v>34</v>
@@ -3945,64 +3945,64 @@
         <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AJ18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL18" t="n">
         <v>48</v>
       </c>
-      <c r="AK18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>55</v>
-      </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP18" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ18" t="n">
         <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU18" t="n">
         <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX18" t="n">
         <v>15.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB18" t="n">
         <v>30</v>
@@ -4011,7 +4011,7 @@
         <v>23</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE18" t="n">
         <v>7.2</v>
@@ -4020,11 +4020,11 @@
         <v>20</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.3</v>
@@ -4097,40 +4097,40 @@
         <v>2.12</v>
       </c>
       <c r="T19" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U19" t="n">
         <v>2.32</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Z19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB19" t="n">
         <v>12.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
         <v>13.5</v>
@@ -4139,86 +4139,86 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AU19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB19" t="n">
         <v>4.9</v>
       </c>
-      <c r="AV19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX19" t="n">
+      <c r="BC19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD19" t="n">
         <v>5.5</v>
       </c>
-      <c r="AY19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ19" t="n">
+      <c r="BE19" t="n">
         <v>6</v>
       </c>
-      <c r="BA19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF19" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H20" t="n">
         <v>2.44</v>
       </c>
       <c r="I20" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J20" t="n">
         <v>3.2</v>
@@ -4288,10 +4288,10 @@
         <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U20" t="n">
         <v>2.06</v>
@@ -4300,7 +4300,7 @@
         <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
         <v>15</v>
@@ -4324,13 +4324,13 @@
         <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF20" t="n">
         <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH20" t="n">
         <v>21</v>
@@ -4342,7 +4342,7 @@
         <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4351,43 +4351,43 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
         <v>30</v>
       </c>
       <c r="AP20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS20" t="n">
         <v>5</v>
       </c>
-      <c r="AS20" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AT20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY20" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BA20" t="n">
         <v>4.9</v>
@@ -4396,23 +4396,23 @@
         <v>4.8</v>
       </c>
       <c r="BC20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE20" t="n">
         <v>4.9</v>
       </c>
-      <c r="BD20" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF20" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG20" t="n">
         <v>19.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -4443,46 +4443,46 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
         <v>2.98</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.1</v>
       </c>
       <c r="I21" t="n">
         <v>3.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N21" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="O21" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="P21" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="R21" t="n">
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="T21" t="n">
         <v>2.08</v>
@@ -4491,7 +4491,7 @@
         <v>1.79</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
         <v>1.5</v>
@@ -4512,7 +4512,7 @@
         <v>8.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD21" t="n">
         <v>15</v>
@@ -4530,7 +4530,7 @@
         <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ21" t="n">
         <v>55</v>
@@ -4539,19 +4539,19 @@
         <v>44</v>
       </c>
       <c r="AL21" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN21" t="n">
         <v>55</v>
       </c>
       <c r="AO21" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ21" t="n">
         <v>7.6</v>
@@ -4584,29 +4584,29 @@
         <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H22" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="I22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K22" t="n">
         <v>2.9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.92</v>
       </c>
       <c r="L22" t="n">
         <v>1.6</v>
@@ -4661,7 +4661,7 @@
         <v>1.18</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O22" t="n">
         <v>1.76</v>
@@ -4679,34 +4679,34 @@
         <v>7.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X22" t="n">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AB22" t="n">
         <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>6</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV22" t="n">
         <v>7</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AX22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>3.05</v>
       </c>
-      <c r="AY22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BA22" t="n">
-        <v>11.5</v>
+        <v>3.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.76</v>
+        <v>3.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BG22" t="n">
-        <v>46</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I23" t="n">
         <v>6.2</v>
@@ -4858,31 +4858,31 @@
         <v>6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="Q23" t="n">
         <v>1.47</v>
       </c>
       <c r="R23" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="S23" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="T23" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U23" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="V23" t="n">
         <v>1.19</v>
       </c>
       <c r="W23" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="X23" t="n">
         <v>34</v>
@@ -4906,13 +4906,13 @@
         <v>24</v>
       </c>
       <c r="AE23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF23" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
         <v>21</v>
@@ -4921,80 +4921,80 @@
         <v>60</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM23" t="n">
         <v>75</v>
       </c>
       <c r="AN23" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AO23" t="n">
         <v>55</v>
       </c>
       <c r="AP23" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AQ23" t="n">
         <v>22</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AU23" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE23" t="n">
         <v>5.9</v>
       </c>
-      <c r="AW23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>7</v>
-      </c>
       <c r="BF23" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -5028,58 +5028,58 @@
         <v>3.85</v>
       </c>
       <c r="G24" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="I24" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="J24" t="n">
         <v>3.85</v>
       </c>
       <c r="K24" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="R24" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S24" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="T24" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V24" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y24" t="n">
         <v>970</v>
@@ -5091,28 +5091,28 @@
         <v>25</v>
       </c>
       <c r="AB24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC24" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AD24" t="n">
         <v>970</v>
       </c>
       <c r="AE24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG24" t="n">
         <v>20</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>21</v>
       </c>
       <c r="AH24" t="n">
         <v>970</v>
       </c>
       <c r="AI24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ24" t="n">
         <v>90</v>
@@ -5121,43 +5121,43 @@
         <v>48</v>
       </c>
       <c r="AL24" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM24" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO24" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR24" t="n">
         <v>11</v>
       </c>
-      <c r="AR24" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT24" t="n">
         <v>4.3</v>
       </c>
       <c r="AU24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV24" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV24" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AW24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY24" t="n">
         <v>4.1</v>
@@ -5166,29 +5166,29 @@
         <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE24" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -5234,10 +5234,10 @@
         <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
@@ -5249,13 +5249,13 @@
         <v>1.23</v>
       </c>
       <c r="P25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q25" t="n">
         <v>1.69</v>
       </c>
       <c r="R25" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S25" t="n">
         <v>2.68</v>
@@ -5324,7 +5324,7 @@
         <v>14.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP25" t="n">
         <v>14.5</v>
@@ -5336,7 +5336,7 @@
         <v>20</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT25" t="n">
         <v>8.800000000000001</v>
@@ -5357,7 +5357,7 @@
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BA25" t="n">
         <v>26</v>
@@ -5372,17 +5372,17 @@
         <v>21</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BG25" t="n">
         <v>20</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="G26" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I26" t="n">
         <v>3.5</v>
@@ -5428,7 +5428,7 @@
         <v>3.55</v>
       </c>
       <c r="K26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.28</v>
@@ -5449,7 +5449,7 @@
         <v>1.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
         <v>2.74</v>
@@ -5458,19 +5458,19 @@
         <v>1.62</v>
       </c>
       <c r="U26" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V26" t="n">
         <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="X26" t="n">
         <v>23</v>
       </c>
       <c r="Y26" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
         <v>30</v>
@@ -5479,7 +5479,7 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
@@ -5491,22 +5491,22 @@
         <v>42</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH26" t="n">
         <v>19.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL26" t="n">
         <v>40</v>
@@ -5515,10 +5515,10 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
         <v>13.5</v>
@@ -5530,7 +5530,7 @@
         <v>17.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AT26" t="n">
         <v>9</v>
@@ -5542,7 +5542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AX26" t="n">
         <v>12</v>
@@ -5554,7 +5554,7 @@
         <v>11.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BB26" t="n">
         <v>21</v>
@@ -5563,10 +5563,10 @@
         <v>16.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BF26" t="n">
         <v>10.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="G27" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="H27" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="I27" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="J27" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
@@ -5634,10 +5634,10 @@
         <v>3.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P27" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q27" t="n">
         <v>2.04</v>
@@ -5646,7 +5646,7 @@
         <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T27" t="n">
         <v>1.81</v>
@@ -5655,122 +5655,122 @@
         <v>2.02</v>
       </c>
       <c r="V27" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="W27" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="X27" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AB27" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD27" t="n">
         <v>12</v>
       </c>
       <c r="AE27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
         <v>20</v>
       </c>
       <c r="AI27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL27" t="n">
         <v>55</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AM27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN27" t="n">
         <v>55</v>
       </c>
-      <c r="AK27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>36</v>
-      </c>
       <c r="AO27" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="AX27" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ27" t="n">
         <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BB27" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC27" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BD27" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>26</v>
+        <v>8.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -5801,55 +5801,55 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="J28" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K28" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L28" t="n">
         <v>1.5</v>
       </c>
       <c r="M28" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O28" t="n">
         <v>1.54</v>
       </c>
       <c r="P28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V28" t="n">
         <v>1.54</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.51</v>
       </c>
       <c r="W28" t="n">
         <v>1.43</v>
@@ -5882,7 +5882,7 @@
         <v>25</v>
       </c>
       <c r="AG28" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AH28" t="n">
         <v>23</v>
@@ -5903,7 +5903,7 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
         <v>50</v>
@@ -5915,22 +5915,22 @@
         <v>6.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT28" t="n">
         <v>7.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AV28" t="n">
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AX28" t="n">
         <v>15</v>
@@ -5939,32 +5939,32 @@
         <v>12</v>
       </c>
       <c r="AZ28" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC28" t="n">
         <v>36</v>
       </c>
       <c r="BD28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE28" t="n">
         <v>6.8</v>
       </c>
-      <c r="BE28" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF28" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G29" t="n">
         <v>9</v>
@@ -6037,13 +6037,13 @@
         <v>2.74</v>
       </c>
       <c r="T29" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U29" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V29" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="W29" t="n">
         <v>1.13</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR29" t="n">
         <v>3.65</v>
       </c>
       <c r="AS29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.5</v>
+        <v>2.96</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AW29" t="n">
         <v>4.2</v>
       </c>
       <c r="AX29" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.4</v>
+        <v>2.92</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.84</v>
+        <v>3.25</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="BG29" t="n">
         <v>3.3</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -6195,19 +6195,19 @@
         <v>2.5</v>
       </c>
       <c r="H30" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.66</v>
       </c>
-      <c r="I30" t="n">
-        <v>2.68</v>
-      </c>
       <c r="J30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K30" t="n">
         <v>4.5</v>
       </c>
-      <c r="K30" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M30" t="n">
         <v>1.03</v>
@@ -6216,31 +6216,31 @@
         <v>7</v>
       </c>
       <c r="O30" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P30" t="n">
         <v>3.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R30" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="S30" t="n">
         <v>2.16</v>
       </c>
       <c r="T30" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U30" t="n">
         <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X30" t="n">
         <v>34</v>
@@ -6258,7 +6258,7 @@
         <v>19</v>
       </c>
       <c r="AC30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD30" t="n">
         <v>13</v>
@@ -6285,7 +6285,7 @@
         <v>21</v>
       </c>
       <c r="AL30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM30" t="n">
         <v>46</v>
@@ -6300,7 +6300,7 @@
         <v>29</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR30" t="n">
         <v>21</v>
@@ -6342,7 +6342,7 @@
         <v>23</v>
       </c>
       <c r="BE30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF30" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -6389,10 +6389,10 @@
         <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I31" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J31" t="n">
         <v>4.6</v>
@@ -6407,25 +6407,25 @@
         <v>1.02</v>
       </c>
       <c r="N31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O31" t="n">
         <v>1.11</v>
       </c>
       <c r="P31" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R31" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S31" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="T31" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U31" t="n">
         <v>3.25</v>
@@ -6440,10 +6440,10 @@
         <v>42</v>
       </c>
       <c r="Y31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z31" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA31" t="n">
         <v>24</v>
@@ -6455,7 +6455,7 @@
         <v>12.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6467,10 +6467,10 @@
         <v>17.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="n">
         <v>75</v>
@@ -6482,13 +6482,13 @@
         <v>32</v>
       </c>
       <c r="AM31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN31" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AP31" t="n">
         <v>38</v>
@@ -6497,7 +6497,7 @@
         <v>20</v>
       </c>
       <c r="AR31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS31" t="n">
         <v>22</v>
@@ -6509,19 +6509,19 @@
         <v>11.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
         <v>14.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA31" t="n">
         <v>19.5</v>
@@ -6530,13 +6530,13 @@
         <v>65</v>
       </c>
       <c r="BC31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF31" t="n">
         <v>17</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -781,13 +781,13 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
         <v>1.95</v>
@@ -796,31 +796,31 @@
         <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
         <v>1.52</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB2" t="n">
         <v>14</v>
@@ -829,98 +829,98 @@
         <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>55</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>60</v>
-      </c>
       <c r="AK2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AO2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>550</v>
+        <v>970</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>660</v>
+        <v>1.83</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
@@ -972,37 +972,37 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.31</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U3" t="n">
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1062,59 +1062,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -1145,64 +1145,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="I4" t="n">
-        <v>2.82</v>
+        <v>2.54</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V4" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR5" t="n">
         <v>5.5</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -1542,10 +1542,10 @@
         <v>5.7</v>
       </c>
       <c r="I6" t="n">
-        <v>140</v>
+        <v>970</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K6" t="n">
         <v>8.4</v>
@@ -1557,7 +1557,7 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O6" t="n">
         <v>1.29</v>
@@ -1566,13 +1566,13 @@
         <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="R6" t="n">
         <v>1.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1581,7 +1581,7 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
         <v>2.5</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
         <v>2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>5.9</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1769,7 +1769,7 @@
         <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U7" t="n">
         <v>1.01</v>
@@ -1883,14 +1883,14 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -1942,16 +1942,16 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
         <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
         <v>1.47</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -2115,136 +2115,136 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G9" t="n">
         <v>3.55</v>
       </c>
       <c r="H9" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="I9" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="T9" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="W9" t="n">
         <v>1.39</v>
       </c>
       <c r="X9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z9" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>19</v>
-      </c>
       <c r="AA9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB9" t="n">
         <v>16.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AF9" t="n">
         <v>29</v>
       </c>
       <c r="AG9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO9" t="n">
         <v>17.5</v>
       </c>
-      <c r="AH9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>22</v>
-      </c>
       <c r="AP9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR9" t="n">
         <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>4.7</v>
       </c>
       <c r="AX9" t="n">
         <v>17.5</v>
@@ -2253,32 +2253,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="BG9" t="n">
         <v>13</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2342,7 +2342,7 @@
         <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R10" t="n">
         <v>1.31</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -2527,13 +2527,13 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O11" t="n">
         <v>1.31</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Q11" t="n">
         <v>1.31</v>
@@ -2542,7 +2542,7 @@
         <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2659,14 +2659,14 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
         <v>2.4</v>
       </c>
       <c r="I12" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
         <v>1.35</v>
@@ -2730,7 +2730,7 @@
         <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
         <v>1.35</v>
@@ -2745,7 +2745,7 @@
         <v>2.12</v>
       </c>
       <c r="V12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W12" t="n">
         <v>1.45</v>
@@ -2757,31 +2757,31 @@
         <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA12" t="n">
         <v>34</v>
       </c>
       <c r="AB12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>13</v>
-      </c>
       <c r="AE12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>40</v>
@@ -2790,7 +2790,7 @@
         <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
         <v>55</v>
@@ -2799,7 +2799,7 @@
         <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO12" t="n">
         <v>22</v>
@@ -2814,7 +2814,7 @@
         <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
         <v>10.5</v>
@@ -2838,29 +2838,29 @@
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>30</v>
+        <v>5.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
@@ -2906,34 +2906,34 @@
         <v>2.66</v>
       </c>
       <c r="K13" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N13" t="n">
         <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
         <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U13" t="n">
         <v>1.73</v>
@@ -2948,10 +2948,10 @@
         <v>8</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
         <v>75</v>
@@ -2969,10 +2969,10 @@
         <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
         <v>26</v>
@@ -2987,7 +2987,7 @@
         <v>55</v>
       </c>
       <c r="AL13" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3020,7 +3020,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3032,29 +3032,29 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.8</v>
+        <v>60</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.8</v>
+        <v>44</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G14" t="n">
         <v>3.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I14" t="n">
         <v>3.2</v>
       </c>
       <c r="J14" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K14" t="n">
         <v>3.3</v>
@@ -3112,7 +3112,7 @@
         <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P14" t="n">
         <v>1.7</v>
@@ -3136,7 +3136,7 @@
         <v>1.49</v>
       </c>
       <c r="W14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X14" t="n">
         <v>13</v>
@@ -3163,10 +3163,10 @@
         <v>46</v>
       </c>
       <c r="AF14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH14" t="n">
         <v>21</v>
@@ -3193,7 +3193,7 @@
         <v>44</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
         <v>8</v>
@@ -3208,13 +3208,13 @@
         <v>7.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AV14" t="n">
         <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AX14" t="n">
         <v>14</v>
@@ -3232,23 +3232,23 @@
         <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD14" t="n">
         <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
         <v>1.55</v>
       </c>
       <c r="U15" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V15" t="n">
         <v>1.58</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -3494,16 +3494,16 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q16" t="n">
         <v>1.19</v>
@@ -3581,52 +3581,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="H17" t="n">
         <v>7</v>
@@ -3718,10 +3718,10 @@
         <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y17" t="n">
         <v>1000</v>
@@ -3736,19 +3736,19 @@
         <v>11</v>
       </c>
       <c r="AC17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>26</v>
@@ -3757,7 +3757,7 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AK17" t="n">
         <v>16</v>
@@ -3769,7 +3769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -3781,10 +3781,10 @@
         <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
@@ -3793,10 +3793,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AX17" t="n">
         <v>8.800000000000001</v>
@@ -3808,7 +3808,7 @@
         <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BB17" t="n">
         <v>11.5</v>
@@ -3817,20 +3817,20 @@
         <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BF17" t="n">
         <v>5.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I18" t="n">
         <v>2.86</v>
       </c>
-      <c r="I18" t="n">
-        <v>2.94</v>
-      </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L18" t="n">
         <v>1.35</v>
@@ -3894,37 +3894,37 @@
         <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U18" t="n">
         <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W18" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X18" t="n">
         <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB18" t="n">
         <v>12.5</v>
@@ -3936,13 +3936,13 @@
         <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
         <v>20</v>
       </c>
       <c r="AG18" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH18" t="n">
         <v>16.5</v>
@@ -3951,10 +3951,10 @@
         <v>42</v>
       </c>
       <c r="AJ18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL18" t="n">
         <v>48</v>
@@ -3963,10 +3963,10 @@
         <v>100</v>
       </c>
       <c r="AN18" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
         <v>13</v>
@@ -3975,22 +3975,22 @@
         <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV18" t="n">
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX18" t="n">
         <v>15.5</v>
@@ -3999,32 +3999,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB18" t="n">
         <v>30</v>
       </c>
       <c r="BC18" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF18" t="n">
         <v>20</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>1.69</v>
       </c>
       <c r="G19" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
         <v>1.3</v>
@@ -4088,13 +4088,13 @@
         <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R19" t="n">
         <v>1.54</v>
       </c>
       <c r="S19" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="T19" t="n">
         <v>1.64</v>
@@ -4106,10 +4106,10 @@
         <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="X19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y19" t="n">
         <v>26</v>
@@ -4124,7 +4124,7 @@
         <v>12.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD19" t="n">
         <v>21</v>
@@ -4163,62 +4163,62 @@
         <v>48</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU19" t="n">
         <v>4.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG19" t="n">
         <v>6</v>
       </c>
-      <c r="BB19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I20" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J20" t="n">
         <v>3.2</v>
@@ -4300,7 +4300,7 @@
         <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
         <v>15</v>
@@ -4318,7 +4318,7 @@
         <v>13.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
         <v>14</v>
@@ -4357,13 +4357,13 @@
         <v>30</v>
       </c>
       <c r="AP20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS20" t="n">
         <v>5</v>
@@ -4378,10 +4378,10 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>16</v>
+        <v>4.5</v>
       </c>
       <c r="AY20" t="n">
         <v>11.5</v>
@@ -4390,29 +4390,29 @@
         <v>5</v>
       </c>
       <c r="BA20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB20" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.8</v>
       </c>
       <c r="BC20" t="n">
         <v>5</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG20" t="n">
         <v>19.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>3.3</v>
@@ -4458,16 +4458,16 @@
         <v>2.78</v>
       </c>
       <c r="K21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="M21" t="n">
         <v>1.14</v>
       </c>
       <c r="N21" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>1.58</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -4640,28 +4640,28 @@
         <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H22" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="I22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
         <v>2.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="M22" t="n">
         <v>1.18</v>
       </c>
       <c r="N22" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="O22" t="n">
         <v>1.76</v>
@@ -4676,10 +4676,10 @@
         <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
         <v>1.61</v>
@@ -4715,7 +4715,7 @@
         <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AG22" t="n">
         <v>970</v>
@@ -4766,7 +4766,7 @@
         <v>7</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AX22" t="n">
         <v>7.6</v>
@@ -4775,32 +4775,32 @@
         <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BA22" t="n">
         <v>3.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BE22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BF22" t="n">
         <v>3.4</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>3.3</v>
       </c>
       <c r="BG22" t="n">
         <v>10.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G23" t="n">
         <v>1.62</v>
@@ -4846,7 +4846,7 @@
         <v>4.6</v>
       </c>
       <c r="K23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.21</v>
@@ -4861,13 +4861,13 @@
         <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S23" t="n">
         <v>2.24</v>
@@ -4879,13 +4879,13 @@
         <v>2.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W23" t="n">
         <v>2.6</v>
       </c>
       <c r="X23" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="Y23" t="n">
         <v>32</v>
@@ -4903,13 +4903,13 @@
         <v>13.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG23" t="n">
         <v>10.5</v>
@@ -4921,16 +4921,16 @@
         <v>60</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK23" t="n">
         <v>19</v>
       </c>
       <c r="AL23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM23" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN23" t="n">
         <v>7</v>
@@ -4939,28 +4939,28 @@
         <v>55</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ23" t="n">
         <v>22</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.7</v>
+        <v>38</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
-        <v>9.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX23" t="n">
         <v>11.5</v>
@@ -4969,32 +4969,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BA23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD23" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.9</v>
       </c>
       <c r="BE23" t="n">
         <v>5.9</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
         <v>1.97</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K24" t="n">
         <v>4.8</v>
@@ -5058,7 +5058,7 @@
         <v>2.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R24" t="n">
         <v>1.62</v>
@@ -5079,7 +5079,7 @@
         <v>1.29</v>
       </c>
       <c r="X24" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="Y24" t="n">
         <v>970</v>
@@ -5097,7 +5097,7 @@
         <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
         <v>21</v>
@@ -5133,7 +5133,7 @@
         <v>970</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ24" t="n">
         <v>10.5</v>
@@ -5142,53 +5142,53 @@
         <v>11</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AU24" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA24" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BB24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC24" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BD24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF24" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG24" t="n">
         <v>6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -5228,10 +5228,10 @@
         <v>3.7</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J25" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K25" t="n">
         <v>4.2</v>
@@ -5246,19 +5246,19 @@
         <v>4.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P25" t="n">
         <v>2.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R25" t="n">
         <v>1.49</v>
       </c>
       <c r="S25" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="T25" t="n">
         <v>1.64</v>
@@ -5267,7 +5267,7 @@
         <v>2.34</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
         <v>1.86</v>
@@ -5354,10 +5354,10 @@
         <v>10.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BA25" t="n">
         <v>26</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -5473,40 +5473,40 @@
         <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE26" t="n">
         <v>42</v>
       </c>
       <c r="AF26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH26" t="n">
         <v>19</v>
       </c>
-      <c r="AG26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL26" t="n">
         <v>40</v>
@@ -5515,68 +5515,68 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP26" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR26" t="n">
         <v>17.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.6</v>
+        <v>38</v>
       </c>
       <c r="AT26" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV26" t="n">
         <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.5</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.5</v>
+        <v>28</v>
       </c>
       <c r="BB26" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="BC26" t="n">
         <v>16.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF26" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>19</v>
+        <v>5.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>3.05</v>
       </c>
       <c r="G27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H27" t="n">
         <v>2.38</v>
@@ -5625,7 +5625,7 @@
         <v>3.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
@@ -5634,10 +5634,10 @@
         <v>3.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q27" t="n">
         <v>2.04</v>
@@ -5649,7 +5649,7 @@
         <v>3.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U27" t="n">
         <v>2.02</v>
@@ -5673,7 +5673,7 @@
         <v>36</v>
       </c>
       <c r="AB27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC27" t="n">
         <v>7.8</v>
@@ -5685,7 +5685,7 @@
         <v>30</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
         <v>970</v>
@@ -5694,7 +5694,7 @@
         <v>20</v>
       </c>
       <c r="AI27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ27" t="n">
         <v>70</v>
@@ -5709,22 +5709,22 @@
         <v>120</v>
       </c>
       <c r="AN27" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP27" t="n">
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR27" t="n">
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT27" t="n">
         <v>10.5</v>
@@ -5736,7 +5736,7 @@
         <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
         <v>18.5</v>
@@ -5748,29 +5748,29 @@
         <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC27" t="n">
         <v>32</v>
       </c>
       <c r="BD27" t="n">
-        <v>44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG27" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -5804,28 +5804,28 @@
         <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H28" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I28" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J28" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M28" t="n">
         <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O28" t="n">
         <v>1.54</v>
@@ -5849,10 +5849,10 @@
         <v>1.82</v>
       </c>
       <c r="V28" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X28" t="n">
         <v>9.199999999999999</v>
@@ -5921,13 +5921,13 @@
         <v>6.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW28" t="n">
         <v>6</v>
@@ -5939,7 +5939,7 @@
         <v>12</v>
       </c>
       <c r="AZ28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA28" t="n">
         <v>6.4</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
         <v>9</v>
@@ -6004,13 +6004,13 @@
         <v>1.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K29" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L29" t="n">
         <v>1.34</v>
@@ -6040,10 +6040,10 @@
         <v>1.89</v>
       </c>
       <c r="U29" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V29" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="W29" t="n">
         <v>1.13</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.65</v>
+        <v>2.68</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="BB29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BC29" t="n">
         <v>3.25</v>
       </c>
-      <c r="BC29" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BD29" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G30" t="n">
         <v>2.48</v>
       </c>
-      <c r="G30" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.64</v>
       </c>
-      <c r="I30" t="n">
-        <v>2.66</v>
-      </c>
       <c r="J30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L30" t="n">
         <v>1.25</v>
@@ -6213,25 +6213,25 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O30" t="n">
         <v>1.15</v>
       </c>
       <c r="P30" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q30" t="n">
         <v>1.47</v>
       </c>
       <c r="R30" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S30" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T30" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U30" t="n">
         <v>3</v>
@@ -6240,31 +6240,31 @@
         <v>1.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X30" t="n">
         <v>34</v>
       </c>
       <c r="Y30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA30" t="n">
         <v>38</v>
       </c>
       <c r="AB30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD30" t="n">
         <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF30" t="n">
         <v>22</v>
@@ -6273,7 +6273,7 @@
         <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
@@ -6294,10 +6294,10 @@
         <v>11</v>
       </c>
       <c r="AO30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AQ30" t="n">
         <v>18.5</v>
@@ -6306,34 +6306,34 @@
         <v>21</v>
       </c>
       <c r="AS30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT30" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU30" t="n">
         <v>10.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW30" t="n">
         <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY30" t="n">
         <v>12</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA30" t="n">
         <v>24</v>
       </c>
       <c r="BB30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC30" t="n">
         <v>19.5</v>
@@ -6348,11 +6348,11 @@
         <v>10</v>
       </c>
       <c r="BG30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I31" t="n">
         <v>1.88</v>
       </c>
-      <c r="I31" t="n">
-        <v>1.89</v>
-      </c>
       <c r="J31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K31" t="n">
         <v>4.6</v>
-      </c>
-      <c r="K31" t="n">
-        <v>4.7</v>
       </c>
       <c r="L31" t="n">
         <v>1.21</v>
@@ -6410,37 +6410,37 @@
         <v>9.4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P31" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R31" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S31" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="T31" t="n">
         <v>1.41</v>
       </c>
       <c r="U31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V31" t="n">
         <v>2.12</v>
       </c>
       <c r="W31" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X31" t="n">
         <v>42</v>
       </c>
       <c r="Y31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z31" t="n">
         <v>18.5</v>
@@ -6449,7 +6449,7 @@
         <v>24</v>
       </c>
       <c r="AB31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC31" t="n">
         <v>12.5</v>
@@ -6458,19 +6458,19 @@
         <v>11.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF31" t="n">
         <v>40</v>
       </c>
       <c r="AG31" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH31" t="n">
         <v>14.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
         <v>75</v>
@@ -6485,10 +6485,10 @@
         <v>38</v>
       </c>
       <c r="AN31" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO31" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AP31" t="n">
         <v>38</v>
@@ -6500,19 +6500,19 @@
         <v>17.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT31" t="n">
         <v>30</v>
       </c>
       <c r="AU31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV31" t="n">
         <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX31" t="n">
         <v>36</v>
@@ -6521,13 +6521,13 @@
         <v>16.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BB31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BC31" t="n">
         <v>30</v>
@@ -6536,17 +6536,17 @@
         <v>29</v>
       </c>
       <c r="BE31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF31" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -781,7 +781,7 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="I3" t="n">
-        <v>1.83</v>
+        <v>660</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
@@ -975,7 +975,7 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
@@ -990,7 +990,7 @@
         <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="T3" t="n">
         <v>1.05</v>
@@ -999,10 +999,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -1181,10 +1181,10 @@
         <v>2.14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
         <v>1.9</v>
@@ -1253,13 +1253,13 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
         <v>3.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS4" t="n">
         <v>5.2</v>
@@ -1268,13 +1268,13 @@
         <v>4.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
         <v>5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -1366,19 +1366,19 @@
         <v>2.72</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
         <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="T5" t="n">
         <v>1.88</v>
@@ -1450,19 +1450,19 @@
         <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR5" t="n">
         <v>5.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
         <v>4</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AV5" t="n">
         <v>5</v>
@@ -1474,7 +1474,7 @@
         <v>4.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ5" t="n">
         <v>5.4</v>
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
         <v>6.8</v>
@@ -1498,11 +1498,11 @@
         <v>5.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G6" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.82</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.29</v>
-      </c>
       <c r="R6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.1</v>
       </c>
-      <c r="S6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.05</v>
-      </c>
       <c r="W6" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,104 +1599,104 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.02</v>
+        <v>7.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.02</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.02</v>
+        <v>10.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.02</v>
+        <v>5.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.02</v>
+        <v>8.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.02</v>
+        <v>10</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.02</v>
+        <v>4.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.02</v>
+        <v>5.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.02</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.02</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.02</v>
+        <v>5.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.02</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.02</v>
+        <v>10.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.02</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G7" t="n">
         <v>5.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="I7" t="n">
         <v>2.82</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1754,7 +1754,7 @@
         <v>1.44</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="P7" t="n">
         <v>1.44</v>
@@ -1775,7 +1775,7 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
         <v>1.24</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -1924,19 +1924,19 @@
         <v>7.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="I8" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="J8" t="n">
         <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,7 +1945,7 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="O8" t="n">
         <v>1.19</v>
@@ -1969,7 +1969,7 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
@@ -1984,13 +1984,13 @@
         <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2026,65 +2026,65 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H9" t="n">
         <v>2.16</v>
@@ -2127,7 +2127,7 @@
         <v>2.32</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
         <v>4.2</v>
@@ -2145,7 +2145,7 @@
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
         <v>1.71</v>
@@ -2154,7 +2154,7 @@
         <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T9" t="n">
         <v>1.61</v>
@@ -2166,10 +2166,10 @@
         <v>1.75</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
         <v>12.5</v>
@@ -2202,19 +2202,19 @@
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
         <v>70</v>
       </c>
       <c r="AK9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="n">
         <v>50</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>36</v>
@@ -2232,7 +2232,7 @@
         <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
         <v>11</v>
@@ -2244,7 +2244,7 @@
         <v>9.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
         <v>17.5</v>
@@ -2256,10 +2256,10 @@
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC9" t="n">
         <v>5.1</v>
@@ -2268,17 +2268,17 @@
         <v>34</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="BG9" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -2309,49 +2309,49 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
         <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I10" t="n">
         <v>3.35</v>
       </c>
       <c r="J10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.2</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.35</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
         <v>1.91</v>
@@ -2363,58 +2363,58 @@
         <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
         <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AC10" t="n">
         <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
         <v>9.4</v>
@@ -2423,56 +2423,56 @@
         <v>8.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
         <v>7.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>1.31</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
         <v>1.31</v>
       </c>
       <c r="P11" t="n">
-        <v>1.31</v>
+        <v>1.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.31</v>
+        <v>1.76</v>
       </c>
       <c r="R11" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2569,10 +2569,10 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2581,10 +2581,10 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2593,10 +2593,10 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2605,68 +2605,68 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.05</v>
+        <v>5.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -2697,25 +2697,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G12" t="n">
         <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
         <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -2730,7 +2730,7 @@
         <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R12" t="n">
         <v>1.35</v>
@@ -2739,13 +2739,13 @@
         <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U12" t="n">
         <v>2.12</v>
       </c>
       <c r="V12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W12" t="n">
         <v>1.45</v>
@@ -2757,19 +2757,19 @@
         <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>32</v>
@@ -2781,16 +2781,16 @@
         <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AJ12" t="n">
         <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="n">
         <v>55</v>
@@ -2814,7 +2814,7 @@
         <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AT12" t="n">
         <v>10.5</v>
@@ -2826,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AX12" t="n">
         <v>18.5</v>
@@ -2838,29 +2838,29 @@
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.8</v>
+        <v>30</v>
       </c>
       <c r="BD12" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H13" t="n">
         <v>3.25</v>
@@ -2903,13 +2903,13 @@
         <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="L13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="M13" t="n">
         <v>1.16</v>
@@ -2921,13 +2921,13 @@
         <v>1.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q13" t="n">
         <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S13" t="n">
         <v>6.4</v>
@@ -2942,10 +2942,10 @@
         <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X13" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="Y13" t="n">
         <v>8.800000000000001</v>
@@ -2954,19 +2954,19 @@
         <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB13" t="n">
         <v>7.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD13" t="n">
         <v>16.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
         <v>18</v>
@@ -2981,19 +2981,19 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK13" t="n">
         <v>55</v>
       </c>
       <c r="AL13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
         <v>85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>75</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3020,7 +3020,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3032,29 +3032,29 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD13" t="n">
         <v>60</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
         <v>60</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H14" t="n">
         <v>2.8</v>
       </c>
       <c r="I14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.2</v>
       </c>
-      <c r="J14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M14" t="n">
         <v>1.1</v>
@@ -3115,7 +3115,7 @@
         <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
         <v>2.16</v>
@@ -3136,119 +3136,119 @@
         <v>1.49</v>
       </c>
       <c r="W14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AB14" t="n">
         <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="AF14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
         <v>16</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AJ14" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AK14" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AL14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AO14" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AV14" t="n">
         <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.95</v>
+        <v>16</v>
       </c>
       <c r="AX14" t="n">
         <v>14</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.95</v>
+        <v>16</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>2.72</v>
       </c>
       <c r="G15" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="H15" t="n">
         <v>2.56</v>
       </c>
       <c r="I15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J15" t="n">
         <v>3.65</v>
@@ -3297,46 +3297,46 @@
         <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="R15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.54</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X15" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
         <v>23</v>
@@ -3345,19 +3345,19 @@
         <v>42</v>
       </c>
       <c r="AB15" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG15" t="n">
         <v>15</v>
@@ -3369,7 +3369,7 @@
         <v>36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
         <v>32</v>
@@ -3378,7 +3378,7 @@
         <v>38</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="n">
         <v>20</v>
@@ -3387,7 +3387,7 @@
         <v>17.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>12.5</v>
@@ -3396,7 +3396,7 @@
         <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AT15" t="n">
         <v>13</v>
@@ -3420,19 +3420,19 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF15" t="n">
         <v>14.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.02</v>
+        <v>2.92</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,13 +3497,13 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
         <v>1.19</v>
@@ -3515,16 +3515,16 @@
         <v>1.19</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U16" t="n">
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3563,7 +3563,7 @@
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K17" t="n">
         <v>5.6</v>
@@ -3697,10 +3697,10 @@
         <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
         <v>1.54</v>
@@ -3709,22 +3709,22 @@
         <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="X17" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3739,37 +3739,37 @@
         <v>12.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AJ17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK17" t="n">
         <v>16</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -3781,10 +3781,10 @@
         <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
@@ -3793,44 +3793,44 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
         <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB17" t="n">
         <v>11.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G18" t="n">
         <v>2.82</v>
@@ -3870,43 +3870,43 @@
         <v>2.82</v>
       </c>
       <c r="I18" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
         <v>1.53</v>
@@ -3924,19 +3924,19 @@
         <v>19.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>44</v>
+        <v>290</v>
       </c>
       <c r="AB18" t="n">
         <v>12.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD18" t="n">
         <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="n">
         <v>20</v>
@@ -3945,28 +3945,28 @@
         <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI18" t="n">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="AJ18" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="AK18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
         <v>48</v>
       </c>
       <c r="AM18" t="n">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AP18" t="n">
         <v>13</v>
@@ -3978,19 +3978,19 @@
         <v>17.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.6</v>
+        <v>26</v>
       </c>
       <c r="AX18" t="n">
         <v>15.5</v>
@@ -3999,22 +3999,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="BF18" t="n">
         <v>20</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
         <v>5.3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
         <v>4.6</v>
@@ -4085,43 +4085,43 @@
         <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
         <v>1.55</v>
       </c>
       <c r="R19" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
         <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z19" t="n">
         <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC19" t="n">
         <v>10.5</v>
@@ -4130,95 +4130,95 @@
         <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AJ19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK19" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM19" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO19" t="n">
         <v>48</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AR19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB19" t="n">
         <v>5.9</v>
       </c>
-      <c r="AS19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU19" t="n">
+      <c r="BC19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF19" t="n">
         <v>4.2</v>
       </c>
-      <c r="AV19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG19" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G20" t="n">
         <v>3.3</v>
@@ -4258,7 +4258,7 @@
         <v>2.46</v>
       </c>
       <c r="I20" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>3.2</v>
@@ -4309,10 +4309,10 @@
         <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AA20" t="n">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="AB20" t="n">
         <v>13.5</v>
@@ -4324,10 +4324,10 @@
         <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AG20" t="n">
         <v>15.5</v>
@@ -4336,25 +4336,25 @@
         <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
         <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO20" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
         <v>10</v>
@@ -4363,10 +4363,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
@@ -4378,41 +4378,41 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY20" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA20" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG20" t="n">
         <v>19.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I21" t="n">
         <v>3.3</v>
@@ -4458,37 +4458,37 @@
         <v>2.78</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L21" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M21" t="n">
         <v>1.14</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="O21" t="n">
         <v>1.58</v>
       </c>
       <c r="P21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
         <v>5.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U21" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="V21" t="n">
         <v>1.44</v>
@@ -4497,10 +4497,10 @@
         <v>1.5</v>
       </c>
       <c r="X21" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
         <v>21</v>
@@ -4509,7 +4509,7 @@
         <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC21" t="n">
         <v>7</v>
@@ -4518,7 +4518,7 @@
         <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF21" t="n">
         <v>18</v>
@@ -4530,28 +4530,28 @@
         <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ21" t="n">
         <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AL21" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM21" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO21" t="n">
         <v>75</v>
       </c>
       <c r="AP21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ21" t="n">
         <v>7.6</v>
@@ -4560,7 +4560,7 @@
         <v>16.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT21" t="n">
         <v>7</v>
@@ -4584,29 +4584,29 @@
         <v>19</v>
       </c>
       <c r="BA21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC21" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>8</v>
-      </c>
       <c r="BD21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>2.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="L22" t="n">
         <v>1.72</v>
@@ -4670,7 +4670,7 @@
         <v>1.37</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
         <v>1.12</v>
@@ -4679,16 +4679,16 @@
         <v>7.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U22" t="n">
         <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X22" t="n">
         <v>6.4</v>
@@ -4700,10 +4700,10 @@
         <v>20</v>
       </c>
       <c r="AA22" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC22" t="n">
         <v>7</v>
@@ -4712,7 +4712,7 @@
         <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
         <v>970</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>6</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU22" t="n">
         <v>6.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC22" t="n">
         <v>3.5</v>
       </c>
-      <c r="AX22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BA22" t="n">
+      <c r="BD22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF22" t="n">
         <v>3.6</v>
       </c>
-      <c r="BB22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BG22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="G23" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H23" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I23" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.21</v>
@@ -4855,146 +4855,146 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="Q23" t="n">
         <v>1.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="S23" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U23" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V23" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W23" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="X23" t="n">
         <v>90</v>
       </c>
       <c r="Y23" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="Z23" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA23" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AB23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG23" t="n">
         <v>970</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
         <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM23" t="n">
-        <v>65</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AO23" t="n">
         <v>55</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="AR23" t="n">
-        <v>38</v>
+        <v>7.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="AY23" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA23" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="G24" t="n">
         <v>4.4</v>
       </c>
       <c r="H24" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="I24" t="n">
         <v>1.97</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
         <v>1.24</v>
@@ -5052,7 +5052,7 @@
         <v>5.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
         <v>2.52</v>
@@ -5061,16 +5061,16 @@
         <v>1.55</v>
       </c>
       <c r="R24" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S24" t="n">
         <v>2.18</v>
       </c>
       <c r="T24" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U24" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V24" t="n">
         <v>2.02</v>
@@ -5082,58 +5082,58 @@
         <v>90</v>
       </c>
       <c r="Y24" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="Z24" t="n">
         <v>970</v>
       </c>
       <c r="AA24" t="n">
-        <v>25</v>
+        <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="AC24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE24" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AF24" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI24" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AJ24" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AK24" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AL24" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM24" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AO24" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
         <v>10.5</v>
@@ -5142,53 +5142,53 @@
         <v>11</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="AU24" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -5219,25 +5219,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.7</v>
       </c>
-      <c r="I25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
@@ -5246,143 +5246,143 @@
         <v>4.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
         <v>2.76</v>
       </c>
       <c r="T25" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U25" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR25" t="n">
         <v>24</v>
       </c>
-      <c r="Y25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>20</v>
-      </c>
       <c r="AS25" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV25" t="n">
         <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AX25" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.9</v>
+        <v>14</v>
       </c>
       <c r="BA25" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BB25" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BC25" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BD25" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG25" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -5437,25 +5437,25 @@
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.24</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R26" t="n">
         <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T26" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U26" t="n">
         <v>2.32</v>
@@ -5470,13 +5470,13 @@
         <v>23</v>
       </c>
       <c r="Y26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z26" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB26" t="n">
         <v>14</v>
@@ -5494,25 +5494,25 @@
         <v>18.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
         <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ26" t="n">
         <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL26" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
         <v>15</v>
@@ -5557,7 +5557,7 @@
         <v>28</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC26" t="n">
         <v>16.5</v>
@@ -5566,17 +5566,17 @@
         <v>23</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF26" t="n">
         <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -5610,19 +5610,19 @@
         <v>3.05</v>
       </c>
       <c r="G27" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H27" t="n">
         <v>2.38</v>
       </c>
       <c r="I27" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J27" t="n">
         <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L27" t="n">
         <v>1.44</v>
@@ -5631,13 +5631,13 @@
         <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
         <v>2.04</v>
@@ -5649,16 +5649,16 @@
         <v>3.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W27" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X27" t="n">
         <v>12.5</v>
@@ -5667,10 +5667,10 @@
         <v>9.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB27" t="n">
         <v>14.5</v>
@@ -5685,46 +5685,46 @@
         <v>30</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG27" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AH27" t="n">
         <v>20</v>
       </c>
       <c r="AI27" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AK27" t="n">
         <v>40</v>
       </c>
       <c r="AL27" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM27" t="n">
         <v>120</v>
       </c>
       <c r="AN27" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO27" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AP27" t="n">
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AT27" t="n">
         <v>10.5</v>
@@ -5736,7 +5736,7 @@
         <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="AX27" t="n">
         <v>18.5</v>
@@ -5748,29 +5748,29 @@
         <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BB27" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC27" t="n">
         <v>32</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF27" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG27" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="G28" t="n">
         <v>3.35</v>
@@ -5810,28 +5810,28 @@
         <v>2.64</v>
       </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K28" t="n">
         <v>3.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N28" t="n">
         <v>2.68</v>
       </c>
       <c r="O28" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P28" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q28" t="n">
         <v>2.6</v>
@@ -5846,79 +5846,79 @@
         <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V28" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W28" t="n">
         <v>1.44</v>
       </c>
       <c r="X28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC28" t="n">
         <v>7.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF28" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG28" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AH28" t="n">
         <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ28" t="n">
         <v>75</v>
       </c>
       <c r="AK28" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO28" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ28" t="n">
         <v>6.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AT28" t="n">
         <v>8.4</v>
@@ -5927,44 +5927,44 @@
         <v>6.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AX28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ28" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.4</v>
+        <v>44</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.4</v>
+        <v>48</v>
       </c>
       <c r="BC28" t="n">
         <v>36</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>1.5</v>
@@ -6007,13 +6007,13 @@
         <v>1.6</v>
       </c>
       <c r="J29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
@@ -6025,7 +6025,7 @@
         <v>1.26</v>
       </c>
       <c r="P29" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
         <v>1.77</v>
@@ -6034,7 +6034,7 @@
         <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="T29" t="n">
         <v>1.89</v>
@@ -6046,16 +6046,16 @@
         <v>2.66</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -6064,13 +6064,13 @@
         <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF29" t="n">
         <v>1000</v>
@@ -6100,65 +6100,65 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP29" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.68</v>
+        <v>4.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="AT29" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.98</v>
+        <v>6.8</v>
       </c>
       <c r="BA29" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE29" t="n">
         <v>3.25</v>
       </c>
-      <c r="BB29" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BF29" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G30" t="n">
         <v>2.48</v>
       </c>
       <c r="H30" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="I30" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="J30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K30" t="n">
         <v>4.5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4.6</v>
       </c>
       <c r="L30" t="n">
         <v>1.25</v>
@@ -6213,7 +6213,7 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O30" t="n">
         <v>1.15</v>
@@ -6222,10 +6222,10 @@
         <v>3.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R30" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S30" t="n">
         <v>2.14</v>
@@ -6234,10 +6234,10 @@
         <v>1.46</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V30" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W30" t="n">
         <v>1.67</v>
@@ -6255,19 +6255,19 @@
         <v>38</v>
       </c>
       <c r="AB30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC30" t="n">
         <v>11.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE30" t="n">
         <v>22</v>
       </c>
       <c r="AF30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG30" t="n">
         <v>13</v>
@@ -6294,22 +6294,22 @@
         <v>11</v>
       </c>
       <c r="AO30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR30" t="n">
         <v>21</v>
       </c>
       <c r="AS30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT30" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
         <v>10.5</v>
@@ -6321,7 +6321,7 @@
         <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY30" t="n">
         <v>12</v>
@@ -6333,10 +6333,10 @@
         <v>24</v>
       </c>
       <c r="BB30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC30" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD30" t="n">
         <v>23</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -6389,16 +6389,16 @@
         <v>4.1</v>
       </c>
       <c r="H31" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="I31" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="J31" t="n">
         <v>4.5</v>
       </c>
       <c r="K31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L31" t="n">
         <v>1.21</v>
@@ -6407,13 +6407,13 @@
         <v>1.02</v>
       </c>
       <c r="N31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P31" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q31" t="n">
         <v>1.35</v>
@@ -6428,10 +6428,10 @@
         <v>1.41</v>
       </c>
       <c r="U31" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V31" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="W31" t="n">
         <v>1.32</v>
@@ -6440,13 +6440,13 @@
         <v>42</v>
       </c>
       <c r="Y31" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA31" t="n">
         <v>23</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>24</v>
       </c>
       <c r="AB31" t="n">
         <v>34</v>
@@ -6455,28 +6455,28 @@
         <v>12.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>14.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AG31" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH31" t="n">
         <v>14.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="n">
         <v>75</v>
       </c>
       <c r="AK31" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL31" t="n">
         <v>32</v>
@@ -6485,7 +6485,7 @@
         <v>38</v>
       </c>
       <c r="AN31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO31" t="n">
         <v>5.5</v>
@@ -6497,10 +6497,10 @@
         <v>20</v>
       </c>
       <c r="AR31" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT31" t="n">
         <v>30</v>
@@ -6512,19 +6512,19 @@
         <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY31" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ31" t="n">
         <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BB31" t="n">
         <v>60</v>
@@ -6533,20 +6533,20 @@
         <v>30</v>
       </c>
       <c r="BD31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE31" t="n">
         <v>32</v>
       </c>
       <c r="BF31" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG31" t="n">
         <v>5.3</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -760,13 +760,13 @@
         <v>2.72</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -781,7 +781,7 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
@@ -796,10 +796,10 @@
         <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
         <v>2.08</v>
@@ -808,13 +808,13 @@
         <v>1.52</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
         <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
         <v>19</v>
@@ -865,62 +865,62 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AS2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW2" t="n">
         <v>6</v>
       </c>
-      <c r="AT2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="AX2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG2" t="n">
         <v>5.7</v>
       </c>
-      <c r="AX2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>1.53</v>
       </c>
       <c r="I3" t="n">
-        <v>660</v>
+        <v>55</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
@@ -969,13 +969,13 @@
         <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
@@ -984,13 +984,13 @@
         <v>1.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="R3" t="n">
         <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="T3" t="n">
         <v>1.05</v>
@@ -999,7 +999,7 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
         <v>1.19</v>
@@ -1059,7 +1059,7 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.07</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1184,16 +1184,16 @@
         <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T4" t="n">
         <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W4" t="n">
         <v>1.32</v>
@@ -1256,13 +1256,13 @@
         <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT4" t="n">
         <v>4.1</v>
@@ -1271,44 +1271,44 @@
         <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AW4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX4" t="n">
         <v>5.1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5</v>
       </c>
       <c r="AY4" t="n">
         <v>4.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB4" t="n">
         <v>5.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG4" t="n">
         <v>5.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -1366,13 +1366,13 @@
         <v>2.72</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
         <v>1.23</v>
@@ -1381,13 +1381,13 @@
         <v>3.65</v>
       </c>
       <c r="T5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
         <v>1.64</v>
@@ -1450,13 +1450,13 @@
         <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AR5" t="n">
         <v>5.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
         <v>4</v>
@@ -1465,16 +1465,16 @@
         <v>3.95</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AZ5" t="n">
         <v>5.4</v>
@@ -1486,7 +1486,7 @@
         <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD5" t="n">
         <v>6.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G6" t="n">
         <v>1.5</v>
@@ -1566,7 +1566,7 @@
         <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
         <v>1.37</v>
@@ -1644,7 +1644,7 @@
         <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
         <v>9.800000000000001</v>
@@ -1653,19 +1653,19 @@
         <v>10.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU6" t="n">
         <v>5.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW6" t="n">
         <v>10</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY6" t="n">
         <v>5.4</v>
@@ -1680,7 +1680,7 @@
         <v>5.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD6" t="n">
         <v>8.800000000000001</v>
@@ -1692,11 +1692,11 @@
         <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -1727,100 +1727,100 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="J7" t="n">
-        <v>2.64</v>
+        <v>2.96</v>
       </c>
       <c r="K7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC7" t="n">
         <v>7.6</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>95</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.47</v>
+        <v>5.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.53</v>
+        <v>7.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.46</v>
+        <v>6.2</v>
       </c>
       <c r="AU7" t="n">
         <v>4.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.47</v>
+        <v>5.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.52</v>
+        <v>7.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.52</v>
+        <v>6.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.51</v>
+        <v>6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.52</v>
+        <v>6.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.54</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.54</v>
+        <v>8.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.54</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.54</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.54</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.55</v>
+        <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -1921,82 +1921,82 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="I8" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="K8" t="n">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>2.08</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>11</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AF8" t="n">
         <v>1000</v>
@@ -2005,10 +2005,10 @@
         <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
         <v>1000</v>
@@ -2026,65 +2026,65 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>29</v>
+        <v>5.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.73</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.67</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.2</v>
+        <v>30</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.67</v>
+        <v>11.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.67</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.74</v>
+        <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.2</v>
+        <v>34</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.84</v>
+        <v>7.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.83</v>
+        <v>30</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.82</v>
+        <v>4.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
         <v>2.16</v>
@@ -2157,7 +2157,7 @@
         <v>2.86</v>
       </c>
       <c r="T9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U9" t="n">
         <v>2.4</v>
@@ -2166,7 +2166,7 @@
         <v>1.75</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
         <v>90</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.38</v>
@@ -2342,7 +2342,7 @@
         <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
         <v>1.29</v>
@@ -2357,10 +2357,10 @@
         <v>1.91</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
         <v>22</v>
@@ -2426,7 +2426,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
         <v>7.8</v>
@@ -2453,7 +2453,7 @@
         <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC10" t="n">
         <v>4.6</v>
@@ -2468,11 +2468,11 @@
         <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>1.83</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="I11" t="n">
         <v>6.4</v>
@@ -2584,7 +2584,7 @@
         <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB11" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G12" t="n">
         <v>3.2</v>
@@ -2706,7 +2706,7 @@
         <v>2.44</v>
       </c>
       <c r="I12" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
@@ -2727,7 +2727,7 @@
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q12" t="n">
         <v>1.96</v>
@@ -2745,7 +2745,7 @@
         <v>2.12</v>
       </c>
       <c r="V12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W12" t="n">
         <v>1.45</v>
@@ -2787,7 +2787,7 @@
         <v>85</v>
       </c>
       <c r="AJ12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK12" t="n">
         <v>80</v>
@@ -2799,7 +2799,7 @@
         <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO12" t="n">
         <v>22</v>
@@ -2826,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX12" t="n">
         <v>18.5</v>
@@ -2838,29 +2838,29 @@
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BC12" t="n">
         <v>30</v>
       </c>
       <c r="BD12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF12" t="n">
         <v>6.8</v>
       </c>
-      <c r="BE12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG12" t="n">
-        <v>5.6</v>
+        <v>19.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
         <v>2.7</v>
       </c>
       <c r="K13" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="L13" t="n">
         <v>1.63</v>
@@ -2915,7 +2915,7 @@
         <v>1.16</v>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
         <v>1.7</v>
@@ -2969,7 +2969,7 @@
         <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG13" t="n">
         <v>15</v>
@@ -2999,7 +2999,7 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>7.2</v>
@@ -3008,7 +3008,7 @@
         <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3020,7 +3020,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3032,29 +3032,29 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB13" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BC13" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BD13" t="n">
         <v>60</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG13" t="n">
         <v>60</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
         <v>2.8</v>
@@ -3097,7 +3097,7 @@
         <v>3.05</v>
       </c>
       <c r="J14" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K14" t="n">
         <v>3.2</v>
@@ -3166,7 +3166,7 @@
         <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
         <v>19</v>
@@ -3202,7 +3202,7 @@
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
@@ -3226,19 +3226,19 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
         <v>16</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF14" t="n">
         <v>6.8</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>2.84</v>
       </c>
       <c r="H15" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I15" t="n">
         <v>2.74</v>
@@ -3294,19 +3294,19 @@
         <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>2.24</v>
       </c>
       <c r="O15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
         <v>2.24</v>
@@ -3342,7 +3342,7 @@
         <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AB15" t="n">
         <v>15.5</v>
@@ -3369,7 +3369,7 @@
         <v>36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK15" t="n">
         <v>32</v>
@@ -3387,7 +3387,7 @@
         <v>17.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AQ15" t="n">
         <v>12.5</v>
@@ -3423,7 +3423,7 @@
         <v>16</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC15" t="n">
         <v>13</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.45</v>
       </c>
       <c r="G16" t="n">
-        <v>4.8</v>
+        <v>2.36</v>
       </c>
       <c r="H16" t="n">
         <v>2.92</v>
@@ -3596,7 +3596,7 @@
         <v>1.71</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.67</v>
+        <v>5.8</v>
       </c>
       <c r="AV16" t="n">
         <v>1.81</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -3673,10 +3673,10 @@
         <v>1.5</v>
       </c>
       <c r="H17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17" t="n">
         <v>4.8</v>
@@ -3703,7 +3703,7 @@
         <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
         <v>2.5</v>
@@ -3778,13 +3778,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
@@ -3796,7 +3796,7 @@
         <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="AX17" t="n">
         <v>8.800000000000001</v>
@@ -3808,7 +3808,7 @@
         <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB17" t="n">
         <v>11.5</v>
@@ -3820,7 +3820,7 @@
         <v>14.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
         <v>5.1</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G18" t="n">
         <v>2.82</v>
@@ -3870,7 +3870,7 @@
         <v>2.82</v>
       </c>
       <c r="I18" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>3.35</v>
@@ -3990,10 +3990,10 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AY18" t="n">
         <v>10.5</v>
@@ -4005,7 +4005,7 @@
         <v>10.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC18" t="n">
         <v>14.5</v>
@@ -4017,14 +4017,14 @@
         <v>24</v>
       </c>
       <c r="BF18" t="n">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>1.83</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
         <v>5.3</v>
@@ -4118,7 +4118,7 @@
         <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
         <v>13.5</v>
@@ -4154,7 +4154,7 @@
         <v>30</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
         <v>8.6</v>
@@ -4169,7 +4169,7 @@
         <v>6</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS19" t="n">
         <v>7.4</v>
@@ -4178,7 +4178,7 @@
         <v>5.1</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AV19" t="n">
         <v>5.8</v>
@@ -4187,38 +4187,38 @@
         <v>7</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY19" t="n">
         <v>4.7</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB19" t="n">
         <v>5.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE19" t="n">
         <v>7.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG19" t="n">
         <v>6.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>2.94</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H20" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J20" t="n">
         <v>3.2</v>
@@ -4300,7 +4300,7 @@
         <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X20" t="n">
         <v>15</v>
@@ -4315,13 +4315,13 @@
         <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
         <v>75</v>
@@ -4330,7 +4330,7 @@
         <v>55</v>
       </c>
       <c r="AG20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
         <v>21</v>
@@ -4342,10 +4342,10 @@
         <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AL20" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -4387,22 +4387,22 @@
         <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF20" t="n">
         <v>6.6</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
         <v>2.46</v>
       </c>
       <c r="O21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P21" t="n">
         <v>1.47</v>
@@ -4500,7 +4500,7 @@
         <v>8</v>
       </c>
       <c r="Y21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z21" t="n">
         <v>21</v>
@@ -4542,13 +4542,13 @@
         <v>170</v>
       </c>
       <c r="AM21" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO21" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
         <v>6.8</v>
@@ -4560,7 +4560,7 @@
         <v>16.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT21" t="n">
         <v>7</v>
@@ -4578,35 +4578,35 @@
         <v>14.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
         <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC21" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BD21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
         <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="K22" t="n">
         <v>2.8</v>
@@ -4679,7 +4679,7 @@
         <v>7.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
         <v>1.61</v>
@@ -4688,7 +4688,7 @@
         <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X22" t="n">
         <v>6.4</v>
@@ -4745,7 +4745,7 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ22" t="n">
         <v>6</v>
@@ -4766,7 +4766,7 @@
         <v>7.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX22" t="n">
         <v>7.8</v>
@@ -4775,32 +4775,32 @@
         <v>7.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
         <v>12</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BD22" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="BE22" t="n">
         <v>13</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BG22" t="n">
         <v>11</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -4831,25 +4831,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G23" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J23" t="n">
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
@@ -4882,13 +4882,13 @@
         <v>1.18</v>
       </c>
       <c r="W23" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X23" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y23" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
         <v>500</v>
@@ -4912,7 +4912,7 @@
         <v>12.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
         <v>21</v>
@@ -4939,16 +4939,16 @@
         <v>55</v>
       </c>
       <c r="AP23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS23" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>7.8</v>
       </c>
       <c r="AT23" t="n">
         <v>11.5</v>
@@ -4957,44 +4957,44 @@
         <v>11.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AY23" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BA23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE23" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>7.4</v>
       </c>
       <c r="BF23" t="n">
         <v>4.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="I24" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.24</v>
@@ -5049,79 +5049,79 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R24" t="n">
         <v>1.61</v>
       </c>
       <c r="S24" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="T24" t="n">
         <v>1.56</v>
       </c>
       <c r="U24" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V24" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X24" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="Y24" t="n">
         <v>30</v>
       </c>
       <c r="Z24" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>900</v>
+        <v>24</v>
       </c>
       <c r="AB24" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AC24" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AF24" t="n">
         <v>500</v>
       </c>
       <c r="AG24" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AH24" t="n">
         <v>60</v>
       </c>
       <c r="AI24" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AJ24" t="n">
         <v>500</v>
       </c>
       <c r="AK24" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AL24" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM24" t="n">
         <v>580</v>
@@ -5130,65 +5130,65 @@
         <v>500</v>
       </c>
       <c r="AO24" t="n">
-        <v>55</v>
+        <v>9.4</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS24" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT24" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AV24" t="n">
         <v>5.8</v>
       </c>
       <c r="AW24" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AX24" t="n">
         <v>8.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AZ24" t="n">
         <v>7.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BG24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G25" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="H25" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I25" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5243,76 +5243,76 @@
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>1.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="T25" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U25" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W25" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="X25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z25" t="n">
         <v>30</v>
       </c>
       <c r="AA25" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB25" t="n">
         <v>12</v>
       </c>
       <c r="AC25" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AK25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="n">
         <v>34</v>
@@ -5321,68 +5321,68 @@
         <v>75</v>
       </c>
       <c r="AN25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO25" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP25" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>15</v>
       </c>
       <c r="AR25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AT25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AX25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BA25" t="n">
         <v>20</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC25" t="n">
         <v>19</v>
       </c>
       <c r="BD25" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BF25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG25" t="n">
         <v>29</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G26" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H26" t="n">
         <v>3.35</v>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J26" t="n">
         <v>3.55</v>
@@ -5461,7 +5461,7 @@
         <v>2.32</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W26" t="n">
         <v>1.74</v>
@@ -5479,7 +5479,7 @@
         <v>130</v>
       </c>
       <c r="AB26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC26" t="n">
         <v>10.5</v>
@@ -5488,34 +5488,34 @@
         <v>17</v>
       </c>
       <c r="AE26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF26" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI26" t="n">
         <v>95</v>
       </c>
       <c r="AJ26" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM26" t="n">
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO26" t="n">
         <v>32</v>
@@ -5566,17 +5566,17 @@
         <v>23</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF26" t="n">
         <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
         <v>500</v>
       </c>
       <c r="AK27" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL27" t="n">
         <v>500</v>
@@ -5757,7 +5757,7 @@
         <v>32</v>
       </c>
       <c r="BD27" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BE27" t="n">
         <v>10.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G28" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H28" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I28" t="n">
         <v>2.82</v>
       </c>
       <c r="J28" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L28" t="n">
         <v>1.57</v>
@@ -5843,7 +5843,7 @@
         <v>5.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U28" t="n">
         <v>1.83</v>
@@ -5918,7 +5918,7 @@
         <v>13.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT28" t="n">
         <v>8.4</v>
@@ -5933,7 +5933,7 @@
         <v>16</v>
       </c>
       <c r="AX28" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AY28" t="n">
         <v>13</v>
@@ -5954,7 +5954,7 @@
         <v>9.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF28" t="n">
         <v>9.199999999999999</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -5995,67 +5995,67 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="G29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K29" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U29" t="n">
         <v>1.91</v>
       </c>
       <c r="V29" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
         <v>15</v>
       </c>
       <c r="Z29" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -6100,40 +6100,40 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>29</v>
+        <v>7.2</v>
       </c>
       <c r="AP29" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AW29" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY29" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="BA29" t="n">
         <v>18</v>
@@ -6148,17 +6148,17 @@
         <v>4.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BF29" t="n">
         <v>4.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G30" t="n">
         <v>2.48</v>
@@ -6219,10 +6219,10 @@
         <v>1.15</v>
       </c>
       <c r="P30" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R30" t="n">
         <v>1.86</v>
@@ -6249,13 +6249,13 @@
         <v>21</v>
       </c>
       <c r="Z30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA30" t="n">
         <v>38</v>
       </c>
       <c r="AB30" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC30" t="n">
         <v>11.5</v>
@@ -6264,7 +6264,7 @@
         <v>13.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF30" t="n">
         <v>21</v>
@@ -6291,10 +6291,10 @@
         <v>46</v>
       </c>
       <c r="AN30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP30" t="n">
         <v>30</v>
@@ -6309,7 +6309,7 @@
         <v>34</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>10.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -6389,16 +6389,16 @@
         <v>4.1</v>
       </c>
       <c r="H31" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I31" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="J31" t="n">
         <v>4.5</v>
       </c>
       <c r="K31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L31" t="n">
         <v>1.21</v>
@@ -6413,13 +6413,13 @@
         <v>1.11</v>
       </c>
       <c r="P31" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q31" t="n">
         <v>1.35</v>
       </c>
       <c r="R31" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S31" t="n">
         <v>1.88</v>
@@ -6428,10 +6428,10 @@
         <v>1.41</v>
       </c>
       <c r="U31" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="V31" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="W31" t="n">
         <v>1.32</v>
@@ -6443,7 +6443,7 @@
         <v>21</v>
       </c>
       <c r="Z31" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA31" t="n">
         <v>23</v>
@@ -6452,28 +6452,28 @@
         <v>34</v>
       </c>
       <c r="AC31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD31" t="n">
         <v>12</v>
       </c>
       <c r="AE31" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AF31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH31" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI31" t="n">
         <v>21</v>
       </c>
       <c r="AJ31" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK31" t="n">
         <v>36</v>
@@ -6482,13 +6482,13 @@
         <v>32</v>
       </c>
       <c r="AM31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN31" t="n">
         <v>19</v>
       </c>
       <c r="AO31" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AP31" t="n">
         <v>38</v>
@@ -6497,7 +6497,7 @@
         <v>20</v>
       </c>
       <c r="AR31" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS31" t="n">
         <v>22</v>
@@ -6506,31 +6506,31 @@
         <v>30</v>
       </c>
       <c r="AU31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AY31" t="n">
         <v>17.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA31" t="n">
         <v>19.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BC31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD31" t="n">
         <v>30</v>
@@ -6542,11 +6542,11 @@
         <v>17.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -763,43 +763,43 @@
         <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="U2" t="n">
         <v>2.08</v>
@@ -814,7 +814,7 @@
         <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>990</v>
       </c>
       <c r="Z2" t="n">
         <v>19</v>
@@ -826,7 +826,7 @@
         <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
@@ -847,7 +847,7 @@
         <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
         <v>36</v>
@@ -865,62 +865,62 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU2" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AV2" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="H3" t="n">
-        <v>1.53</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
@@ -969,28 +969,28 @@
         <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="T3" t="n">
         <v>1.05</v>
@@ -1002,7 +1002,7 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1062,59 +1062,59 @@
         <v>1.04</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BE3" t="n">
         <v>1.07</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -1145,43 +1145,43 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
         <v>1.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
         <v>3.9</v>
@@ -1193,16 +1193,16 @@
         <v>1.86</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W4" t="n">
         <v>1.32</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1256,28 +1256,28 @@
         <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS4" t="n">
         <v>5.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AU4" t="n">
         <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
         <v>5.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="n">
         <v>4.6</v>
@@ -1286,13 +1286,13 @@
         <v>4.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB4" t="n">
         <v>5.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD4" t="n">
         <v>5.7</v>
@@ -1304,11 +1304,11 @@
         <v>5.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -1366,7 +1366,7 @@
         <v>2.72</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
@@ -1384,10 +1384,10 @@
         <v>1.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
         <v>1.64</v>
@@ -1423,7 +1423,7 @@
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>75</v>
@@ -1444,19 +1444,19 @@
         <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
         <v>4</v>
@@ -1465,44 +1465,44 @@
         <v>3.95</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
         <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ5" t="n">
         <v>5.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
         <v>6.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG5" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.42</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
@@ -1545,7 +1545,7 @@
         <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
         <v>5.2</v>
@@ -1569,7 +1569,7 @@
         <v>1.86</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
         <v>2.96</v>
@@ -1581,7 +1581,7 @@
         <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
         <v>3</v>
@@ -1590,7 +1590,7 @@
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1644,59 +1644,59 @@
         <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU6" t="n">
         <v>5.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
         <v>7.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
         <v>1.5</v>
@@ -1760,7 +1760,7 @@
         <v>1.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
         <v>1.2</v>
@@ -1769,7 +1769,7 @@
         <v>3.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
         <v>1.8</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -1945,28 +1945,28 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
         <v>3.65</v>
@@ -1975,10 +1975,10 @@
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z8" t="n">
         <v>8.800000000000001</v>
@@ -1987,10 +1987,10 @@
         <v>11</v>
       </c>
       <c r="AB8" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
         <v>11.5</v>
@@ -2053,38 +2053,38 @@
         <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
         <v>34</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BA8" t="n">
         <v>30</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -2133,34 +2133,34 @@
         <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="T9" t="n">
         <v>1.62</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V9" t="n">
         <v>1.75</v>
@@ -2172,43 +2172,43 @@
         <v>90</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB9" t="n">
         <v>16.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE9" t="n">
         <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
         <v>70</v>
       </c>
       <c r="AK9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
         <v>50</v>
@@ -2217,68 +2217,68 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
         <v>17.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AT9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.5</v>
+        <v>42</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BD9" t="n">
         <v>34</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>2.54</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H10" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>3.4</v>
@@ -2342,13 +2342,13 @@
         <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
         <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
         <v>1.65</v>
@@ -2363,19 +2363,19 @@
         <v>1.56</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
         <v>9</v>
@@ -2384,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
@@ -2393,13 +2393,13 @@
         <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -2414,7 +2414,7 @@
         <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
         <v>9.4</v>
@@ -2423,56 +2423,56 @@
         <v>8.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="AZ10" t="n">
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -2503,67 +2503,67 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="G11" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.31</v>
       </c>
       <c r="P11" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2</v>
+        <v>2.84</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
         <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2572,7 +2572,7 @@
         <v>16.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2581,11 +2581,11 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG11" t="n">
         <v>21</v>
       </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
       <c r="AH11" t="n">
         <v>1000</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>180</v>
       </c>
       <c r="AK11" t="n">
         <v>65</v>
@@ -2605,68 +2605,68 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>85</v>
+        <v>8.6</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="AW11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX11" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX11" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AY11" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF11" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG11" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G12" t="n">
         <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
@@ -2715,7 +2715,7 @@
         <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -2727,10 +2727,10 @@
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R12" t="n">
         <v>1.35</v>
@@ -2739,13 +2739,13 @@
         <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U12" t="n">
         <v>2.12</v>
       </c>
       <c r="V12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W12" t="n">
         <v>1.45</v>
@@ -2826,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AX12" t="n">
         <v>18.5</v>
@@ -2853,14 +2853,14 @@
         <v>30</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG12" t="n">
         <v>19.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G13" t="n">
         <v>3.05</v>
@@ -2903,13 +2903,13 @@
         <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="K13" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="M13" t="n">
         <v>1.16</v>
@@ -2918,19 +2918,19 @@
         <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="P13" t="n">
         <v>1.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>1.14</v>
       </c>
       <c r="S13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T13" t="n">
         <v>2.24</v>
@@ -2942,10 +2942,10 @@
         <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y13" t="n">
         <v>8.800000000000001</v>
@@ -2954,7 +2954,7 @@
         <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>7.8</v>
@@ -2978,10 +2978,10 @@
         <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ13" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK13" t="n">
         <v>55</v>
@@ -2993,13 +2993,13 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AQ13" t="n">
         <v>7.2</v>
@@ -3008,7 +3008,7 @@
         <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3020,10 +3020,10 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="AX13" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="n">
         <v>11.5</v>
@@ -3032,10 +3032,10 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC13" t="n">
         <v>15</v>
@@ -3044,7 +3044,7 @@
         <v>60</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
         <v>9.199999999999999</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -3085,100 +3085,100 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="G14" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="I14" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="J14" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.38</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
         <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.05</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>220</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3187,68 +3187,68 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>8</v>
+        <v>1.62</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.61</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>1.67</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>1.72</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>1.63</v>
       </c>
       <c r="AW14" t="n">
-        <v>16</v>
+        <v>1.71</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>1.68</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>1.63</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>1.66</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>1.72</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>1.72</v>
       </c>
       <c r="BC14" t="n">
-        <v>16</v>
+        <v>1.71</v>
       </c>
       <c r="BD14" t="n">
-        <v>6</v>
+        <v>1.72</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.4</v>
+        <v>1.74</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.8</v>
+        <v>1.71</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.8</v>
+        <v>1.71</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
@@ -3315,13 +3315,13 @@
         <v>1.66</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="T15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U15" t="n">
         <v>2.38</v>
@@ -3432,7 +3432,7 @@
         <v>16</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF15" t="n">
         <v>14.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -3497,13 +3497,13 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
         <v>1.19</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="H17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I17" t="n">
         <v>8.800000000000001</v>
@@ -3715,10 +3715,10 @@
         <v>2.02</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="X17" t="n">
         <v>42</v>
@@ -3748,13 +3748,13 @@
         <v>10.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH17" t="n">
         <v>36</v>
       </c>
       <c r="AI17" t="n">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
         <v>13.5</v>
@@ -3769,7 +3769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -3778,13 +3778,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AR17" t="n">
         <v>48</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
@@ -3793,7 +3793,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW17" t="n">
         <v>70</v>
@@ -3808,29 +3808,29 @@
         <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC17" t="n">
         <v>12.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
         <v>5.1</v>
       </c>
       <c r="BG17" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -3891,13 +3891,13 @@
         <v>1.31</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
         <v>1.94</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
         <v>3.4</v>
@@ -3909,7 +3909,7 @@
         <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
         <v>1.54</v>
@@ -3930,7 +3930,7 @@
         <v>12.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
         <v>12.5</v>
@@ -3978,7 +3978,7 @@
         <v>17.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
         <v>9.800000000000001</v>
@@ -4002,10 +4002,10 @@
         <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC18" t="n">
         <v>14.5</v>
@@ -4017,14 +4017,14 @@
         <v>24</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>1.83</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
         <v>3.75</v>
@@ -4151,10 +4151,10 @@
         <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM19" t="n">
-        <v>580</v>
+        <v>75</v>
       </c>
       <c r="AN19" t="n">
         <v>8.6</v>
@@ -4169,7 +4169,7 @@
         <v>6</v>
       </c>
       <c r="AR19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS19" t="n">
         <v>7.4</v>
@@ -4178,7 +4178,7 @@
         <v>5.1</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV19" t="n">
         <v>5.8</v>
@@ -4211,14 +4211,14 @@
         <v>7.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG19" t="n">
         <v>6.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G20" t="n">
         <v>3.4</v>
       </c>
       <c r="H20" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="I20" t="n">
         <v>2.68</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
         <v>3.7</v>
@@ -4273,13 +4273,13 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.35</v>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q20" t="n">
         <v>2</v>
@@ -4300,13 +4300,13 @@
         <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z20" t="n">
         <v>29</v>
@@ -4318,7 +4318,7 @@
         <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD20" t="n">
         <v>12.5</v>
@@ -4330,13 +4330,13 @@
         <v>55</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AJ20" t="n">
         <v>1000</v>
@@ -4351,10 +4351,10 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP20" t="n">
         <v>10</v>
@@ -4387,32 +4387,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG20" t="n">
         <v>19.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -4455,13 +4455,13 @@
         <v>3.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K21" t="n">
         <v>2.96</v>
       </c>
       <c r="L21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M21" t="n">
         <v>1.14</v>
@@ -4470,13 +4470,13 @@
         <v>2.46</v>
       </c>
       <c r="O21" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="P21" t="n">
         <v>1.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R21" t="n">
         <v>1.16</v>
@@ -4500,7 +4500,7 @@
         <v>8</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z21" t="n">
         <v>21</v>
@@ -4515,7 +4515,7 @@
         <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>55</v>
@@ -4536,7 +4536,7 @@
         <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AL21" t="n">
         <v>170</v>
@@ -4560,7 +4560,7 @@
         <v>16.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT21" t="n">
         <v>7</v>
@@ -4584,29 +4584,29 @@
         <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BC21" t="n">
         <v>34</v>
       </c>
       <c r="BD21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE21" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>10</v>
       </c>
       <c r="BF21" t="n">
         <v>42</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G22" t="n">
         <v>3.35</v>
@@ -4649,7 +4649,7 @@
         <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K22" t="n">
         <v>2.8</v>
@@ -4664,10 +4664,10 @@
         <v>2.22</v>
       </c>
       <c r="O22" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="P22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q22" t="n">
         <v>3.5</v>
@@ -4676,22 +4676,22 @@
         <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
         <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V22" t="n">
         <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X22" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="Y22" t="n">
         <v>7.4</v>
@@ -4745,16 +4745,16 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ22" t="n">
         <v>6</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS22" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT22" t="n">
         <v>4.9</v>
@@ -4766,41 +4766,41 @@
         <v>7.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX22" t="n">
         <v>7.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.7</v>
+        <v>2.76</v>
       </c>
       <c r="BA22" t="n">
         <v>12</v>
       </c>
       <c r="BB22" t="n">
-        <v>3.9</v>
+        <v>2.54</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="BD22" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE22" t="n">
         <v>13</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.85</v>
+        <v>2.22</v>
       </c>
       <c r="BG22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G23" t="n">
         <v>1.6</v>
       </c>
       <c r="H23" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I23" t="n">
         <v>6.8</v>
@@ -4846,7 +4846,7 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.25</v>
@@ -4879,7 +4879,7 @@
         <v>2.38</v>
       </c>
       <c r="V23" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W23" t="n">
         <v>2.66</v>
@@ -4939,37 +4939,37 @@
         <v>55</v>
       </c>
       <c r="AP23" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="AR23" t="n">
         <v>7</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT23" t="n">
         <v>11.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="AV23" t="n">
         <v>6</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AY23" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BA23" t="n">
         <v>7</v>
@@ -4978,23 +4978,23 @@
         <v>5.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>4.6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
@@ -5076,7 +5076,7 @@
         <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
         <v>24</v>
@@ -5091,10 +5091,10 @@
         <v>24</v>
       </c>
       <c r="AB24" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
         <v>14.5</v>
@@ -5103,13 +5103,13 @@
         <v>18</v>
       </c>
       <c r="AF24" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AG24" t="n">
         <v>18.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
         <v>28</v>
@@ -5118,10 +5118,10 @@
         <v>500</v>
       </c>
       <c r="AK24" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AL24" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AM24" t="n">
         <v>580</v>
@@ -5142,7 +5142,7 @@
         <v>12</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT24" t="n">
         <v>18.5</v>
@@ -5154,10 +5154,10 @@
         <v>5.8</v>
       </c>
       <c r="AW24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY24" t="n">
         <v>14.5</v>
@@ -5169,26 +5169,26 @@
         <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC24" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BD24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF24" t="n">
         <v>22</v>
       </c>
       <c r="BG24" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G25" t="n">
         <v>2.2</v>
@@ -5228,10 +5228,10 @@
         <v>3.8</v>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
         <v>3.8</v>
@@ -5255,7 +5255,7 @@
         <v>1.76</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
         <v>2.82</v>
@@ -5273,16 +5273,16 @@
         <v>1.83</v>
       </c>
       <c r="X25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y25" t="n">
         <v>18</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>18.5</v>
       </c>
       <c r="Z25" t="n">
         <v>30</v>
       </c>
       <c r="AA25" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AB25" t="n">
         <v>12</v>
@@ -5318,7 +5318,7 @@
         <v>34</v>
       </c>
       <c r="AM25" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AN25" t="n">
         <v>14</v>
@@ -5330,7 +5330,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR25" t="n">
         <v>25</v>
@@ -5378,11 +5378,11 @@
         <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
         <v>2.34</v>
@@ -5422,13 +5422,13 @@
         <v>3.35</v>
       </c>
       <c r="I26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
         <v>1.28</v>
@@ -5437,28 +5437,28 @@
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.24</v>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
         <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V26" t="n">
         <v>1.39</v>
@@ -5467,10 +5467,10 @@
         <v>1.74</v>
       </c>
       <c r="X26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z26" t="n">
         <v>27</v>
@@ -5488,16 +5488,16 @@
         <v>17</v>
       </c>
       <c r="AE26" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AF26" t="n">
         <v>17</v>
       </c>
       <c r="AG26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
         <v>95</v>
@@ -5509,16 +5509,16 @@
         <v>23</v>
       </c>
       <c r="AL26" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AM26" t="n">
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO26" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP26" t="n">
         <v>13.5</v>
@@ -5566,17 +5566,17 @@
         <v>23</v>
       </c>
       <c r="BE26" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF26" t="n">
         <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -5610,10 +5610,10 @@
         <v>3.05</v>
       </c>
       <c r="G27" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H27" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="I27" t="n">
         <v>2.58</v>
@@ -5622,7 +5622,7 @@
         <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L27" t="n">
         <v>1.44</v>
@@ -5640,13 +5640,13 @@
         <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R27" t="n">
         <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
         <v>1.81</v>
@@ -5658,13 +5658,13 @@
         <v>1.63</v>
       </c>
       <c r="W27" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X27" t="n">
         <v>12.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z27" t="n">
         <v>16</v>
@@ -5673,7 +5673,7 @@
         <v>38</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC27" t="n">
         <v>7.8</v>
@@ -5685,25 +5685,25 @@
         <v>30</v>
       </c>
       <c r="AF27" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AJ27" t="n">
         <v>500</v>
       </c>
       <c r="AK27" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL27" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM27" t="n">
         <v>120</v>
@@ -5712,25 +5712,25 @@
         <v>50</v>
       </c>
       <c r="AO27" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AP27" t="n">
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS27" t="n">
         <v>18</v>
       </c>
       <c r="AT27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV27" t="n">
         <v>10.5</v>
@@ -5742,35 +5742,35 @@
         <v>18.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AZ27" t="n">
         <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BB27" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC27" t="n">
         <v>32</v>
       </c>
       <c r="BD27" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF27" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BG27" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>3.3</v>
       </c>
       <c r="H28" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I28" t="n">
         <v>2.82</v>
@@ -5825,7 +5825,7 @@
         <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O28" t="n">
         <v>1.53</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
         <v>1.91</v>
       </c>
       <c r="V29" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="W29" t="n">
         <v>1.13</v>
@@ -6100,7 +6100,7 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="AP29" t="n">
         <v>8.4</v>
@@ -6112,7 +6112,7 @@
         <v>4.9</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="AT29" t="n">
         <v>7.4</v>
@@ -6124,7 +6124,7 @@
         <v>5.2</v>
       </c>
       <c r="AW29" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="AX29" t="n">
         <v>9.199999999999999</v>
@@ -6148,7 +6148,7 @@
         <v>4.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="BF29" t="n">
         <v>4.2</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         <v>2.48</v>
       </c>
       <c r="H30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.7</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.72</v>
       </c>
       <c r="J30" t="n">
         <v>4.4</v>
@@ -6225,7 +6225,7 @@
         <v>1.47</v>
       </c>
       <c r="R30" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S30" t="n">
         <v>2.14</v>
@@ -6240,7 +6240,7 @@
         <v>1.58</v>
       </c>
       <c r="W30" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X30" t="n">
         <v>34</v>
@@ -6270,7 +6270,7 @@
         <v>21</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
         <v>14</v>
@@ -6291,7 +6291,7 @@
         <v>46</v>
       </c>
       <c r="AN30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO30" t="n">
         <v>11.5</v>
@@ -6303,7 +6303,7 @@
         <v>20</v>
       </c>
       <c r="AR30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS30" t="n">
         <v>34</v>
@@ -6318,7 +6318,7 @@
         <v>12.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX30" t="n">
         <v>20</v>
@@ -6336,7 +6336,7 @@
         <v>32</v>
       </c>
       <c r="BC30" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD30" t="n">
         <v>23</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -6389,16 +6389,16 @@
         <v>4.1</v>
       </c>
       <c r="H31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I31" t="n">
         <v>1.86</v>
       </c>
-      <c r="I31" t="n">
-        <v>1.87</v>
-      </c>
       <c r="J31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L31" t="n">
         <v>1.21</v>
@@ -6416,7 +6416,7 @@
         <v>3.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R31" t="n">
         <v>2.1</v>
@@ -6431,13 +6431,13 @@
         <v>3.35</v>
       </c>
       <c r="V31" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W31" t="n">
         <v>1.32</v>
       </c>
       <c r="X31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y31" t="n">
         <v>21</v>
@@ -6452,7 +6452,7 @@
         <v>34</v>
       </c>
       <c r="AC31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD31" t="n">
         <v>12</v>
@@ -6464,7 +6464,7 @@
         <v>40</v>
       </c>
       <c r="AG31" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH31" t="n">
         <v>14</v>
@@ -6485,7 +6485,7 @@
         <v>36</v>
       </c>
       <c r="AN31" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO31" t="n">
         <v>5.6</v>
@@ -6506,7 +6506,7 @@
         <v>30</v>
       </c>
       <c r="AU31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV31" t="n">
         <v>11.5</v>
@@ -6515,7 +6515,7 @@
         <v>14.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY31" t="n">
         <v>17.5</v>
@@ -6539,14 +6539,14 @@
         <v>32</v>
       </c>
       <c r="BF31" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG31" t="n">
         <v>5.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H2" t="n">
         <v>2.72</v>
       </c>
-      <c r="G2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.56</v>
-      </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.25</v>
       </c>
-      <c r="K2" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="X2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD2" t="n">
         <v>14</v>
       </c>
-      <c r="Y2" t="n">
-        <v>990</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>13</v>
-      </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AO2" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA2" t="n">
         <v>6</v>
       </c>
-      <c r="AU2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV2" t="n">
+      <c r="BB2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD2" t="n">
         <v>5.9</v>
       </c>
-      <c r="AW2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -951,91 +951,91 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.23</v>
+        <v>6.4</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>1.48</v>
       </c>
       <c r="I3" t="n">
-        <v>980</v>
+        <v>1.53</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.29</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>1.93</v>
+        <v>2.86</v>
       </c>
       <c r="T3" t="n">
-        <v>1.05</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>2.84</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
         <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1056,65 +1056,65 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.08</v>
+        <v>4.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.08</v>
+        <v>4.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.08</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.08</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.08</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.08</v>
+        <v>4.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.08</v>
+        <v>5.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.08</v>
+        <v>7.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.08</v>
+        <v>6.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.08</v>
+        <v>6.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.08</v>
+        <v>6.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.08</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.08</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.08</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.07</v>
+        <v>7.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.08</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.3</v>
       </c>
-      <c r="H4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>1.05</v>
       </c>
       <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW4" t="n">
         <v>1.86</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AX4" t="n">
-        <v>5</v>
+        <v>1.17</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.6</v>
+        <v>1.78</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.9</v>
+        <v>1.19</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>1.21</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.7</v>
+        <v>1.21</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.7</v>
+        <v>1.21</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>1.22</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>1.22</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.7</v>
+        <v>1.22</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>1.22</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="G5" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="K5" t="n">
         <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O5" t="n">
         <v>1.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.89</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.88</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
         <v>12.5</v>
@@ -1402,10 +1402,10 @@
         <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
         <v>8</v>
@@ -1414,95 +1414,95 @@
         <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
         <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV5" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AW5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE5" t="n">
         <v>5.6</v>
       </c>
-      <c r="AS5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="BF5" t="n">
         <v>5</v>
       </c>
-      <c r="AW5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BG5" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1533,61 +1533,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="O6" t="n">
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>1.47</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1599,104 +1599,104 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="AH6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>12.5</v>
+        <v>180</v>
       </c>
       <c r="AK6" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>2.16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8.4</v>
+        <v>2.28</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
         <v>7.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.199999999999999</v>
+        <v>2.42</v>
       </c>
       <c r="BE6" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.7</v>
+        <v>2.08</v>
       </c>
       <c r="BG6" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1727,46 +1727,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I7" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="K7" t="n">
         <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
         <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
         <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
         <v>2.04</v>
@@ -1775,25 +1775,25 @@
         <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
         <v>7.6</v>
@@ -1802,19 +1802,19 @@
         <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="AF7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
@@ -1832,10 +1832,10 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.2</v>
@@ -1844,7 +1844,7 @@
         <v>5.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>6.2</v>
@@ -1853,44 +1853,44 @@
         <v>4.9</v>
       </c>
       <c r="AV7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY7" t="n">
         <v>5.7</v>
       </c>
-      <c r="AW7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>6</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BD7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE7" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BE7" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF7" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="I8" t="n">
         <v>1.38</v>
       </c>
       <c r="J8" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="K8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.26</v>
@@ -1945,7 +1945,7 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
         <v>1.21</v>
@@ -1954,22 +1954,22 @@
         <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R8" t="n">
         <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
@@ -1987,7 +1987,7 @@
         <v>11</v>
       </c>
       <c r="AB8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
         <v>14</v>
@@ -2005,10 +2005,10 @@
         <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>250</v>
       </c>
       <c r="AJ8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>5.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -2115,70 +2115,70 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G9" t="n">
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U9" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X9" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB9" t="n">
         <v>16.5</v>
@@ -2187,25 +2187,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE9" t="n">
         <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2217,68 +2217,68 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
         <v>17.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>19</v>
+        <v>5.1</v>
       </c>
       <c r="AQ9" t="n">
         <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>5.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AW9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>5.2</v>
       </c>
-      <c r="AX9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA9" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="n">
         <v>5.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>34</v>
+        <v>5.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG9" t="n">
         <v>12</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -2309,97 +2309,97 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="G10" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
         <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG10" t="n">
         <v>970</v>
       </c>
-      <c r="AC10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -2411,68 +2411,68 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
         <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF10" t="n">
         <v>6.6</v>
       </c>
-      <c r="BF10" t="n">
-        <v>23</v>
-      </c>
       <c r="BG10" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -2503,67 +2503,67 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="G11" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
         <v>1.31</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
         <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2572,7 +2572,7 @@
         <v>16.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2581,7 +2581,7 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AG11" t="n">
         <v>21</v>
@@ -2593,7 +2593,7 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="AK11" t="n">
         <v>65</v>
@@ -2605,68 +2605,68 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT11" t="n">
         <v>6.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX11" t="n">
         <v>6.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -2697,97 +2697,97 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I12" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S12" t="n">
         <v>3.75</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.5</v>
       </c>
       <c r="T12" t="n">
         <v>1.84</v>
       </c>
       <c r="U12" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH12" t="n">
         <v>18</v>
       </c>
-      <c r="AA12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>20</v>
-      </c>
       <c r="AI12" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AJ12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK12" t="n">
         <v>80</v>
@@ -2796,71 +2796,71 @@
         <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AO12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AR12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AT12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE12" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>30</v>
-      </c>
       <c r="BF12" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>19.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -2891,73 +2891,73 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="G13" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="K13" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N13" t="n">
         <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="P13" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U13" t="n">
         <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC13" t="n">
         <v>7</v>
@@ -2969,25 +2969,25 @@
         <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI13" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AK13" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AL13" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AS13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
         <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AY13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BB13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BD13" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="BE13" t="n">
         <v>10</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>60</v>
+        <v>9.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G14" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="H14" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.35</v>
       </c>
-      <c r="J14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>1.05</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ14" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.62</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.61</v>
+        <v>5.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.67</v>
+        <v>6.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.72</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.63</v>
+        <v>5.7</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.71</v>
+        <v>7.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.68</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.63</v>
+        <v>5.9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.66</v>
+        <v>6.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.72</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.72</v>
+        <v>8.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.71</v>
+        <v>7.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.72</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.74</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.71</v>
+        <v>7.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.71</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -3294,40 +3294,40 @@
         <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>2.08</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S15" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W15" t="n">
         <v>1.54</v>
@@ -3339,7 +3339,7 @@
         <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
         <v>120</v>
@@ -3348,7 +3348,7 @@
         <v>15.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
         <v>13</v>
@@ -3360,34 +3360,34 @@
         <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP15" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>17</v>
       </c>
       <c r="AQ15" t="n">
         <v>12.5</v>
@@ -3420,19 +3420,19 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC15" t="n">
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF15" t="n">
         <v>14.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>1.45</v>
       </c>
       <c r="G16" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="H16" t="n">
         <v>2.92</v>
       </c>
       <c r="I16" t="n">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
         <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3509,10 +3509,10 @@
         <v>1.19</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="T16" t="n">
         <v>1.05</v>
@@ -3524,7 +3524,7 @@
         <v>1.16</v>
       </c>
       <c r="W16" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3563,7 +3563,7 @@
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
         <v>1000</v>
@@ -3575,68 +3575,68 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.82</v>
+        <v>1.26</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.87</v>
+        <v>1.26</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.89</v>
+        <v>1.27</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.71</v>
+        <v>1.21</v>
       </c>
       <c r="AU16" t="n">
         <v>5.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.81</v>
+        <v>1.26</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.69</v>
+        <v>1.23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.8</v>
+        <v>1.24</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.87</v>
+        <v>1.27</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.82</v>
+        <v>1.26</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.84</v>
+        <v>1.26</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="BF16" t="n">
         <v>2.18</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.86</v>
+        <v>1.55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -3667,49 +3667,49 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="G17" t="n">
         <v>1.47</v>
       </c>
       <c r="H17" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J17" t="n">
         <v>4.8</v>
       </c>
       <c r="K17" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
         <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
         <v>2.02</v>
@@ -3727,7 +3727,7 @@
         <v>85</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -3739,7 +3739,7 @@
         <v>12.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -3751,7 +3751,7 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -3760,10 +3760,10 @@
         <v>13.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -3775,16 +3775,16 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ17" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AR17" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
@@ -3793,10 +3793,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AW17" t="n">
-        <v>70</v>
+        <v>8.4</v>
       </c>
       <c r="AX17" t="n">
         <v>8.800000000000001</v>
@@ -3805,10 +3805,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BB17" t="n">
         <v>10.5</v>
@@ -3820,17 +3820,17 @@
         <v>15</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
         <v>5.1</v>
       </c>
       <c r="BG17" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -3861,73 +3861,73 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="G18" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="H18" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>290</v>
+        <v>46</v>
       </c>
       <c r="AB18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
         <v>7.4</v>
@@ -3936,95 +3936,95 @@
         <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
         <v>16</v>
       </c>
       <c r="AI18" t="n">
-        <v>160</v>
+        <v>44</v>
       </c>
       <c r="AJ18" t="n">
         <v>240</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>390</v>
+        <v>90</v>
       </c>
       <c r="AN18" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
         <v>48</v>
       </c>
       <c r="AP18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY18" t="n">
         <v>11</v>
       </c>
-      <c r="AT18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW18" t="n">
+      <c r="AZ18" t="n">
         <v>14.5</v>
       </c>
-      <c r="AX18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA18" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="BB18" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BC18" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BD18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BE18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG18" t="n">
         <v>24</v>
       </c>
-      <c r="BF18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>10</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="G19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
         <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
       <c r="T19" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
         <v>2.2</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
         <v>120</v>
       </c>
       <c r="AJ19" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK19" t="n">
         <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG19" t="n">
         <v>8.6</v>
       </c>
-      <c r="AO19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -4249,61 +4249,61 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I20" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L20" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
         <v>1.35</v>
       </c>
       <c r="P20" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U20" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W20" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
         <v>10.5</v>
@@ -4312,7 +4312,7 @@
         <v>29</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AB20" t="n">
         <v>12</v>
@@ -4321,7 +4321,7 @@
         <v>8</v>
       </c>
       <c r="AD20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
         <v>75</v>
@@ -4333,7 +4333,7 @@
         <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
         <v>160</v>
@@ -4342,7 +4342,7 @@
         <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4351,13 +4351,13 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO20" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AP20" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AQ20" t="n">
         <v>8.800000000000001</v>
@@ -4366,7 +4366,7 @@
         <v>8.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
@@ -4375,44 +4375,44 @@
         <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="AX20" t="n">
         <v>10.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA20" t="n">
         <v>9.6</v>
       </c>
       <c r="BB20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC20" t="n">
         <v>9.4</v>
       </c>
-      <c r="BC20" t="n">
-        <v>16</v>
-      </c>
       <c r="BD20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BE20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>19.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -4443,46 +4443,46 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="G21" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K21" t="n">
         <v>2.96</v>
       </c>
       <c r="L21" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="M21" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="O21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="R21" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="T21" t="n">
         <v>2.14</v>
@@ -4491,22 +4491,22 @@
         <v>1.74</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA21" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB21" t="n">
         <v>8.4</v>
@@ -4515,13 +4515,13 @@
         <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE21" t="n">
         <v>55</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>14.5</v>
@@ -4530,13 +4530,13 @@
         <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AJ21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK21" t="n">
         <v>55</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>48</v>
       </c>
       <c r="AL21" t="n">
         <v>170</v>
@@ -4545,7 +4545,7 @@
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AO21" t="n">
         <v>500</v>
@@ -4554,16 +4554,16 @@
         <v>6.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR21" t="n">
         <v>16.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU21" t="n">
         <v>6</v>
@@ -4575,38 +4575,38 @@
         <v>38</v>
       </c>
       <c r="AX21" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AY21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BF21" t="n">
-        <v>42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>3.15</v>
       </c>
       <c r="G22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H22" t="n">
         <v>3.05</v>
@@ -4649,22 +4649,22 @@
         <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="K22" t="n">
         <v>2.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="M22" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N22" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O22" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="P22" t="n">
         <v>1.38</v>
@@ -4673,31 +4673,31 @@
         <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X22" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
@@ -4706,10 +4706,10 @@
         <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE22" t="n">
         <v>500</v>
@@ -4727,7 +4727,7 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="AQ22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU22" t="n">
         <v>6</v>
       </c>
-      <c r="AR22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV22" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.2</v>
+        <v>2.56</v>
       </c>
       <c r="AX22" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.76</v>
+        <v>9.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>2.62</v>
       </c>
       <c r="BB22" t="n">
-        <v>2.54</v>
+        <v>11.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.54</v>
+        <v>7</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.3</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="BG22" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="H23" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="I23" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="J23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K23" t="n">
         <v>5</v>
       </c>
-      <c r="K23" t="n">
-        <v>5.6</v>
-      </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="Q23" t="n">
         <v>1.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S23" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="T23" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="U23" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="V23" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="X23" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Z23" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AA23" t="n">
         <v>700</v>
       </c>
       <c r="AB23" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AC23" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AI23" t="n">
         <v>700</v>
       </c>
       <c r="AJ23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB23" t="n">
         <v>16</v>
       </c>
-      <c r="AK23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BC23" t="n">
-        <v>5.6</v>
+        <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BE23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -5025,70 +5025,70 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G24" t="n">
         <v>4.6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="J24" t="n">
         <v>3.85</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="M24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R24" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="S24" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="T24" t="n">
         <v>1.56</v>
       </c>
       <c r="U24" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="V24" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X24" t="n">
         <v>24</v>
       </c>
       <c r="Y24" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AB24" t="n">
         <v>70</v>
@@ -5097,13 +5097,13 @@
         <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF24" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AG24" t="n">
         <v>18.5</v>
@@ -5112,7 +5112,7 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AJ24" t="n">
         <v>500</v>
@@ -5127,68 +5127,68 @@
         <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AO24" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AP24" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AR24" t="n">
         <v>12</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT24" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AW24" t="n">
         <v>15</v>
       </c>
       <c r="AX24" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AY24" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BA24" t="n">
         <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC24" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BD24" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BF24" t="n">
         <v>22</v>
       </c>
       <c r="BG24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -5231,52 +5231,52 @@
         <v>4.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
         <v>4.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U25" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="V25" t="n">
         <v>1.31</v>
       </c>
       <c r="W25" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X25" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z25" t="n">
         <v>30</v>
@@ -5285,10 +5285,10 @@
         <v>160</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
         <v>16.5</v>
@@ -5315,13 +5315,13 @@
         <v>21</v>
       </c>
       <c r="AL25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM25" t="n">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO25" t="n">
         <v>40</v>
@@ -5330,16 +5330,16 @@
         <v>14.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
         <v>25</v>
       </c>
       <c r="AS25" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AT25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU25" t="n">
         <v>7.2</v>
@@ -5348,7 +5348,7 @@
         <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AX25" t="n">
         <v>12.5</v>
@@ -5357,7 +5357,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA25" t="n">
         <v>20</v>
@@ -5372,17 +5372,17 @@
         <v>28</v>
       </c>
       <c r="BE25" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BF25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG25" t="n">
         <v>30</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -5413,170 +5413,170 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G26" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H26" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="I26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.6</v>
       </c>
-      <c r="J26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.75</v>
-      </c>
       <c r="L26" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R26" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T26" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="U26" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V26" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="X26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD26" t="n">
         <v>27</v>
       </c>
-      <c r="AA26" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG26" t="n">
+      <c r="BE26" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF26" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW26" t="n">
+      <c r="BG26" t="n">
         <v>24</v>
       </c>
-      <c r="AX26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -5610,43 +5610,43 @@
         <v>3.05</v>
       </c>
       <c r="G27" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H27" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I27" t="n">
         <v>2.58</v>
       </c>
       <c r="J27" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R27" t="n">
         <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T27" t="n">
         <v>1.81</v>
@@ -5655,25 +5655,25 @@
         <v>2.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W27" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y27" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z27" t="n">
         <v>16</v>
       </c>
       <c r="AA27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB27" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC27" t="n">
         <v>7.8</v>
@@ -5682,95 +5682,95 @@
         <v>12</v>
       </c>
       <c r="AE27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI27" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AK27" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AL27" t="n">
         <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN27" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AO27" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
         <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX27" t="n">
         <v>18.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
         <v>34</v>
       </c>
       <c r="BB27" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BC27" t="n">
         <v>32</v>
       </c>
       <c r="BD27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE27" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG27" t="n">
         <v>20</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="I28" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
@@ -5825,16 +5825,16 @@
         <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O28" t="n">
         <v>1.53</v>
       </c>
       <c r="P28" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R28" t="n">
         <v>1.21</v>
@@ -5849,25 +5849,25 @@
         <v>1.83</v>
       </c>
       <c r="V28" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W28" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X28" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC28" t="n">
         <v>7.4</v>
@@ -5876,10 +5876,10 @@
         <v>13.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG28" t="n">
         <v>15.5</v>
@@ -5888,16 +5888,16 @@
         <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ28" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AK28" t="n">
         <v>120</v>
       </c>
       <c r="AL28" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
@@ -5906,19 +5906,19 @@
         <v>65</v>
       </c>
       <c r="AO28" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP28" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR28" t="n">
         <v>13.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AT28" t="n">
         <v>8.4</v>
@@ -5933,38 +5933,38 @@
         <v>16</v>
       </c>
       <c r="AX28" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY28" t="n">
         <v>13</v>
       </c>
       <c r="AZ28" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA28" t="n">
         <v>44</v>
       </c>
       <c r="BB28" t="n">
-        <v>48</v>
+        <v>9.6</v>
       </c>
       <c r="BC28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD28" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE28" t="n">
         <v>10.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -5995,55 +5995,55 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="G29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="I29" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="J29" t="n">
         <v>4.2</v>
       </c>
       <c r="K29" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P29" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="U29" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V29" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="W29" t="n">
         <v>1.13</v>
@@ -6052,13 +6052,13 @@
         <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB29" t="n">
         <v>1000</v>
@@ -6100,40 +6100,40 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AP29" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="AU29" t="n">
         <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="AW29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="BA29" t="n">
         <v>18</v>
@@ -6148,17 +6148,17 @@
         <v>4.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.82</v>
+        <v>4.7</v>
       </c>
       <c r="BF29" t="n">
         <v>4.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G30" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H30" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="J30" t="n">
         <v>4.4</v>
@@ -6207,7 +6207,7 @@
         <v>4.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="n">
         <v>1.03</v>
@@ -6216,49 +6216,49 @@
         <v>7.2</v>
       </c>
       <c r="O30" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P30" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S30" t="n">
         <v>2.14</v>
       </c>
       <c r="T30" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U30" t="n">
         <v>3.05</v>
       </c>
       <c r="V30" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W30" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X30" t="n">
         <v>34</v>
       </c>
       <c r="Y30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA30" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB30" t="n">
         <v>19</v>
       </c>
       <c r="AC30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD30" t="n">
         <v>13.5</v>
@@ -6270,43 +6270,43 @@
         <v>21</v>
       </c>
       <c r="AG30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH30" t="n">
         <v>14</v>
       </c>
       <c r="AI30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>21</v>
       </c>
-      <c r="AL30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>46</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>20</v>
-      </c>
       <c r="AR30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS30" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT30" t="n">
         <v>18</v>
@@ -6315,25 +6315,25 @@
         <v>10.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX30" t="n">
         <v>20</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
         <v>13.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC30" t="n">
         <v>19.5</v>
@@ -6345,14 +6345,14 @@
         <v>42</v>
       </c>
       <c r="BF30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG30" t="n">
         <v>11</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -6407,28 +6407,28 @@
         <v>1.02</v>
       </c>
       <c r="N31" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O31" t="n">
         <v>1.11</v>
       </c>
       <c r="P31" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R31" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S31" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="T31" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="U31" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="V31" t="n">
         <v>2.16</v>
@@ -6437,19 +6437,19 @@
         <v>1.32</v>
       </c>
       <c r="X31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y31" t="n">
         <v>21</v>
       </c>
       <c r="Z31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA31" t="n">
         <v>23</v>
       </c>
       <c r="AB31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC31" t="n">
         <v>12.5</v>
@@ -6464,10 +6464,10 @@
         <v>40</v>
       </c>
       <c r="AG31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AI31" t="n">
         <v>21</v>
@@ -6482,16 +6482,16 @@
         <v>32</v>
       </c>
       <c r="AM31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AN31" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AO31" t="n">
         <v>5.6</v>
       </c>
       <c r="AP31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AQ31" t="n">
         <v>20</v>
@@ -6509,7 +6509,7 @@
         <v>12</v>
       </c>
       <c r="AV31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
         <v>14.5</v>
@@ -6521,7 +6521,7 @@
         <v>17.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
         <v>19.5</v>
@@ -6536,17 +6536,17 @@
         <v>30</v>
       </c>
       <c r="BE31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG31" t="n">
         <v>5.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="I2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X2" t="n">
         <v>3.2</v>
       </c>
-      <c r="J2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X2" t="n">
-        <v>11.5</v>
-      </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>290</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>520</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS2" t="n">
         <v>55</v>
       </c>
-      <c r="AB2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.5</v>
+        <v>27</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.7</v>
+        <v>130</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.2</v>
+        <v>30</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>220</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.8</v>
+        <v>120</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.8</v>
+        <v>95</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.9</v>
+        <v>250</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.9</v>
+        <v>220</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.8</v>
+        <v>200</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>34</v>
+      </c>
+      <c r="G3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS3" t="n">
         <v>6.4</v>
       </c>
-      <c r="G3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
+      <c r="AT3" t="n">
         <v>7.4</v>
       </c>
-      <c r="AP3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AU3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW3" t="n">
         <v>6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.5</v>
       </c>
       <c r="AX3" t="n">
         <v>7.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.6</v>
+        <v>48</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.2</v>
+        <v>42</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>250</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1145,97 +1145,97 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
         <v>2.28</v>
       </c>
-      <c r="I4" t="n">
+      <c r="M4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.58</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.05</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.93</v>
+        <v>38</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.48</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.86</v>
+        <v>36</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.78</v>
+        <v>15.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.19</v>
+        <v>27</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.21</v>
+        <v>2.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.21</v>
+        <v>60</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.21</v>
+        <v>50</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.22</v>
+        <v>2.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.22</v>
+        <v>24</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.22</v>
+        <v>7.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.22</v>
+        <v>46</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
         <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U5" t="n">
         <v>1.89</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA5" t="n">
         <v>75</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN5" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.4</v>
+        <v>46</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.2</v>
+        <v>42</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.7</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.4</v>
+        <v>44</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.3</v>
+        <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O6" t="n">
         <v>1.3</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>15</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.29</v>
-      </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>1.47</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1602,19 +1602,19 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
         <v>42</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>180</v>
+        <v>12.5</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1641,10 +1641,10 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.16</v>
+        <v>6.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>4.2</v>
@@ -1656,7 +1656,7 @@
         <v>3.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="AV6" t="n">
         <v>4.2</v>
@@ -1668,10 +1668,10 @@
         <v>3.85</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="BA6" t="n">
         <v>4.2</v>
@@ -1683,20 +1683,20 @@
         <v>7.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="n">
         <v>2.22</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="K7" t="n">
         <v>3.4</v>
@@ -1751,13 +1751,13 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
         <v>2.48</v>
@@ -1766,7 +1766,7 @@
         <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T7" t="n">
         <v>2.04</v>
@@ -1775,25 +1775,25 @@
         <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X7" t="n">
         <v>9.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
         <v>7.6</v>
@@ -1802,22 +1802,22 @@
         <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -1832,19 +1832,19 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR7" t="n">
         <v>5.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT7" t="n">
         <v>6.2</v>
@@ -1853,44 +1853,44 @@
         <v>4.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AW7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX7" t="n">
         <v>7</v>
       </c>
-      <c r="AX7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG7" t="n">
         <v>7.4</v>
       </c>
-      <c r="BD7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>7</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>12.5</v>
@@ -1933,13 +1933,13 @@
         <v>1.38</v>
       </c>
       <c r="J8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
@@ -1948,43 +1948,43 @@
         <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
         <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AB8" t="n">
         <v>1000</v>
@@ -2029,16 +2029,16 @@
         <v>5.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
         <v>5.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT8" t="n">
         <v>16.5</v>
@@ -2047,44 +2047,44 @@
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AW8" t="n">
         <v>6.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>2.36</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
@@ -2145,19 +2145,19 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
         <v>2.38</v>
@@ -2166,119 +2166,119 @@
         <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE9" t="n">
         <v>42</v>
       </c>
-      <c r="Y9" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>27</v>
-      </c>
       <c r="AF9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
         <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.6</v>
+        <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.9</v>
+        <v>18.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -2315,13 +2315,13 @@
         <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I10" t="n">
         <v>3.15</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
         <v>3.5</v>
@@ -2330,7 +2330,7 @@
         <v>1.45</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
         <v>3.5</v>
@@ -2339,7 +2339,7 @@
         <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q10" t="n">
         <v>2.14</v>
@@ -2360,13 +2360,13 @@
         <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
         <v>42</v>
@@ -2381,25 +2381,25 @@
         <v>7.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -2417,62 +2417,62 @@
         <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV10" t="n">
         <v>6</v>
       </c>
-      <c r="AS10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AW10" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
         <v>7.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -2503,46 +2503,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H11" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I11" t="n">
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
         <v>4.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
         <v>1.31</v>
       </c>
       <c r="P11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.94</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.92</v>
       </c>
       <c r="R11" t="n">
         <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
         <v>2</v>
@@ -2551,16 +2551,16 @@
         <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,13 +2569,13 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
         <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
@@ -2584,10 +2584,10 @@
         <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -2596,10 +2596,10 @@
         <v>15</v>
       </c>
       <c r="AK11" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
@@ -2611,40 +2611,40 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AV11" t="n">
         <v>7.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="AY11" t="n">
         <v>5.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB11" t="n">
         <v>6.2</v>
@@ -2653,20 +2653,20 @@
         <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
         <v>2.4</v>
       </c>
       <c r="I12" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
         <v>3.7</v>
@@ -2721,28 +2721,28 @@
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
         <v>1.65</v>
@@ -2751,40 +2751,40 @@
         <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z12" t="n">
         <v>15.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
         <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AJ12" t="n">
         <v>60</v>
@@ -2793,74 +2793,74 @@
         <v>80</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
         <v>13</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="BD12" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BE12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -2894,70 +2894,70 @@
         <v>3.1</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J13" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="M13" t="n">
         <v>1.18</v>
       </c>
       <c r="N13" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="O13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
         <v>1.13</v>
       </c>
       <c r="S13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="V13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.45</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.44</v>
-      </c>
       <c r="X13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Y13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB13" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>8</v>
       </c>
       <c r="AC13" t="n">
         <v>7</v>
@@ -2966,13 +2966,13 @@
         <v>16.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH13" t="n">
         <v>29</v>
@@ -2981,7 +2981,7 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AK13" t="n">
         <v>120</v>
@@ -2996,65 +2996,65 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX13" t="n">
         <v>17</v>
       </c>
       <c r="AY13" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BE13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF13" t="n">
         <v>10</v>
       </c>
-      <c r="BF13" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BG13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -3085,67 +3085,67 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X14" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
         <v>220</v>
@@ -3154,7 +3154,7 @@
         <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
         <v>12.5</v>
@@ -3163,13 +3163,13 @@
         <v>85</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
         <v>290</v>
@@ -3184,71 +3184,71 @@
         <v>290</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
         <v>75</v>
       </c>
       <c r="AO14" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
         <v>5.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AX14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG14" t="n">
         <v>7.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G15" t="n">
         <v>2.84</v>
@@ -3288,46 +3288,46 @@
         <v>2.58</v>
       </c>
       <c r="I15" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="J15" t="n">
         <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.46</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W15" t="n">
         <v>1.54</v>
@@ -3336,7 +3336,7 @@
         <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z15" t="n">
         <v>20</v>
@@ -3348,7 +3348,7 @@
         <v>15.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD15" t="n">
         <v>13</v>
@@ -3357,7 +3357,7 @@
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
         <v>13.5</v>
@@ -3372,46 +3372,46 @@
         <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AM15" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP15" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
         <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
         <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY15" t="n">
         <v>11</v>
@@ -3420,29 +3420,29 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="BC15" t="n">
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BE15" t="n">
         <v>8.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="G16" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="H16" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>1.48</v>
+        <v>2.48</v>
       </c>
       <c r="T16" t="n">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="W16" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>600</v>
+        <v>8.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.25</v>
+        <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.26</v>
+        <v>6.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.26</v>
+        <v>7.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.27</v>
+        <v>8.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.21</v>
+        <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.26</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.27</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.23</v>
+        <v>6.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.24</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.27</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.26</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.18</v>
+        <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.55</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
         <v>1.47</v>
       </c>
       <c r="H17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.3</v>
@@ -3691,7 +3691,7 @@
         <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.2</v>
@@ -3703,22 +3703,22 @@
         <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T17" t="n">
         <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V17" t="n">
         <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X17" t="n">
         <v>42</v>
@@ -3727,7 +3727,7 @@
         <v>85</v>
       </c>
       <c r="Z17" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -3745,7 +3745,7 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG17" t="n">
         <v>10.5</v>
@@ -3763,7 +3763,7 @@
         <v>15.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -3778,37 +3778,37 @@
         <v>20</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>28</v>
+        <v>7.4</v>
       </c>
       <c r="BB17" t="n">
         <v>10.5</v>
@@ -3820,17 +3820,17 @@
         <v>15</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BG17" t="n">
         <v>15</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G18" t="n">
         <v>2.66</v>
       </c>
-      <c r="G18" t="n">
-        <v>2.72</v>
-      </c>
       <c r="H18" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J18" t="n">
         <v>3.4</v>
@@ -3879,19 +3879,19 @@
         <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
         <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q18" t="n">
         <v>1.99</v>
@@ -3900,31 +3900,31 @@
         <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y18" t="n">
         <v>12.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB18" t="n">
         <v>11.5</v>
@@ -3933,13 +3933,13 @@
         <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG18" t="n">
         <v>12</v>
@@ -3951,28 +3951,28 @@
         <v>44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>240</v>
+        <v>38</v>
       </c>
       <c r="AK18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO18" t="n">
         <v>29</v>
       </c>
-      <c r="AL18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>48</v>
-      </c>
       <c r="AP18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR18" t="n">
         <v>18</v>
@@ -3993,38 +3993,38 @@
         <v>29</v>
       </c>
       <c r="AX18" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
         <v>24</v>
       </c>
       <c r="BB18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD18" t="n">
         <v>34</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BE18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG18" t="n">
         <v>26</v>
       </c>
-      <c r="BD18" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>24</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -4055,31 +4055,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="G19" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
         <v>4.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.23</v>
@@ -4091,43 +4091,43 @@
         <v>1.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
         <v>2.78</v>
       </c>
       <c r="T19" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="n">
         <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB19" t="n">
         <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>130</v>
@@ -4145,7 +4145,7 @@
         <v>120</v>
       </c>
       <c r="AJ19" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
         <v>18</v>
@@ -4154,71 +4154,71 @@
         <v>30</v>
       </c>
       <c r="AM19" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="n">
         <v>9</v>
       </c>
       <c r="AO19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP19" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AR19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU19" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AS19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AV19" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H20" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="I20" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.44</v>
@@ -4279,10 +4279,10 @@
         <v>1.35</v>
       </c>
       <c r="P20" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R20" t="n">
         <v>1.32</v>
@@ -4294,13 +4294,13 @@
         <v>1.79</v>
       </c>
       <c r="U20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V20" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X20" t="n">
         <v>13.5</v>
@@ -4309,7 +4309,7 @@
         <v>10.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AA20" t="n">
         <v>85</v>
@@ -4321,52 +4321,52 @@
         <v>8</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="AF20" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AG20" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="n">
         <v>90</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AR20" t="n">
         <v>8.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
@@ -4375,44 +4375,44 @@
         <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="AX20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB20" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>10</v>
-      </c>
       <c r="BC20" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>3.15</v>
       </c>
       <c r="H21" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I21" t="n">
         <v>3.15</v>
       </c>
       <c r="J21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K21" t="n">
         <v>2.96</v>
@@ -4467,16 +4467,16 @@
         <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O21" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="P21" t="n">
         <v>1.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
         <v>1.17</v>
@@ -4485,10 +4485,10 @@
         <v>6.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U21" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V21" t="n">
         <v>1.46</v>
@@ -4509,16 +4509,16 @@
         <v>150</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC21" t="n">
         <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF21" t="n">
         <v>19</v>
@@ -4530,13 +4530,13 @@
         <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ21" t="n">
         <v>120</v>
       </c>
       <c r="AK21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL21" t="n">
         <v>170</v>
@@ -4545,10 +4545,10 @@
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AO21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
         <v>6.8</v>
@@ -4557,13 +4557,13 @@
         <v>7.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
         <v>6</v>
@@ -4572,7 +4572,7 @@
         <v>12</v>
       </c>
       <c r="AW21" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="AX21" t="n">
         <v>16</v>
@@ -4584,29 +4584,29 @@
         <v>20</v>
       </c>
       <c r="BA21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB21" t="n">
         <v>10</v>
       </c>
-      <c r="BB21" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BC21" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF21" t="n">
         <v>10</v>
       </c>
-      <c r="BE21" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG21" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -4643,13 +4643,13 @@
         <v>3.3</v>
       </c>
       <c r="H22" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="I22" t="n">
         <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K22" t="n">
         <v>2.8</v>
@@ -4679,7 +4679,7 @@
         <v>7.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
         <v>1.64</v>
@@ -4691,13 +4691,13 @@
         <v>1.44</v>
       </c>
       <c r="X22" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
@@ -4706,7 +4706,7 @@
         <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AD22" t="n">
         <v>500</v>
@@ -4727,7 +4727,7 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
         <v>1000</v>
@@ -4745,16 +4745,16 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AT22" t="n">
         <v>5.2</v>
@@ -4763,44 +4763,44 @@
         <v>6</v>
       </c>
       <c r="AV22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>9.6</v>
+        <v>2.3</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>11.5</v>
+        <v>1.78</v>
       </c>
       <c r="BC22" t="n">
-        <v>7</v>
+        <v>1.78</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>14.5</v>
+        <v>2.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.62</v>
+        <v>1.79</v>
       </c>
       <c r="BG22" t="n">
-        <v>12.5</v>
+        <v>1.79</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G23" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H23" t="n">
         <v>5.2</v>
       </c>
       <c r="I23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.27</v>
@@ -4855,10 +4855,10 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P23" t="n">
         <v>2.88</v>
@@ -4870,58 +4870,58 @@
         <v>1.76</v>
       </c>
       <c r="S23" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T23" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="U23" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W23" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="X23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y23" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="Z23" t="n">
         <v>60</v>
       </c>
       <c r="AA23" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AB23" t="n">
         <v>14</v>
       </c>
       <c r="AC23" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD23" t="n">
         <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK23" t="n">
         <v>15</v>
@@ -4933,7 +4933,7 @@
         <v>65</v>
       </c>
       <c r="AN23" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AO23" t="n">
         <v>40</v>
@@ -4942,13 +4942,13 @@
         <v>25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="AS23" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="AT23" t="n">
         <v>12.5</v>
@@ -4957,44 +4957,44 @@
         <v>10.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23" t="n">
         <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BB23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BC23" t="n">
         <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE23" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG23" t="n">
         <v>32</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -5031,16 +5031,16 @@
         <v>4.6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I24" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.29</v>
@@ -5049,34 +5049,34 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O24" t="n">
         <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q24" t="n">
         <v>1.57</v>
       </c>
       <c r="R24" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S24" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U24" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V24" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X24" t="n">
         <v>24</v>
@@ -5088,16 +5088,16 @@
         <v>15</v>
       </c>
       <c r="AA24" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB24" t="n">
         <v>38</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>70</v>
       </c>
       <c r="AC24" t="n">
         <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
         <v>17</v>
@@ -5115,7 +5115,7 @@
         <v>25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AK24" t="n">
         <v>120</v>
@@ -5133,7 +5133,7 @@
         <v>9</v>
       </c>
       <c r="AP24" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>12</v>
@@ -5142,7 +5142,7 @@
         <v>12</v>
       </c>
       <c r="AS24" t="n">
-        <v>9.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="AT24" t="n">
         <v>13.5</v>
@@ -5154,25 +5154,25 @@
         <v>7</v>
       </c>
       <c r="AW24" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA24" t="n">
         <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD24" t="n">
         <v>18.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H25" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I25" t="n">
         <v>4.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K25" t="n">
         <v>3.7</v>
@@ -5243,37 +5243,37 @@
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W25" t="n">
         <v>1.84</v>
       </c>
       <c r="X25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y25" t="n">
         <v>17</v>
@@ -5285,7 +5285,7 @@
         <v>160</v>
       </c>
       <c r="AB25" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC25" t="n">
         <v>8.199999999999999</v>
@@ -5294,7 +5294,7 @@
         <v>16.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF25" t="n">
         <v>17</v>
@@ -5321,25 +5321,25 @@
         <v>80</v>
       </c>
       <c r="AN25" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP25" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR25" t="n">
         <v>25</v>
       </c>
       <c r="AS25" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AT25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU25" t="n">
         <v>7.2</v>
@@ -5348,7 +5348,7 @@
         <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AX25" t="n">
         <v>12.5</v>
@@ -5357,32 +5357,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BB25" t="n">
         <v>23</v>
       </c>
       <c r="BC25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD25" t="n">
         <v>28</v>
       </c>
       <c r="BE25" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BF25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G26" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H26" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J26" t="n">
         <v>3.55</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L26" t="n">
         <v>1.34</v>
@@ -5446,10 +5446,10 @@
         <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S26" t="n">
         <v>2.76</v>
@@ -5458,13 +5458,13 @@
         <v>1.58</v>
       </c>
       <c r="U26" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W26" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="X26" t="n">
         <v>18</v>
@@ -5488,10 +5488,10 @@
         <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
         <v>12</v>
@@ -5512,34 +5512,34 @@
         <v>32</v>
       </c>
       <c r="AM26" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO26" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>15.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AT26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5554,7 +5554,7 @@
         <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB26" t="n">
         <v>24</v>
@@ -5566,17 +5566,17 @@
         <v>27</v>
       </c>
       <c r="BE26" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="BF26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -5610,16 +5610,16 @@
         <v>3.05</v>
       </c>
       <c r="G27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H27" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I27" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K27" t="n">
         <v>3.55</v>
@@ -5637,7 +5637,7 @@
         <v>1.37</v>
       </c>
       <c r="P27" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
         <v>2.12</v>
@@ -5649,16 +5649,16 @@
         <v>3.9</v>
       </c>
       <c r="T27" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U27" t="n">
         <v>2.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W27" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X27" t="n">
         <v>13</v>
@@ -5670,7 +5670,7 @@
         <v>16</v>
       </c>
       <c r="AA27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB27" t="n">
         <v>12</v>
@@ -5694,7 +5694,7 @@
         <v>19</v>
       </c>
       <c r="AI27" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AJ27" t="n">
         <v>160</v>
@@ -5712,16 +5712,16 @@
         <v>40</v>
       </c>
       <c r="AO27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP27" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS27" t="n">
         <v>18.5</v>
@@ -5736,7 +5736,7 @@
         <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AX27" t="n">
         <v>18.5</v>
@@ -5748,29 +5748,29 @@
         <v>16</v>
       </c>
       <c r="BA27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB27" t="n">
         <v>23</v>
       </c>
       <c r="BC27" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF27" t="n">
         <v>32</v>
       </c>
       <c r="BG27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -5807,13 +5807,13 @@
         <v>3.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="I28" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K28" t="n">
         <v>3.15</v>
@@ -5825,61 +5825,61 @@
         <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O28" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P28" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
         <v>5.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V28" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W28" t="n">
         <v>1.41</v>
       </c>
       <c r="X28" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC28" t="n">
         <v>7.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
         <v>38</v>
       </c>
       <c r="AF28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG28" t="n">
         <v>15.5</v>
@@ -5891,43 +5891,43 @@
         <v>150</v>
       </c>
       <c r="AJ28" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AK28" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AL28" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>65</v>
+        <v>600</v>
       </c>
       <c r="AO28" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR28" t="n">
         <v>13.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW28" t="n">
         <v>16</v>
@@ -5936,35 +5936,35 @@
         <v>18.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB28" t="n">
-        <v>9.6</v>
+        <v>50</v>
       </c>
       <c r="BC28" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>46</v>
+      </c>
+      <c r="BG28" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>1.49</v>
       </c>
       <c r="I29" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="J29" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K29" t="n">
         <v>5.1</v>
@@ -6025,34 +6025,34 @@
         <v>1.26</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
         <v>1.79</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="U29" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V29" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="W29" t="n">
         <v>1.13</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y29" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z29" t="n">
         <v>500</v>
@@ -6106,37 +6106,37 @@
         <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AU29" t="n">
         <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AW29" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY29" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AZ29" t="n">
         <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="BB29" t="n">
         <v>4.2</v>
@@ -6148,17 +6148,17 @@
         <v>4.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="BF29" t="n">
         <v>4.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -6189,82 +6189,82 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G30" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.76</v>
       </c>
-      <c r="I30" t="n">
-        <v>2.78</v>
-      </c>
       <c r="J30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K30" t="n">
         <v>4.4</v>
       </c>
-      <c r="K30" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M30" t="n">
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O30" t="n">
         <v>1.14</v>
       </c>
       <c r="P30" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R30" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S30" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T30" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U30" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V30" t="n">
         <v>1.56</v>
       </c>
       <c r="W30" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X30" t="n">
         <v>34</v>
       </c>
       <c r="Y30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB30" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC30" t="n">
         <v>11</v>
       </c>
       <c r="AD30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF30" t="n">
         <v>21</v>
@@ -6282,7 +6282,7 @@
         <v>34</v>
       </c>
       <c r="AK30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -6291,10 +6291,10 @@
         <v>44</v>
       </c>
       <c r="AN30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP30" t="n">
         <v>32</v>
@@ -6303,10 +6303,10 @@
         <v>21</v>
       </c>
       <c r="AR30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AS30" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AT30" t="n">
         <v>18</v>
@@ -6315,13 +6315,13 @@
         <v>10.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW30" t="n">
         <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY30" t="n">
         <v>11.5</v>
@@ -6333,26 +6333,26 @@
         <v>26</v>
       </c>
       <c r="BB30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC30" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD30" t="n">
         <v>23</v>
       </c>
       <c r="BE30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF30" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -6389,46 +6389,46 @@
         <v>4.1</v>
       </c>
       <c r="H31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I31" t="n">
         <v>1.85</v>
       </c>
-      <c r="I31" t="n">
-        <v>1.86</v>
-      </c>
       <c r="J31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="M31" t="n">
         <v>1.02</v>
       </c>
       <c r="N31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O31" t="n">
         <v>1.11</v>
       </c>
       <c r="P31" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R31" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S31" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="T31" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="U31" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V31" t="n">
         <v>2.16</v>
@@ -6437,13 +6437,13 @@
         <v>1.32</v>
       </c>
       <c r="X31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA31" t="n">
         <v>23</v>
@@ -6461,7 +6461,7 @@
         <v>15</v>
       </c>
       <c r="AF31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG31" t="n">
         <v>18</v>
@@ -6476,37 +6476,37 @@
         <v>70</v>
       </c>
       <c r="AK31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AN31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AP31" t="n">
         <v>36</v>
       </c>
       <c r="AQ31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR31" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS31" t="n">
         <v>22</v>
       </c>
       <c r="AT31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV31" t="n">
         <v>11</v>
@@ -6515,16 +6515,16 @@
         <v>14.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AY31" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AZ31" t="n">
         <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB31" t="n">
         <v>65</v>
@@ -6533,20 +6533,20 @@
         <v>32</v>
       </c>
       <c r="BD31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE31" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BF31" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH26"/>
+  <dimension ref="A1:BH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Armenian Premier League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alashkert</t>
+          <t>Al-Jndal</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Ararat Yerevan</t>
+          <t>Al-Ula FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>1.15</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>12.5</v>
+        <v>2.66</v>
       </c>
       <c r="I2" t="n">
-        <v>680</v>
+        <v>2.76</v>
       </c>
       <c r="J2" t="n">
-        <v>8.4</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -781,34 +781,34 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.96</v>
+        <v>1.23</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>7.6</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -826,108 +826,108 @@
         <v>8.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>770</v>
+        <v>4.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="AG2" t="n">
-        <v>990</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>990</v>
+        <v>14</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF2" t="n">
         <v>80</v>
       </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG2" t="n">
-        <v>1.34</v>
+        <v>14</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Guangdong Mingtu</t>
+          <t>Aris FC Limassol</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Guangzhou Alpha</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>16.5</v>
+        <v>1.81</v>
       </c>
       <c r="G3" t="n">
-        <v>19.5</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
-        <v>1.31</v>
+        <v>4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1.34</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -975,153 +975,153 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>13.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="P3" t="n">
-        <v>1.69</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.34</v>
+        <v>1.35</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
-        <v>5.9</v>
+        <v>2.02</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>4.2</v>
       </c>
       <c r="V3" t="n">
-        <v>3.9</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>2.2</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF3" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL3" t="n">
         <v>21</v>
       </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>180</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>190</v>
-      </c>
       <c r="AM3" t="n">
-        <v>390</v>
+        <v>50</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG3" t="n">
         <v>23</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>110</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>130</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>160</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>300</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,108 +1131,108 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al-Jndal</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al-Ula FC</t>
+          <t>Apollon Limassol</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10.5</v>
+        <v>2.82</v>
       </c>
       <c r="G4" t="n">
-        <v>12.5</v>
+        <v>2.92</v>
       </c>
       <c r="H4" t="n">
-        <v>1.33</v>
+        <v>2.78</v>
       </c>
       <c r="I4" t="n">
-        <v>1.35</v>
+        <v>2.88</v>
       </c>
       <c r="J4" t="n">
-        <v>5.9</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="R4" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>2.68</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="V4" t="n">
-        <v>3.85</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>1.48</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD4" t="n">
         <v>14</v>
       </c>
-      <c r="AD4" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AE4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>70</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>550</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1241,7 +1241,7 @@
         <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1250,72 +1250,72 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AT4" t="n">
-        <v>27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="AX4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB4" t="n">
         <v>36</v>
       </c>
-      <c r="AY4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BC4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG4" t="n">
         <v>32</v>
       </c>
-      <c r="BB4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aris FC Limassol</t>
+          <t>FC Hunedoara</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="H5" t="n">
-        <v>2.36</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.46</v>
+        <v>6.8</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>2.86</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.77</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
-        <v>1.68</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.45</v>
+        <v>2.32</v>
       </c>
       <c r="X5" t="n">
-        <v>19.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="AA5" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>340</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR5" t="n">
         <v>42</v>
       </c>
-      <c r="AB5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="AS5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>110</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD5" t="n">
         <v>55</v>
       </c>
-      <c r="AL5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>28</v>
-      </c>
       <c r="BE5" t="n">
-        <v>46</v>
+        <v>210</v>
       </c>
       <c r="BF5" t="n">
         <v>15</v>
       </c>
       <c r="BG5" t="n">
-        <v>14.5</v>
+        <v>150</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Hunedoara</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L6" t="n">
         <v>1.54</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="H6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.4</v>
-      </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="W6" t="n">
-        <v>2.78</v>
+        <v>1.41</v>
       </c>
       <c r="X6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS6" t="n">
         <v>17</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AT6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE6" t="n">
         <v>24</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BF6" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="N7" t="n">
-        <v>2.84</v>
+        <v>2.16</v>
       </c>
       <c r="O7" t="n">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.52</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>420</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AA7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AY7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB7" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ7" t="n">
+      <c r="BC7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE7" t="n">
         <v>110</v>
       </c>
-      <c r="AK7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>24</v>
-      </c>
       <c r="BF7" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>2.52</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="J8" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.26</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>7.8</v>
+        <v>3.45</v>
       </c>
       <c r="T8" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.05</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.52</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.53</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.53</v>
+        <v>19.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.54</v>
+        <v>27</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.53</v>
+        <v>32</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.52</v>
+        <v>30</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.53</v>
+        <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>100</v>
+        <v>15.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.55</v>
+        <v>19</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia</t>
+          <t>NK Maribor</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="G9" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="H9" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="I9" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>2.74</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="Y9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV9" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AW9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>12</v>
       </c>
-      <c r="AE9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX9" t="n">
+      <c r="BA9" t="n">
         <v>20</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>27</v>
       </c>
       <c r="BB9" t="n">
         <v>18</v>
       </c>
       <c r="BC9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>13:20:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Al-Wahda (KSA)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NK Maribor</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.76</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9</v>
+        <v>1.83</v>
       </c>
       <c r="H10" t="n">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>2.74</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.7</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.52</v>
-      </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.36</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U10" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="X10" t="n">
         <v>90</v>
       </c>
       <c r="Y10" t="n">
+        <v>130</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>15</v>
-      </c>
       <c r="AC10" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
         <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="AO10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>20</v>
       </c>
-      <c r="AP10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT10" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>12</v>
-      </c>
       <c r="AU10" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>20</v>
       </c>
       <c r="BB10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>18</v>
       </c>
-      <c r="BC10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>21</v>
-      </c>
       <c r="BE10" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BF10" t="n">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>17</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:20:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al-Wahda (KSA)</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Adalh</t>
+          <t>Puskas Akademia</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="T11" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>2.16</v>
+        <v>3.1</v>
       </c>
       <c r="X11" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Z11" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AF11" t="n">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH11" t="n">
         <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM11" t="n">
         <v>140</v>
       </c>
-      <c r="AK11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>500</v>
-      </c>
       <c r="AN11" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="AP11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB11" t="n">
         <v>11</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BC11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BE11" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puskas Akademia</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L12" t="n">
         <v>1.43</v>
       </c>
-      <c r="G12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="V12" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>3.15</v>
+        <v>2.06</v>
       </c>
       <c r="X12" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>21</v>
       </c>
-      <c r="Y12" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AK12" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
         <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AW12" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BA12" t="n">
         <v>55</v>
       </c>
       <c r="BB12" t="n">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD12" t="n">
         <v>30</v>
       </c>
       <c r="BE12" t="n">
-        <v>11.5</v>
+        <v>65</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.89</v>
+        <v>2.74</v>
       </c>
       <c r="G13" t="n">
-        <v>1.93</v>
+        <v>2.78</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="W13" t="n">
-        <v>2.06</v>
+        <v>1.56</v>
       </c>
       <c r="X13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX13" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y13" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AY13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB13" t="n">
         <v>36</v>
       </c>
-      <c r="AA13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL13" t="n">
+      <c r="BC13" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD13" t="n">
         <v>34</v>
       </c>
-      <c r="AM13" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>29</v>
-      </c>
       <c r="BE13" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="BF13" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.68</v>
+        <v>3.35</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="I14" t="n">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.4</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.58</v>
-      </c>
       <c r="X14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>15</v>
       </c>
-      <c r="Y14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z14" t="n">
+      <c r="BA14" t="n">
         <v>20</v>
       </c>
-      <c r="AA14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN14" t="n">
+      <c r="BB14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD14" t="n">
         <v>23</v>
       </c>
-      <c r="AO14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC14" t="n">
+      <c r="BE14" t="n">
         <v>26</v>
       </c>
-      <c r="BD14" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>50</v>
-      </c>
       <c r="BF14" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BG14" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>2.52</v>
       </c>
       <c r="O15" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>1.81</v>
+        <v>1.49</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>2.92</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="S15" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
         <v>15</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AJ15" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AK15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO15" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AY15" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BB15" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BD15" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BE15" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="BF15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="J16" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="K16" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="L16" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="M16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="N16" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="O16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.62</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.74</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>65</v>
       </c>
       <c r="AE16" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>15.5</v>
+        <v>500</v>
       </c>
       <c r="AH16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="AK16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV16" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>34</v>
+        <v>12.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY16" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="BB16" t="n">
-        <v>48</v>
+        <v>12.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BE16" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="BF16" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.35</v>
+        <v>1.61</v>
       </c>
       <c r="G17" t="n">
-        <v>3.55</v>
+        <v>1.63</v>
       </c>
       <c r="H17" t="n">
-        <v>2.88</v>
+        <v>5.2</v>
       </c>
       <c r="I17" t="n">
-        <v>2.96</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
-        <v>2.68</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="M17" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.76</v>
+        <v>1.13</v>
       </c>
       <c r="P17" t="n">
-        <v>1.37</v>
+        <v>3.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="S17" t="n">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.42</v>
+        <v>1.53</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>2.72</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>2.58</v>
       </c>
       <c r="X17" t="n">
-        <v>6.4</v>
+        <v>60</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="Z17" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.8</v>
+        <v>34</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.5</v>
+        <v>44</v>
       </c>
       <c r="AS17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU17" t="n">
         <v>12</v>
       </c>
-      <c r="AT17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6</v>
-      </c>
       <c r="AV17" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="AX17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BB17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BC17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,184 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.67</v>
+        <v>4.3</v>
       </c>
       <c r="G18" t="n">
-        <v>1.72</v>
+        <v>4.5</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8</v>
+        <v>1.87</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="R18" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="S18" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="T18" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="U18" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="V18" t="n">
-        <v>1.23</v>
+        <v>2.08</v>
       </c>
       <c r="W18" t="n">
-        <v>2.38</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="Y18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN18" t="n">
         <v>32</v>
       </c>
-      <c r="Z18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AO18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AR18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF18" t="n">
         <v>19.5</v>
       </c>
-      <c r="AE18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG18" t="n">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I19" t="n">
         <v>4.1</v>
       </c>
-      <c r="G19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.91</v>
-      </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="R19" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U19" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="V19" t="n">
-        <v>2.08</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="X19" t="n">
-        <v>40</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="Z19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH19" t="n">
         <v>15</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AI19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB19" t="n">
         <v>22</v>
       </c>
-      <c r="AB19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH19" t="n">
+      <c r="BC19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG19" t="n">
         <v>25</v>
       </c>
-      <c r="AI19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>26</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>26</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Boston Utd</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="G20" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L20" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.76</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.89</v>
       </c>
       <c r="X20" t="n">
         <v>17.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA20" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AB20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG20" t="n">
         <v>12</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11</v>
       </c>
       <c r="AH20" t="n">
         <v>15</v>
       </c>
       <c r="AI20" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AJ20" t="n">
         <v>30</v>
       </c>
       <c r="AK20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
         <v>32</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS20" t="n">
         <v>38</v>
       </c>
-      <c r="AP20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>36</v>
-      </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AX20" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BB20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE20" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BF20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG20" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boston Utd</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="I21" t="n">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>1.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.78</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="W21" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Z21" t="n">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AB21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG21" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12</v>
-      </c>
       <c r="AH21" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AI21" t="n">
         <v>44</v>
       </c>
       <c r="AJ21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS21" t="n">
         <v>30</v>
       </c>
-      <c r="AK21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL21" t="n">
+      <c r="AT21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD21" t="n">
         <v>32</v>
       </c>
-      <c r="AM21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW21" t="n">
+      <c r="BE21" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF21" t="n">
         <v>30</v>
       </c>
-      <c r="AX21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>12</v>
-      </c>
       <c r="BG21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -4628,133 +4628,133 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Queens Park</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Raith</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="G22" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="H22" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="O22" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="P22" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="V22" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="W22" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="X22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z22" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>16</v>
-      </c>
       <c r="AA22" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
         <v>12</v>
       </c>
       <c r="AE22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO22" t="n">
         <v>29</v>
       </c>
-      <c r="AF22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>25</v>
-      </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AR22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AT22" t="n">
         <v>10</v>
@@ -4763,51 +4763,51 @@
         <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AY22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BB22" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC22" t="n">
         <v>32</v>
       </c>
-      <c r="BC22" t="n">
-        <v>30</v>
-      </c>
       <c r="BD22" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BE22" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BF22" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="BG22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Queens Park</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Raith</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="G23" t="n">
-        <v>3.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>2.52</v>
+        <v>1.53</v>
       </c>
       <c r="I23" t="n">
-        <v>2.64</v>
+        <v>1.57</v>
       </c>
       <c r="J23" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="M23" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>2.82</v>
+        <v>4.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>1.59</v>
+        <v>2.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.56</v>
+        <v>1.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X23" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV23" t="n">
         <v>5.2</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AW23" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU23" t="n">
+      <c r="AX23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG23" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>27</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>30</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,184 +5011,184 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6.8</v>
+        <v>2.46</v>
       </c>
       <c r="G24" t="n">
-        <v>8.4</v>
+        <v>2.48</v>
       </c>
       <c r="H24" t="n">
-        <v>1.52</v>
+        <v>2.72</v>
       </c>
       <c r="I24" t="n">
-        <v>1.56</v>
+        <v>2.74</v>
       </c>
       <c r="J24" t="n">
         <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="P24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S24" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.92</v>
-      </c>
       <c r="T24" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="V24" t="n">
-        <v>2.78</v>
+        <v>1.57</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="X24" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="Z24" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AD24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF24" t="n">
         <v>19</v>
       </c>
-      <c r="AE24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO24" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.9</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AT24" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="AX24" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AY24" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA24" t="n">
         <v>26</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="BC24" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.3</v>
+        <v>22</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.4</v>
+        <v>48</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -5210,373 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.46</v>
+        <v>3.9</v>
       </c>
       <c r="G25" t="n">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="H25" t="n">
-        <v>2.74</v>
+        <v>1.85</v>
       </c>
       <c r="I25" t="n">
-        <v>2.76</v>
+        <v>1.86</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K25" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="R25" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="T25" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U25" t="n">
         <v>3.15</v>
       </c>
       <c r="V25" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="W25" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="X25" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF25" t="n">
         <v>34</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AG25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS25" t="n">
         <v>22</v>
       </c>
-      <c r="Z25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AT25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV25" t="n">
         <v>11</v>
       </c>
-      <c r="AD25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM25" t="n">
+      <c r="AW25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE25" t="n">
         <v>42</v>
       </c>
-      <c r="AN25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>40</v>
-      </c>
       <c r="BF25" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Atletico Madrid</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X26" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>65</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
